--- a/أزهر دمياط/Endocrinology/Endocrinology_Questions.xlsx
+++ b/أزهر دمياط/Endocrinology/Endocrinology_Questions.xlsx
@@ -35478,7 +35478,7 @@
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>Atrophy of Type II muscle fibers. The answer is</t>
+          <t>Atrophy of Type II muscle fibers.</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
@@ -35488,7 +35488,7 @@
       </c>
       <c r="R673" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="V673" t="inlineStr">
@@ -44079,7 +44079,7 @@
       </c>
       <c r="I826" t="inlineStr">
         <is>
-          <t>d-Positive family history is less common than in type 11</t>
+          <t>Positive family history is less common than in type 11</t>
         </is>
       </c>
       <c r="J826" t="inlineStr">

--- a/أزهر دمياط/Endocrinology/Endocrinology_Questions.xlsx
+++ b/أزهر دمياط/Endocrinology/Endocrinology_Questions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE986"/>
+  <dimension ref="A1:AF982"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,21 +572,16 @@
           <t>ExplanationImageMasks</t>
         </is>
       </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ModelAnswer</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="C2" t="inlineStr">
         <is>
-          <t>Qs: Radiological finding in thyrotoxicosis?</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Radioiodine uptake is increased in thyrotoxicosis caused by increased hormone synthesis and decreased in thyroiditis. Thyroid scintigraphy distinguishes the pattern: diffuse uptake suggests Graves disease, a solitary hot nodule suggests a toxic adenoma, and multiple areas of uptake suggest toxic multinodular goiter.</t>
+          <t>Radiological finding in thyrotoxicosis?</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -612,6 +607,11 @@
           <t>Department, IMP Written 2026</t>
         </is>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Radioiodine uptake is increased in thyrotoxicosis caused by increased hormone synthesis and decreased in thyroiditis. Thyroid scintigraphy distinguishes the pattern: diffuse uptake suggests Graves disease, a solitary hot nodule suggests a toxic adenoma, and multiple areas of uptake suggest toxic multinodular goiter.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
@@ -10800,38 +10800,33 @@
           <t>Female patient 28 y. old presented with tremors, excessive sweating insomnia, tachycardia &amp; wt loss inspite of good feeding a. What is your diagnosis? b. What are the investigations? c. TTT you suggest?</t>
         </is>
       </c>
-      <c r="R201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T201" t="inlineStr">
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
         <is>
           <t>a. Diagnosis: thyrotoxicosis, most likely Graves' disease (young female with tremor, sweating, insomnia, tachycardia and weight loss despite good appetite).
 b. Investigations: serum TSH (suppressed) with free T4 and free T3 (raised); TSH-receptor antibodies (TRAb/TSI) to confirm Graves'; thyroid ultrasound with Doppler (diffuse vascular goitre) and/or radioactive iodine uptake scan (diffuse increased uptake; low uptake suggests thyroiditis); ECG for sinus tachycardia or atrial fibrillation; CBC and liver function tests as a baseline before antithyroid drugs.
 c. Treatment: beta-blocker (propranolol 40 mg every 6-8 h) for symptoms; antithyroid drugs - carbimazole/methimazole (propylthiouracil in the first trimester of pregnancy) for 12-18 months, titrated or block-replace, with warning about agranulocytosis (report sore throat/fever); definitive treatment for relapse or large goitre: radioactive iodine (contraindicated in pregnancy and active severe ophthalmopathy) or near-total thyroidectomy after rendering euthyroid; follow up with thyroid function tests.</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="C202" t="inlineStr">
@@ -10839,38 +10834,33 @@
           <t>A female patient 45 y. old presented with constipation, wt gain skin &amp; hair changes &amp; bradycardia. a. What is the diagnosis? b. What are investigations? c. Treatment you suggest</t>
         </is>
       </c>
-      <c r="R202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T202" t="inlineStr">
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
         <is>
           <t>a. Diagnosis: primary hypothyroidism, most likely autoimmune (Hashimoto's) thyroiditis (constipation, weight gain, skin and hair changes, bradycardia).
 b. Investigations: serum TSH (raised) and free T4 (low); anti-TPO and anti-thyroglobulin antibodies; lipid profile (hypercholesterolaemia); CBC (anaemia); ECG (bradycardia, low voltage); CK may be raised; thyroid ultrasound if goitre or nodule.
 c. Treatment: lifelong levothyroxine (L-T4) about 1.6 microgram/kg/day taken on an empty stomach; in elderly or cardiac patients start low (25 microgram/day) and increase slowly; recheck TSH after 6-8 weeks and adjust the dose to keep TSH normal, then yearly.</t>
         </is>
       </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="C203" t="inlineStr">
@@ -10878,38 +10868,33 @@
           <t>A 38 y. old lady noticed that she is losing weight and suffers from anxiety &amp; insomnia at night. Examination revealed a temp. 36.3°C pulse 135/mm, and she has warm tremoring hands. ESR is normal. a. What is your diagnosis? b. What are the investigations? c. TTT you suggest?</t>
         </is>
       </c>
-      <c r="R203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T203" t="inlineStr">
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
         <is>
           <t>a. Diagnosis: thyrotoxicosis, most likely Graves' disease (weight loss, anxiety, insomnia, marked tachycardia and warm tremulous hands); the normal ESR and normal temperature argue against subacute (de Quervain's) thyroiditis.
 b. Investigations: TSH (suppressed), free T4 and free T3 (raised); TSH-receptor antibodies; radioactive iodine uptake scan (diffuse high uptake in Graves', low in thyroiditis) and thyroid ultrasound with Doppler; ECG (sinus tachycardia or atrial fibrillation); CBC and liver functions as baseline.
 c. Treatment: propranolol for symptomatic control; carbimazole/methimazole (e.g. 20-40 mg/day, then titrated) for 12-18 months, with counselling about agranulocytosis; radioactive iodine or thyroidectomy for relapse, large goitre or intolerance of drugs; regular thyroid function follow-up.</t>
         </is>
       </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="C204" t="inlineStr">
@@ -10917,38 +10902,33 @@
           <t>A 45 y. old lady presented to the medical clinic complaining from an increasing sense of general fatigue and intolerance to colds since three months. In the last two weeks her voice became increasingly hoarse. Examination revealed that her temp. is 36.9°C, pulse 60/min, BP 140/80, her skin is dry. Neurological examination was negative but the knee reflexes were slow in their response. a. What is the diagnosis? b. What are investigations? c. Treatment you suggest.</t>
         </is>
       </c>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T204" t="inlineStr">
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
         <is>
           <t>a. Diagnosis: primary hypothyroidism (fatigue, cold intolerance, hoarse voice, dry skin, relative bradycardia, diastolic hypertension and delayed relaxation of the tendon reflexes), most likely Hashimoto's thyroiditis.
 b. Investigations: TSH (raised) and free T4 (low); anti-TPO antibodies; lipid profile, CBC, serum sodium, CK; ECG; thyroid ultrasound if a goitre is palpable.
 c. Treatment: levothyroxine replacement for life, starting at a low dose in older patients (25-50 microgram/day) and increasing gradually to a full dose (about 1.6 microgram/kg/day); monitor TSH every 6-8 weeks until normal, then annually.</t>
         </is>
       </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="C205" t="inlineStr">
@@ -10956,38 +10936,33 @@
           <t>A woman 44 y. old complaining of increasing weakness and constipation over the last 3 months. O/E, she was pale with puffy eyelids. Her pulse was 60/min, regular. Her serum TSH 201 U/ml (N. 1-6) a. What is the possible diagnosis? b. How can you explain the clinical and laboratory findings? c. What is the treatment and how can you follow up her condition?</t>
         </is>
       </c>
-      <c r="R205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T205" t="inlineStr">
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
         <is>
           <t>a. Diagnosis: primary hypothyroidism (markedly raised TSH with weakness, constipation, pallor, puffy eyelids and bradycardia), most likely autoimmune (Hashimoto's) thyroiditis.
 b. Explanation: failure of the thyroid gland lowers T4/T3, removing negative feedback so pituitary TSH rises greatly. Thyroid hormone deficiency reduces metabolic rate and sympathetic sensitivity (bradycardia, weakness), slows gut motility (constipation), causes accumulation of glycosaminoglycans in the tissues (myxoedema: puffy eyelids) and anaemia plus skin vasoconstriction and carotenaemia (pallor).
 c. Treatment: levothyroxine daily on an empty stomach, starting at a moderate dose (lower if elderly or cardiac) and titrating. Follow-up: TSH (with free T4) 6-8 weeks after each dose change, aiming for TSH within the normal range, then every 6-12 months; clinical review of symptoms, weight, pulse and anaemia.</t>
         </is>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="C206" t="inlineStr">
@@ -10995,12 +10970,27 @@
           <t>A 35 y. old woman presented with 6 months history of diarrhea, weight loss and palpitation. She was seen by psychiatrist for feeling anxious &amp; irritable and was given atranquilizer without good response. a. What is the most important disease you have to exclude? b. Mention important clinical signs that can help you in its diagnosis? c. Mention important blood testes help you in its diagnosis? d. If the diagnosis proved to be correct how to manage?</t>
         </is>
       </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T206" t="inlineStr">
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
         <is>
           <t>a. Thyrotoxicosis (hyperthyroidism, e.g. Graves' disease) must be excluded before labelling the patient as an anxiety state.
 b. Clinical signs: sinus tachycardia or atrial fibrillation with wide pulse pressure; warm moist skin and fine tremor of the outstretched hands; lid retraction and lid lag, exophthalmos; diffuse goitre with a bruit; proximal myopathy and brisk reflexes; pretibial myxoedema and thyroid acropachy in Graves'. (Sleeping pulse remains high in thyrotoxicosis but falls in anxiety.)
@@ -11008,26 +10998,6 @@
 d. Management: beta-blocker (propranolol) for symptoms; antithyroid drug (carbimazole/methimazole) for 12-18 months; definitive radioactive iodine or thyroidectomy (after making the patient euthyroid) for relapse, large goitre or drug side effects; follow-up thyroid function tests.</t>
         </is>
       </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="C207" t="inlineStr">
@@ -11035,38 +11005,33 @@
           <t>A 45 y. old female patient complained of regular palpitation that used to increase by exertion, but sometimes also occur during rest, she reported that she had marked weight loss in spite of her reasonable appetite. a. What is your provisional diagnosis? b. What is your D.D.? c. What laboratory tests you need to reach a definitive diagnosis?</t>
         </is>
       </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T207" t="inlineStr">
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
         <is>
           <t>a. Provisional diagnosis: thyrotoxicosis (hyperthyroidism), most likely Graves' disease or toxic nodular goitre (palpitation at rest as well as on exertion, weight loss despite good appetite).
 b. Differential diagnosis: anxiety state/panic disorder; diabetes mellitus (weight loss with good appetite); pheochromocytoma; paroxysmal supraventricular tachycardia or other arrhythmia; malabsorption; malignancy; exogenous thyroxine intake.
 c. Laboratory tests: serum TSH (suppressed) with free T4 and free T3 (raised) - T3 toxicosis possible; TSH-receptor antibodies; radioactive iodine uptake scan/thyroid scintigraphy to distinguish Graves' (diffuse), toxic nodule or multinodular goitre (hot nodules) and thyroiditis (low uptake); thyroid ultrasound; ECG; blood glucose.</t>
         </is>
       </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="C208" t="inlineStr">
@@ -11074,12 +11039,27 @@
           <t>A 55 y. old female presented with coma. Examination revealed puffy face and mild lower limb edema. Her temperature was 35°C. her pulse was 50 beats/mm &amp; regular. Her relatives stated that she was taking pills regularly for long time and she stopped the ttt. The last 4 weeks, she also noticed that her speech was clumsy and slows in the last weeks. a. What is your diagnosis? b. What is your differential diagnosis? c. What are you doing to confirm your diagnosis? d. What ttt should be given?</t>
         </is>
       </c>
-      <c r="R208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T208" t="inlineStr">
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
         <is>
           <t>a. Diagnosis: myxoedema coma (severe decompensated hypothyroidism) after stopping thyroxine replacement - coma with hypothermia (35°C), bradycardia, puffy face, oedema and slow clumsy speech.
 b. Differential diagnosis: other causes of coma with hypothermia - hypoglycaemia, cerebrovascular stroke, drug overdose (sedatives), hypopituitary coma, adrenal crisis, uraemic or hepatic coma, and exposure hypothermia.
@@ -11087,26 +11067,6 @@
 d. Treatment: ICU admission; airway support and ventilation if hypoventilating; IV hydrocortisone 100 mg every 8 h before/with thyroid hormone; IV levothyroxine (loading 200-400 microgram then 50-100 microgram daily) with or without liothyronine; passive slow rewarming; cautious IV fluids and correction of hyponatraemia and hypoglycaemia; treat precipitating infection; then oral levothyroxine for life with education about compliance.</t>
         </is>
       </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="C209" t="inlineStr">
@@ -11114,12 +11074,27 @@
           <t>A 60 y. old female complained of tiredness, constipation, weight gain and tingling in her hands and feet. O/E, she was obese, with pale puffy face. Investigations revealed mild normocytic normochromic anemia and hypercholesterolemia, chest X-ray revealed cardiomegaly. a. What is your diagnosis? b. How would you explain the chest X-ray findings? c. What is the possible cause for the tingling in her hands? d. How would you treat this lady?</t>
         </is>
       </c>
-      <c r="R209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T209" t="inlineStr">
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
         <is>
           <t>a. Diagnosis: primary hypothyroidism (myxoedema).
 b. Chest X-ray: the cardiomegaly is mainly due to pericardial effusion (accumulation of protein- and glycosaminoglycan-rich fluid) and in addition dilated hypothyroid cardiomyopathy; hypercholesterolaemia also predisposes to coronary artery disease.
@@ -11127,26 +11102,6 @@
 d. Treatment: levothyroxine starting at a low dose (25 microgram/day because she is 60 years old with cardiac involvement) increased gradually every 2-4 weeks to full replacement, monitoring TSH and watching for angina; the anaemia, hypercholesterolaemia, pericardial effusion and carpal tunnel symptoms usually improve with euthyroidism.</t>
         </is>
       </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="C210" t="inlineStr">
@@ -11154,37 +11109,32 @@
           <t>A 22 y. old female student suffered from IDDM for the last 7 years. She started a few weeks ago to complain of tachycardia, sweating &amp; nervousness. a. Enumerate possible causes of her complaints. b. Discuss diagnosis &amp; management of one of them.</t>
         </is>
       </c>
-      <c r="R210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T210" t="inlineStr">
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
         <is>
           <t>a. Possible causes of tachycardia, sweating and nervousness in a type 1 diabetic: hypoglycaemia (insulin overdose, missed meals, exercise); thyrotoxicosis (Graves' disease or Hashitoxicosis - autoimmune thyroid disease is associated with type 1 DM); diabetic autonomic neuropathy (resting tachycardia); anxiety state; pheochromocytoma (rare); drugs (e.g. beta-agonists, excessive caffeine).
 b. Hypoglycaemia (example): diagnosis by Whipple's triad - symptoms, low blood glucose (below 70 mg/dl, adrenergic symptoms like tachycardia, sweating, tremor and nervousness, and neuroglycopenic symptoms) and relief after glucose; check capillary glucose during symptoms and review insulin doses and HbA1c. Management: if conscious give 15-20 g rapid oral glucose and recheck after 15 min, then a complex carbohydrate snack; if unconscious give IV 50 ml of 50% dextrose (or 20% dextrose) or IM glucagon 1 mg; then adjust insulin regimen, regular meals and snacks, glucose monitoring, education of patient and family, carry sugar and a diabetic card. (Alternatively thyrotoxicosis: TSH, free T4/T3, TRAb; treat with beta-blocker and carbimazole.)</t>
         </is>
       </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="C211" t="inlineStr">
@@ -11192,38 +11142,33 @@
           <t>A 72 y. old lady complaining of fatigue has become increasingly lethargic. She also said that her hair is thinning. Her pulse rate is 52/min, regular and BP is 138/90 mmHg. Examination of her heart chest and abdomen is normal. a. What is your diagnosis (explain why)? b. How do you investigate this case? c. How would you manage the case?</t>
         </is>
       </c>
-      <c r="R211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T211" t="inlineStr">
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
         <is>
           <t>a. Diagnosis: primary hypothyroidism (elderly woman with fatigue, lethargy, hair thinning, bradycardia 52/min and diastolic hypertension); hypothyroidism is common in elderly women, usually due to autoimmune thyroiditis.
 b. Investigations: TSH (raised) and free T4 (low); anti-TPO antibodies; lipid profile, CBC, serum sodium; ECG (bradycardia, ischaemic changes before therapy); (if TSH is low or normal with low T4, suspect secondary hypothyroidism and assess the pituitary).
 c. Management: levothyroxine started at a low dose (12.5-25 microgram/day because of age and risk of ischaemic heart disease) increased by 25 microgram every 3-4 weeks guided by symptoms and TSH; watch for angina and arrhythmia; lifelong treatment with yearly TSH once stable.</t>
         </is>
       </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W211" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="C212" t="inlineStr">
@@ -11231,38 +11176,33 @@
           <t>Middle age male patient presented with chronic fatigue &amp; hyperpigmentaion on examination his BP was 95/75 mmhg on supine and decreased on standing a) What is your diagnosis? b) What are the investigations? c) TTT you suggest?</t>
         </is>
       </c>
-      <c r="R212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T212" t="inlineStr">
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
         <is>
           <t>a. Diagnosis: primary adrenal insufficiency (Addison's disease) - chronic fatigue, hyperpigmentation and hypotension with postural drop.
 b. Investigations: 8 a.m. serum cortisol (low) with plasma ACTH (high); short Synacthen (ACTH stimulation) test - inadequate cortisol rise (peak below 18-20 microgram/dl); serum sodium (low), potassium (high), urea, blood glucose (low); plasma renin (high) and aldosterone (low); 21-hydroxylase adrenal antibodies; CT of the adrenals and tests for tuberculosis (chest X-ray) when autoimmunity is not proven.
 c. Treatment: glucocorticoid replacement with hydrocortisone 15-25 mg/day in divided doses (larger in the morning); mineralocorticoid fludrocortisone 0.05-0.2 mg/day; liberal salt intake; sick-day rules (double the dose in illness, IV/IM hydrocortisone if vomiting or before surgery); steroid card/bracelet and emergency injection kit; treat the cause (e.g. anti-tuberculous therapy).</t>
         </is>
       </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="C213" t="inlineStr">
@@ -11270,38 +11210,33 @@
           <t>35 years old female suffer from paroxysmal HTN and attack of pallor and sweating, headache, anxiety, palpitation, abdominal pain and vomiting, constipation, wt loss and intolerance also evident. a) What is your diagnosis? b) What are the investigations? c) TTT you suggest?</t>
         </is>
       </c>
-      <c r="R213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T213" t="inlineStr">
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
         <is>
           <t>a. Diagnosis: pheochromocytoma (paroxysmal hypertension with attacks of headache, sweating, palpitation, pallor and anxiety, plus weight loss, heat intolerance and constipation from catecholamine excess).
 b. Investigations: biochemical confirmation by plasma free metanephrines or 24-hour urinary fractionated metanephrines and catecholamines (VMA less sensitive); blood glucose (hyperglycaemia); localisation by CT or MRI of the adrenals/abdomen, then MIBG or PET scan for extra-adrenal or metastatic disease; screening for associated syndromes (MEN 2 - serum calcitonin, calcium and PTH; von Hippel-Lindau, NF1) and genetic testing.
 c. Treatment: preoperative alpha-blockade (phenoxybenzamine or doxazosin) for 10-14 days with high salt and fluid intake, then a beta-blocker added only after adequate alpha-blockade; surgical removal by laparoscopic adrenalectomy with careful anaesthesia (control of hypertensive crisis by IV phentolamine or nitroprusside, and postoperative hypotension/hypoglycaemia by fluids and glucose); for inoperable or malignant disease, alpha-methyl-para-tyrosine, MIBG therapy or chemotherapy; long-term follow-up with metanephrines.</t>
         </is>
       </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="C214" t="inlineStr">
@@ -11309,38 +11244,33 @@
           <t>Male patient 65 years old recently suffered from trunked obesity, DM, HTN &amp; myopathy and presented with sudden back pain with history trauma. a) DD of this case? b) What are the investigations? c) TTT you suggest?</t>
         </is>
       </c>
-      <c r="R214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T214" t="inlineStr">
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
         <is>
           <t>a. Differential diagnosis: Cushing's syndrome (truncal obesity, diabetes, hypertension and proximal myopathy) complicated by an osteoporotic vertebral collapse fracture after minor trauma. Causes to differentiate: exogenous (iatrogenic) glucocorticoid intake; ACTH-dependent - pituitary Cushing's disease and ectopic ACTH secretion (e.g. small cell lung carcinoma, especially in a 65-year-old man); ACTH-independent adrenal adenoma or carcinoma. Other causes of back pain: vertebral metastases (e.g. from lung or prostate cancer), multiple myeloma, traumatic fracture.
 b. Investigations: screening - 24-hour urinary free cortisol, overnight 1 mg dexamethasone suppression test, late-night salivary cortisol; then plasma ACTH (suppressed = adrenal; normal/high = pituitary or ectopic), high-dose dexamethasone suppression and CRH tests, pituitary MRI, adrenal CT, chest CT for an ectopic source, inferior petrosal sinus sampling; serum potassium (hypokalaemia in ectopic ACTH), blood glucose/HbA1c; spine X-ray/MRI and DEXA scan for the fracture and osteoporosis.
 c. Treatment: treat the cause - transsphenoidal pituitary surgery, adrenalectomy, or removal of the ectopic tumour; withdraw exogenous steroids gradually; medical control of cortisol (ketoconazole, metyrapone, osilodrostat) when surgery is delayed or not possible; control of diabetes, hypertension and hypokalaemia; for the fracture - analgesia, rest/brace, calcium, vitamin D and bisphosphonates; postoperative glucocorticoid replacement until the axis recovers.</t>
         </is>
       </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="C215" t="inlineStr">
@@ -11348,12 +11278,27 @@
           <t>Female patient complaining of amenorrhea for 2 years following the last difficult labor complicated by severe postpartum hemorrhage, from that time she was told that she is hypotensive. She has a well-marked asthenia &amp; can't tolerate cold weather a) What are other symptoms to be asked for? b) What is the diagnosis? c) What are the necessary investigations to prove the diagnosis? d) What are the main lines of treatment? e) What is the prognosis?</t>
         </is>
       </c>
-      <c r="R215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T215" t="inlineStr">
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
         <is>
           <t>a. Other symptoms to ask about: failure of lactation after delivery; loss of axillary and pubic hair; loss of libido, breast atrophy; symptoms of hypothyroidism (cold intolerance, constipation, weight gain, dry skin, slowness); symptoms of adrenal insufficiency (fatigue, anorexia, nausea, weight loss, postural dizziness, hypoglycaemic attacks); pallor (skin depigmentation) and loss of energy; polyuria is rare.
 b. Diagnosis: Sheehan's syndrome - postpartum ischaemic necrosis of the anterior pituitary causing hypopituitarism (panhypopituitarism).
@@ -11362,26 +11307,6 @@
 e. Prognosis: good with adequate lifelong replacement and patient education; risk of adrenal crisis and death with stress, infection or surgery if steroid cover is not increased; the pituitary damage is permanent.</t>
         </is>
       </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="C216" t="inlineStr">
@@ -11389,38 +11314,33 @@
           <t>A male patient aged 35 years presented with asthenia. He has been under therapy for his low blood pressure for sometimes. His dermatologist had along run of therapy for discoloration on his trunk &amp; for the deep color of skin. a) What do you expect to find in his history and on full clinical examination? b) What are the steps needed for the diagnosis? c) What do you suggest for treatment?</t>
         </is>
       </c>
-      <c r="R216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T216" t="inlineStr">
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
         <is>
           <t>a. Expected findings (primary adrenal insufficiency / Addison's disease): history - fatigue and weakness, anorexia, weight loss, nausea, vomiting, abdominal pain, salt craving, postural dizziness and fainting, hypoglycaemic attacks, loss of axillary and pubic hair in women, depression; history of tuberculosis or other autoimmune disease; examination - diffuse hyperpigmentation especially of exposed areas, skin creases, scars, knuckles, buccal mucosa and gums; low blood pressure with postural drop; weight loss; vitiligo may coexist.
 b. Steps for diagnosis: 8 a.m. serum cortisol (low) and plasma ACTH (high); short Synacthen test (failure of cortisol to rise); electrolytes - hyponatraemia, hyperkalaemia, raised urea; blood glucose; plasma renin (high) and aldosterone (low); adrenal 21-hydroxylase antibodies; chest X-ray, tuberculin test and adrenal CT (calcification in tuberculosis) to find the cause.
 c. Treatment: hydrocortisone 15-25 mg/day in 2-3 divided doses plus fludrocortisone 50-200 microgram/day; adequate salt; increase the dose during illness, trauma or surgery (parenteral hydrocortisone if vomiting); steroid alert card and emergency hydrocortisone injection; treat the underlying cause (e.g. antituberculous therapy); monitor blood pressure, electrolytes and weight.</t>
         </is>
       </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="C217" t="inlineStr">
@@ -11428,37 +11348,32 @@
           <t>A 64 years old man noticed that he had gained 8 kg in weight over the past 6 months. He started to get easily bruising, he found difficulty in getting up from his arm chair or to climb stairs, he felt depressed. On examination he is overweight particularly on the abdominal region with purpurish stria on his abdomen and thighs. His blood pressure is 168/100, examination of his heart respiratory system and abdomen is normal. There is some weakness in shoulder and hip regions. His routine examinations are within normal abort from elevated 2 hours post prandial blood sugar. a) What is the provisional diagnosis? b) How would you investigate and manage this patient?</t>
         </is>
       </c>
-      <c r="R217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T217" t="inlineStr">
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
         <is>
           <t>a. Provisional diagnosis: Cushing's syndrome (weight gain with central obesity, easy bruising, purple striae, proximal myopathy, depression, hypertension and impaired glucose tolerance); in a 64-year-old man ectopic ACTH secretion (e.g. from a lung tumour) must be considered besides pituitary Cushing's disease, adrenal tumour and exogenous steroid intake.
 b. Investigation: exclude exogenous glucocorticoid use; confirm hypercortisolism with 24-hour urinary free cortisol, overnight 1 mg dexamethasone suppression test and late-night salivary cortisol (two positive tests); then plasma ACTH - suppressed (adrenal adenoma/carcinoma: CT adrenals) or normal/raised (ACTH-dependent: high-dose dexamethasone suppression and CRH tests, pituitary MRI, inferior petrosal sinus sampling, and CT chest/abdomen for an ectopic source); also serum potassium, blood glucose/OGTT, DEXA scan. Management: transsphenoidal adenomectomy for Cushing's disease (radiotherapy or bilateral adrenalectomy if it fails); unilateral adrenalectomy for an adrenal adenoma; resection of the ectopic tumour; medical cortisol-lowering drugs (metyrapone, ketoconazole, osilodrostat, mifepristone) before surgery or if inoperable; treat hypertension, diabetes, hypokalaemia and osteoporosis; postoperative hydrocortisone replacement until the HPA axis recovers.</t>
         </is>
       </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="C218" t="inlineStr">
@@ -11466,38 +11381,33 @@
           <t>A 25 y. old white male consulted his physician for recurrent headache &amp; shortness of breath. The patient was obese and his abdomen was fatty. His BP was 170/100. His face was flushed and greasy, there was some acne on his chest wall. Urine was positive for glucose (++) a) What is your diagnosis? b) What is your differential diagnosis? c) What other tests would you like to ask to reach a definitive diagnosis?</t>
         </is>
       </c>
-      <c r="R218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T218" t="inlineStr">
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
         <is>
           <t>a. Diagnosis: Cushing's syndrome (obesity with fatty abdomen, hypertension, plethoric greasy face, acne and glycosuria), probably pituitary-dependent Cushing's disease in a young man, or iatrogenic steroid intake.
 b. Differential diagnosis: simple (exogenous) obesity with essential hypertension and type 2 diabetes (metabolic syndrome); pseudo-Cushing's state (alcoholism, depression); polycythaemia (plethora with headache); pheochromocytoma; anabolic steroid/androgen abuse (acne, hypertension); congenital adrenal hyperplasia.
 c. Tests for a definitive diagnosis: 24-hour urinary free cortisol, overnight 1 mg dexamethasone suppression test, late-night salivary cortisol, low-dose 48-hour dexamethasone suppression test; plasma ACTH; high-dose dexamethasone suppression and CRH tests; pituitary MRI and adrenal CT; blood glucose/HbA1c, serum potassium, CBC (polycythaemia).</t>
         </is>
       </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="C219" t="inlineStr">
@@ -11505,38 +11415,33 @@
           <t>15 y. old boy known history of IDDM presented to ER with coma a. DD of causes? b. What are the investigations? c. Management on of the above?</t>
         </is>
       </c>
-      <c r="R219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T219" t="inlineStr">
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
         <is>
           <t>a. Differential diagnosis of coma in a type 1 diabetic boy: hypoglycaemic coma; diabetic ketoacidosis; (rarely) hyperosmolar hyperglycaemic state or lactic acidosis; non-diabetic causes - head injury, meningitis/encephalitis, cerebral oedema, drug or alcohol intoxication, epilepsy (post-ictal).
 b. Investigations: immediate bedside capillary glucose; then laboratory blood glucose, blood or urine ketones, arterial/venous blood gases (pH, bicarbonate, anion gap), serum sodium and potassium, urea and creatinine, serum osmolality, CBC and cultures for infection, urine analysis; CT brain and CSF examination if metabolic causes are excluded.
 c. Management of the above: hypoglycaemia - IV 50 ml of 50% (or 2-5 ml/kg of 10%) dextrose or IM glucagon, followed by a dextrose infusion and oral carbohydrate on waking, then review of insulin dose and meals. DKA - isotonic saline for rehydration, IV regular insulin infusion 0.1 unit/kg/h, potassium replacement according to serum K, add dextrose when glucose falls to about 250 mg/dl, bicarbonate only if pH below 6.9, treat the precipitating infection, and monitor glucose, electrolytes, pH and watch for cerebral oedema.</t>
         </is>
       </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="C220" t="inlineStr">
@@ -11544,38 +11449,33 @@
           <t>35 y. old obese female complain of Wt loss inspite of increase appetite pruritus in her vulva and frequent waking up for urination at night a. What is the diagnosis? b. What are the investigations? c. Complication of the case?</t>
         </is>
       </c>
-      <c r="R220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T220" t="inlineStr">
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
         <is>
           <t>a. Diagnosis: diabetes mellitus (type 2, uncontrolled) - weight loss despite increased appetite (polyphagia), nocturia/polyuria and vulval pruritus (candidal vulvovaginitis) in an obese woman.
 b. Investigations: fasting plasma glucose (126 mg/dl or more), 2-hour post-prandial or OGTT glucose (200 mg/dl or more), random glucose 200 mg/dl or more with symptoms, HbA1c (6.5% or more); urine for glucose, ketones and albumin (albumin/creatinine ratio); lipid profile; renal function; fundus examination; ECG; vaginal swab for Candida.
 c. Complications: acute - diabetic ketoacidosis, hyperosmolar hyperglycaemic state, hypoglycaemia with treatment, and infections (candidiasis, urinary tract infection, skin infections); chronic microvascular - retinopathy, nephropathy, neuropathy; macrovascular - coronary artery disease, stroke, peripheral vascular disease; diabetic foot.</t>
         </is>
       </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="C221" t="inlineStr">
@@ -11583,38 +11483,33 @@
           <t>A 16 y. old boy, with known insulin dependent D.M., was admitted to hospital in a lethargic drowsy condition, with history of vomiting, polyuria &amp; polydespia 3 days before. He was taking soluble insulin 10 units each morning. His temp. was 37.6 °C, pulse was 140/min, BP 100/60 mmHg, heart, lung &amp; abdomen were clinical normal a. What is your diagnosis? b. What are the possible precipitating factors? c. What is your immediate management</t>
         </is>
       </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T221" t="inlineStr">
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
         <is>
           <t>a. Diagnosis: diabetic ketoacidosis (DKA) in a type 1 diabetic, with severe dehydration (tachycardia 140/min, low BP) and impaired consciousness.
 b. Possible precipitating factors: inadequate insulin (only 10 units of soluble insulin once daily, missed doses or reduction of insulin during vomiting/anorexia); infection (fever 37.6°C - e.g. respiratory, urinary tract or gastroenteritis); other acute stress (trauma, surgery); dietary indiscretion; insulin pump failure; psychological stress or non-compliance.
 c. Immediate management: ABC and IV access; blood for glucose, ketones, blood gases, electrolytes, urea and creatinine, CBC and cultures; IV normal saline 1 L in the first hour (10-20 ml/kg in children) then replacement over 24-48 h; IV regular insulin infusion 0.1 unit/kg/h after confirming K above 3.3 mmol/L; potassium replacement added to fluids according to serum K; 5% dextrose when glucose falls to about 250 mg/dl while continuing insulin until ketoacidosis resolves; bicarbonate only for pH below 6.9; hourly glucose and 2-4 hourly electrolytes and pH, fluid balance chart, watch for cerebral oedema; treat infection; then switch to a proper subcutaneous basal-bolus insulin regimen and education.</t>
         </is>
       </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="C222" t="inlineStr">
@@ -11622,38 +11517,33 @@
           <t>A 12 y. old underweight boy had fever for 2 days. Examination revealed a very tender swelling in his right buttock that was diagnosed as a gluteus abscess. Next day the patient was very confused and his mouth was dry, had also acidotic breathing. a. What is the likely diagnosis for the confusion? b. What is your differential diagnosis? c. What further tests do you like to perform to this patient to reach a diagnosis?</t>
         </is>
       </c>
-      <c r="R222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T222" t="inlineStr">
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
         <is>
           <t>a. Likely diagnosis for the confusion: diabetic ketoacidosis in a previously undiagnosed type 1 diabetic (underweight child), precipitated by infection (gluteal abscess) - dry mouth (dehydration), acidotic (Kussmaul) breathing and confusion.
 b. Differential diagnosis: septicaemia/septic shock with lactic acidosis; meningitis or encephalitis; salicylate or other poisoning; uraemic acidosis (acute kidney injury); hypoglycaemia; hyperosmolar hyperglycaemic state; gastroenteritis with dehydration and acidosis.
 c. Further tests: blood glucose; blood/urine ketones (beta-hydroxybutyrate); arterial blood gases (low pH and bicarbonate, high anion gap); serum sodium, potassium, urea and creatinine; serum osmolality; CBC with blood culture and pus culture from the abscess; urine analysis; HbA1c; (C-peptide and islet antibodies later to confirm type 1 DM); lumbar puncture if meningitis is suspected.</t>
         </is>
       </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="C223" t="inlineStr">
@@ -11661,38 +11551,33 @@
           <t>A 60 y. old male presented to ER with disturbed level of consciousness of 1 day duration. His relatives reported that he had weight loss over the past few weeks despite of good appetite. They also gave history of polyuria for the last 2-3 weeks. O/E, the pt. was drowsy and dehydrate with sunken eyes. His BP was 140/65 mmHg, temp. was 37°C &amp; tests revealed a Hb of 16 gm/dl, a hematocrit of 50, WBCs 11.000/mm3 &amp; platelets 380.000/mm3. Serum creat. Was 1.8 mg/dl &amp; BUN was 46 mgldl. Random blood sugar was 684 mg/dl. Arterial blood gases (ABG) revealed normal serum bicarbonate. a. What is your provisional diagnosis? b. What investigation would you like to do to confirm your diagnosis? c. What is your suggested line of ttt?</t>
         </is>
       </c>
-      <c r="R223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T223" t="inlineStr">
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
         <is>
           <t>a. Provisional diagnosis: hyperosmolar hyperglycaemic state (HHS; non-ketotic hyperosmolar coma) in a newly presenting type 2 diabetic - elderly patient, very high glucose (684 mg/dl), severe dehydration (haemoconcentration: Hb 16, hematocrit 50; prerenal azotaemia: BUN 46, creatinine 1.8) with normal bicarbonate (no significant acidosis).
 b. Investigations to confirm: serum osmolality (measured or calculated = 2 Na + glucose/18 + BUN/2.8; above 320 mOsm/kg); serum sodium and potassium; blood/urine ketones (absent or mild); arterial blood gases (pH above 7.30, bicarbonate above 18 mmol/L); renal function; HbA1c; search for precipitating factors - CBC, blood and urine cultures, chest X-ray, ECG and cardiac enzymes, CT brain if focal signs.
 c. Line of treatment: IV fluid replacement is the priority - 0.9% saline 1-1.5 L in the first hour, then guided by sodium and osmolality (0.45% saline if corrected sodium is high), replacing the deficit gradually over 24-48 h; low-dose IV insulin (about 0.05-0.1 unit/kg/h) started after fluids have begun to lower glucose, aiming at a slow fall; add 5% dextrose when glucose falls to about 300 mg/dl; potassium replacement; prophylactic low-molecular-weight heparin (thrombosis risk); treat the precipitating cause (infection); monitor glucose, electrolytes, osmolality, urine output and neurological status; later long-term diabetes management (often oral agents or insulin).</t>
         </is>
       </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="C224" t="inlineStr">
@@ -11700,38 +11585,33 @@
           <t>A 22 y. old student presented with abdominal pain, repeated vomiting and marked weakness. Over the last few weeks she noticed polydispia and polyuria. Two days ago she complained of fever, bilateral loin pain and dysuria. O/E, she was dehydrated, tachypneic and feverish. Random blood sugar was 450 mgldl. Abdominal examination revealed tender both loins. a. What is your probable diagnosis? b. What would you investigate such case? c. What is your suggested treatment?</t>
         </is>
       </c>
-      <c r="R224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T224" t="inlineStr">
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>External, Blue book</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
         <is>
           <t>a. Probable diagnosis: diabetic ketoacidosis in a newly presenting (type 1) diabetic, precipitated by acute bilateral pyelonephritis (fever, bilateral loin pain and tenderness, dysuria), with dehydration and tachypnoea (Kussmaul breathing); abdominal pain and vomiting are features of DKA.
 b. Investigations: blood glucose; blood and urine ketones; arterial blood gases (low pH and bicarbonate, raised anion gap); serum sodium, potassium, urea and creatinine; CBC; urine analysis (pus cells, bacteria, glucose, ketones) and urine culture and sensitivity; blood culture; abdominal/renal ultrasound (to exclude obstruction or renal abscess); serum amylase/lipase to exclude pancreatitis; HbA1c.
 c. Treatment: IV fluids (normal saline) for rehydration; IV regular insulin infusion 0.1 unit/kg/h with potassium replacement according to serum K; dextrose when glucose falls to about 250 mg/dl while continuing insulin until ketosis resolves; bicarbonate only if pH below 6.9; IV antibiotics for pyelonephritis (e.g. ceftriaxone or a fluoroquinolone, adjusted to culture); antipyretics and antiemetics; close monitoring of glucose, electrolytes and pH; then subcutaneous basal-bolus insulin with diabetes education.</t>
         </is>
       </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>External, Blue book</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="C225" t="inlineStr">
@@ -12159,16 +12039,6 @@
           <t>According to IDF criteria for diagnosis of metabolic syndrome strike the odd one out- Triglycerymia &lt; 150 mg/dl</t>
         </is>
       </c>
-      <c r="R232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T232" t="inlineStr">
-        <is>
-          <t>A triglyceride level below 150 mg/dL is the odd one out under the stated metabolic syndrome criteria.</t>
-        </is>
-      </c>
       <c r="V232" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -12197,6 +12067,11 @@
           <t>Department, Endocrinology 2026, Metabolic Syndrome</t>
         </is>
       </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>A triglyceride level below 150 mg/dL is the odd one out under the stated metabolic syndrome criteria.</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="C233" t="inlineStr">
@@ -12264,16 +12139,6 @@
           <t>Which of the following conditions not associated with metabolic syndrome Polycystic kidney disease</t>
         </is>
       </c>
-      <c r="R234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T234" t="inlineStr">
-        <is>
-          <t>Polycystic kidney disease is not associated with metabolic syndrome.</t>
-        </is>
-      </c>
       <c r="V234" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -12302,6 +12167,11 @@
           <t>Department, Endocrinology 2026, Metabolic Syndrome</t>
         </is>
       </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>Polycystic kidney disease is not associated with metabolic syndrome.</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="C235" t="inlineStr">
@@ -21156,34 +21026,29 @@
           <t>Grave's disease '1ry thyrotoxicosis' (Define, clinical picture, laboratory investigations, treatment)</t>
         </is>
       </c>
-      <c r="R401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T401" t="inlineStr">
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC401" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF401" t="inlineStr">
         <is>
           <t>Graves disease is autoimmune primary hyperthyroidism caused by TSH-receptor-stimulating antibodies. Symptoms include heat intolerance, sweating, weight loss despite appetite, palpitations, tremor, anxiety, frequent stools and menstrual disturbance. Signs include diffuse goiter with bruit, tachycardia or atrial fibrillation, warm moist skin, fine tremor, lid retraction/stare and, in Graves disease, ophthalmopathy or pretibial dermopathy. TSH is suppressed with raised free T4 and/or T3; TSH-receptor antibodies support the diagnosis. If needed, uptake is diffusely increased; ultrasound shows diffuse enlargement and hypervascularity. Relieve adrenergic symptoms with a beta blocker; control hormone synthesis with methimazole (PTU is preferred in the first trimester of pregnancy). Definitive options are radioactive iodine or thyroidectomy, selected for the patient and disease; monitor thyroid function and treat resulting hypothyroidism.</t>
-        </is>
-      </c>
-      <c r="V401" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W401" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X401" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC401" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21193,34 +21058,29 @@
           <t>Thyrotoxicosis (causes, symptoms, specific clinical signs, Diagnosis &amp; treatment)</t>
         </is>
       </c>
-      <c r="R402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T402" t="inlineStr">
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC402" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF402" t="inlineStr">
         <is>
           <t>Thyrotoxicosis is excess circulating thyroid hormone. Causes include Graves disease, toxic multinodular goiter, toxic adenoma, thyroiditis (subacute, painless or postpartum), excess iodine/amiodarone, exogenous thyroid hormone, hCG-mediated disease, a TSH-secreting pituitary tumor, struma ovarii and functioning metastases. Symptoms: heat intolerance, sweating, weight loss, palpitations, tremor, anxiety, proximal weakness and increased bowel frequency. Signs: tachycardia/atrial fibrillation, warm moist skin, fine tremor, hyperreflexia and goiter; Graves may add eye signs and pretibial dermopathy. Confirm with suppressed TSH and raised free T4 and/or T3. Use TSH-receptor antibodies for Graves; uptake/scintigraphy distinguishes diffuse Graves uptake, focal toxic nodules and low-uptake thyroiditis or exogenous hormone. Treat the cause: beta blocker for symptoms; antithyroid drugs for hormone synthesis; radioactive iodine or surgery for Graves/autonomous nodules when appropriate; thyroiditis is generally treated symptomatically, not with thionamides.</t>
-        </is>
-      </c>
-      <c r="V402" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W402" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X402" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC402" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21230,34 +21090,29 @@
           <t>Define (Subclinical hypothyroidism)</t>
         </is>
       </c>
-      <c r="R403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T403" t="inlineStr">
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W403" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X403" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC403" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF403" t="inlineStr">
         <is>
           <t>Subclinical hypothyroidism is a raised serum TSH with free T4 within the reference range (usually with no or mild symptoms). It may be transient or reflect early autoimmune thyroiditis, prior thyroid treatment, iodine imbalance or a drug effect. Confirm with repeat TSH/free T4 and assess thyroid peroxidase antibodies and symptoms. Consider levothyroxine when TSH is persistently at least 10 mIU/L, or at lower elevations in selected symptomatic patients, pregnancy/planning pregnancy, positive TPO antibodies, goiter or relevant cardiovascular risk. Otherwise monitor TSH and free T4 periodically. Recheck TSH about 6–8 weeks after starting or changing levothyroxine.</t>
-        </is>
-      </c>
-      <c r="V403" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W403" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X403" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC403" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21267,34 +21122,29 @@
           <t>Subacute thyroiditis (De Quervan thyroiditis): C/P, investigations &amp; ttt</t>
         </is>
       </c>
-      <c r="R404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T404" t="inlineStr">
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W404" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X404" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC404" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF404" t="inlineStr">
         <is>
           <t>Subacute (De Quervain) thyroiditis is a usually post-viral, painful inflammatory thyroiditis. It causes fever, malaise and a tender enlarged thyroid with pain that may radiate to the jaw or ear; a transient thyrotoxic phase may be followed by temporary hypothyroidism and then recovery. Early tests show suppressed TSH and raised free T4/T3; ESR/CRP are elevated and radioactive iodine uptake is low. Treat pain/inflammation with an NSAID; use corticosteroids for severe or persistent pain. A beta blocker can control thyrotoxic symptoms. Antithyroid drugs are not useful because hormone excess is from leakage, not increased synthesis. Give temporary levothyroxine if the hypothyroid phase is symptomatic or prolonged, with follow-up thyroid function tests.</t>
-        </is>
-      </c>
-      <c r="V404" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W404" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X404" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC404" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21304,34 +21154,29 @@
           <t>Compare between Graves' disease &amp; toxic multinodular goiter [symptoms, signs, laboratory and radiological diagnosis]</t>
         </is>
       </c>
-      <c r="R405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T405" t="inlineStr">
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X405" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC405" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF405" t="inlineStr">
         <is>
           <t>Graves disease is autoimmune and commonly affects younger adults; toxic multinodular goiter is more common in older people and often follows longstanding nodular goiter. Graves produces a diffuse, smooth goiter, sometimes with bruit, ophthalmopathy and pretibial dermopathy; toxic multinodular goiter has an irregular nodular gland and no characteristic Graves eye/skin disease. Both suppress TSH and raise free T4 and/or T3. TSH-receptor antibodies are usually positive in Graves and negative in toxic multinodular goiter. Radioiodine uptake is diffusely increased in Graves and patchy/heterogeneous with autonomous nodules in toxic multinodular goiter; ultrasound shows diffuse hypervascularity versus multiple nodules. Treatment options include antithyroid drugs, radioactive iodine or surgery, individualized to cause, age, comorbidity, goiter size and patient preference.</t>
-        </is>
-      </c>
-      <c r="V405" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W405" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X405" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC405" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21341,34 +21186,29 @@
           <t>Cancer thyroid: Discuss risk factor for from the history, examination &amp; investigation</t>
         </is>
       </c>
-      <c r="R406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T406" t="inlineStr">
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W406" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X406" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC406" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF406" t="inlineStr">
         <is>
           <t>Thyroid cancer risk clues include childhood head/neck irradiation, a first-degree relative with thyroid cancer, familial medullary cancer or MEN2, and relevant inherited syndromes. Concerning history/examination includes a rapidly enlarging, hard or fixed nodule, hoarseness, dysphagia, compressive symptoms, cervical lymphadenopathy or vocal-cord palsy. Evaluate with TSH and high-quality thyroid/neck ultrasound, including cervical nodes; perform ultrasound-guided fine-needle aspiration when sonographic pattern and nodule size meet criteria. If TSH is low, radionuclide scanning identifies a functioning nodule, which is rarely malignant. Cytology guides surveillance, repeat sampling or surgery. For suspected medullary cancer, measure calcitonin and evaluate for RET/MEN2 as indicated.</t>
-        </is>
-      </c>
-      <c r="V406" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W406" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X406" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC406" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21378,34 +21218,29 @@
           <t>Solitary thyroid nodule: the approaches to diagnosis</t>
         </is>
       </c>
-      <c r="R407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T407" t="inlineStr">
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC407" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF407" t="inlineStr">
         <is>
           <t>For a solitary thyroid nodule, take a history of growth, radiation exposure, family history, hoarseness and compressive symptoms; examine the thyroid, cervical nodes and voice. Measure TSH and perform thyroid/neck ultrasound to characterize the nodule and lymph nodes. If TSH is suppressed, obtain radionuclide scintigraphy: a hyperfunctioning nodule rarely needs cytology, while nonfunctioning nodules are assessed by ultrasound risk and size. Perform ultrasound-guided FNA when indicated and manage according to cytology (Bethesda): observe benign nodules with appropriate follow-up, repeat sampling for nondiagnostic/indeterminate results, and refer suspicious or malignant cytology for surgery. Consider surgery for compression, growth, suspicious cytology or patient-specific reasons.</t>
-        </is>
-      </c>
-      <c r="V407" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W407" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X407" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC407" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21415,34 +21250,29 @@
           <t>hypothyroidism Discuss Causes, Clinical types, Diagnosis and management Cases questions</t>
         </is>
       </c>
-      <c r="R408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T408" t="inlineStr">
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC408" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF408" t="inlineStr">
         <is>
           <t>Causes: primary thyroid failure (Hashimoto thyroiditis, iodine deficiency or excess, thyroidectomy/radioiodine, congenital dysgenesis or dyshormonogenesis, and drugs such as lithium or amiodarone) and central hypothyroidism from pituitary/hypothalamic disease. Types include overt primary, subclinical, central and congenital hypothyroidism. Features include fatigue, cold intolerance, weight gain, constipation, dry coarse skin/hair, hoarse voice, bradycardia, delayed relaxation of reflexes, menstrual disturbance and nonpitting myxedema. In primary disease TSH is high and free T4 low (subclinical: TSH high, free T4 normal); in central disease free T4 is low with an inappropriately low/normal TSH. Check TPO antibodies when autoimmune thyroiditis is suspected and evaluate pituitary/adrenal function in central disease. Treat with oral levothyroxine, individualized by age, weight and cardiac status; take consistently and separate from iron/calcium. Recheck TSH in about 6–8 weeks after a dose change and adjust; follow free T4 rather than TSH in central hypothyroidism. Treat adrenal insufficiency before starting thyroid hormone when suspected.</t>
-        </is>
-      </c>
-      <c r="V408" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W408" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X408" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC408" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21456,34 +21286,29 @@
 D) Mention lines of treatment?</t>
         </is>
       </c>
-      <c r="R409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T409" t="inlineStr">
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC409" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF409" t="inlineStr">
         <is>
           <t>Most likely diagnosis is Graves hyperthyroidism, supported by weight loss, palpitations, anxiety, tremor, staring appearance and diffuse neck swelling. Look for heat intolerance, sweating, increased appetite, frequent stools, diffuse goiter/bruit, lid retraction or lag, proptosis, fine tremor, warm moist skin and hyperreflexia. Measure TSH, free T4 and T3; test TSH-receptor antibodies. Thyroid uptake is diffusely increased in Graves; ultrasound can show diffuse enlargement/hypervascularity. Check ECG for tachyarrhythmia. Relieve symptoms with a beta blocker and treat hormone synthesis with methimazole (PTU in the first trimester of pregnancy); discuss radioactive iodine or thyroidectomy when appropriate, with follow-up thyroid testing.</t>
-        </is>
-      </c>
-      <c r="V409" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W409" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X409" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC409" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21499,34 +21324,29 @@
 F) What can you find in the obstetric and gynecological history in this patient g. Give 3 other signs in the hands h. Do you think that surgery may have a role in the treatment</t>
         </is>
       </c>
-      <c r="R410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T410" t="inlineStr">
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X410" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC410" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF410" t="inlineStr">
         <is>
           <t>The provisional diagnosis is primary hypothyroidism, likely autoimmune thyroiditis, based on cold intolerance, weight gain, lethargy, bradycardia, puffy face and a thick hoarse voice with goiter/compressive symptoms. Bradycardia causes include hypothyroidism, beta blockers and other rate-limiting drugs, sinus-node disease/heart block, ischemia and high vagal tone. Puffy eyelids may occur with hypothyroidism/myxedema, renal disease, nephrotic syndrome, heart failure or allergy. Confirm with high TSH and low free T4; check TPO antibodies, CBC, lipids and thyroid ultrasound for the neck mass/compression. Anemia may be normocytic, iron-deficiency (including from menorrhagia) or macrocytic from B12/folate deficiency. Ask about menorrhagia, irregular cycles, anovulation, infertility and recurrent pregnancy loss. Hand signs include cool dry skin, delayed relaxation of tendon reflexes, carpal tunnel syndrome, and puffy/nonpitting fingers. Thyroidectomy is considered for significant compressive symptoms, a large goiter, suspicious nodule/cancer, or another structural indication; it is not routine treatment for uncomplicated hypothyroidism.</t>
-        </is>
-      </c>
-      <c r="V410" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W410" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X410" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC410" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21542,34 +21362,29 @@
 F) What are expected in the laboratory and radiological investigations of this patient g. Give 2 different drugs (of different classes), with their dosage, for the treatment</t>
         </is>
       </c>
-      <c r="R411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T411" t="inlineStr">
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X411" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC411" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF411" t="inlineStr">
         <is>
           <t>The likely diagnosis is Graves hyperthyroidism, given weight loss, dyspnea, palpitations, anxiety/insomnia and a family history suggesting autoimmune disease. Other causes include toxic multinodular goiter, toxic adenoma, thyroiditis, iodine/amiodarone exposure and exogenous thyroid hormone. Appetite is often increased despite weight loss; menstrual flow may become scant or irregular, with oligomenorrhea/amenorrhea. The most frequent eye sign is upper-lid retraction/stare; assess lid lag, proptosis, conjunctival irritation and restricted eye movements. Hand signs include fine tremor, warm moist palms, palmar erythema, onycholysis and, rarely, thyroid acropachy. Investigations: suppressed TSH, raised free T4 and/or T3, TSH-receptor antibodies; diffuse increased uptake supports Graves, and ultrasound assesses goiter/nodules. ECG is appropriate for palpitations. A beta blocker such as propranolol 20–40 mg every 6 hours controls adrenergic symptoms; methimazole is commonly started at about 10–30 mg/day according to biochemical severity (use PTU in the first trimester of pregnancy). Reassess thyroid function and adjust therapy; discuss definitive treatment if indicated.</t>
-        </is>
-      </c>
-      <c r="V411" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W411" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X411" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC411" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -21584,34 +21399,29 @@
 E) Is this patient need psychiatric consultation and Why?</t>
         </is>
       </c>
-      <c r="R412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T412" t="inlineStr">
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X412" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC412" t="inlineStr">
+        <is>
+          <t>External, Dr Moneer</t>
+        </is>
+      </c>
+      <c r="AF412" t="inlineStr">
         <is>
           <t>The leading possibility is early or mild thyrotoxicosis (including subclinical hyperthyroidism or T3-predominant disease); the absence of a palpable goiter does not exclude it. Repeat TSH and measure free T4 and total/free T3, because TSH is only low-normal; review biotin, thyroid hormone and iodine/amiodarone exposure. If biochemical thyrotoxicosis is confirmed, assess TSH-receptor antibodies and use uptake/scintigraphy or ultrasound according to the suspected cause; obtain an ECG for palpitations. Differential diagnoses include anxiety/panic disorder, stimulant use and pheochromocytoma when clinically suggested. Do not attribute symptoms to a psychiatric disorder before thyroid and relevant medical causes are evaluated. If thyroid testing is normal and symptoms persist, assess for anxiety/depression and arrange psychiatric consultation when indicated.</t>
-        </is>
-      </c>
-      <c r="V412" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W412" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X412" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC412" t="inlineStr">
-        <is>
-          <t>External, Dr Moneer</t>
         </is>
       </c>
     </row>
@@ -38783,16 +38593,6 @@
           <t>Indications of insulin.</t>
         </is>
       </c>
-      <c r="R729" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T729" t="inlineStr">
-        <is>
-          <t>Insulin is indicated for all patients with type 1 diabetes; for diabetic ketoacidosis or hyperosmolar hyperglycemic state; for marked symptomatic hyperglycemia or catabolism; when glycemic targets are not reached with non-insulin therapy; and in pregnancy when needed for safe glycemic control.</t>
-        </is>
-      </c>
       <c r="V729" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -38816,6 +38616,11 @@
           <t>Exams, Final 2023, Final 2022</t>
         </is>
       </c>
+      <c r="AF729" t="inlineStr">
+        <is>
+          <t>Insulin is indicated for all patients with type 1 diabetes; for diabetic ketoacidosis or hyperosmolar hyperglycemic state; for marked symptomatic hyperglycemia or catabolism; when glycemic targets are not reached with non-insulin therapy; and in pregnancy when needed for safe glycemic control.</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="C730" t="inlineStr">
@@ -38823,16 +38628,6 @@
           <t>Complications of hyperparathyroidism.</t>
         </is>
       </c>
-      <c r="R730" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T730" t="inlineStr">
-        <is>
-          <t>Complications include renal stones and nephrocalcinosis; bone resorption, bone pain, osteitis fibrosa cystica, and fractures; gastrointestinal symptoms such as constipation, nausea, peptic ulcer disease, or pancreatitis; neuropsychiatric changes; and cardiovascular effects such as hypertension and shortened QT interval.</t>
-        </is>
-      </c>
       <c r="V730" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -38856,6 +38651,11 @@
           <t>Exams, Final 2023</t>
         </is>
       </c>
+      <c r="AF730" t="inlineStr">
+        <is>
+          <t>Complications include renal stones and nephrocalcinosis; bone resorption, bone pain, osteitis fibrosa cystica, and fractures; gastrointestinal symptoms such as constipation, nausea, peptic ulcer disease, or pancreatitis; neuropsychiatric changes; and cardiovascular effects such as hypertension and shortened QT interval.</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="C731" t="inlineStr">
@@ -38863,16 +38663,6 @@
           <t>Compare between 1ry &amp; 2ry hypoadrenalism ( causes, clinical picture, investigations &amp; treatment 2.5 marks ).</t>
         </is>
       </c>
-      <c r="R731" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T731" t="inlineStr">
-        <is>
-          <t>Primary adrenal insufficiency results from adrenal cortical destruction, most often autoimmune, but also from tuberculosis, hemorrhage, infection, metastases, or genetic disease. Cortisol, aldosterone, and adrenal androgens may be deficient. Patients may have fatigue, weight loss, hypotension, salt craving, hyperpigmentation, hyponatremia, and hyperkalemia. Tests show low cortisol, high ACTH, an inadequate cortisol response to cosyntropin, high renin, and low aldosterone. Treat with glucocorticoid replacement plus fludrocortisone, education about stress dosing, and treatment of the cause. Secondary adrenal insufficiency results from pituitary or hypothalamic disease, surgery, irradiation, or prolonged glucocorticoid suppression. ACTH and cortisol are low or inappropriately normal; aldosterone is usually preserved. Hyperpigmentation and hyperkalemia are generally absent, and other pituitary deficits may coexist. Assess ACTH and other pituitary hormones, perform cosyntropin testing as appropriate, and evaluate the pituitary when indicated. Treat with glucocorticoid replacement and address the pituitary cause; fludrocortisone is generally unnecessary.</t>
-        </is>
-      </c>
       <c r="V731" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -38896,6 +38686,11 @@
           <t>Exams, Final 2023</t>
         </is>
       </c>
+      <c r="AF731" t="inlineStr">
+        <is>
+          <t>Primary adrenal insufficiency results from adrenal cortical destruction, most often autoimmune, but also from tuberculosis, hemorrhage, infection, metastases, or genetic disease. Cortisol, aldosterone, and adrenal androgens may be deficient. Patients may have fatigue, weight loss, hypotension, salt craving, hyperpigmentation, hyponatremia, and hyperkalemia. Tests show low cortisol, high ACTH, an inadequate cortisol response to cosyntropin, high renin, and low aldosterone. Treat with glucocorticoid replacement plus fludrocortisone, education about stress dosing, and treatment of the cause. Secondary adrenal insufficiency results from pituitary or hypothalamic disease, surgery, irradiation, or prolonged glucocorticoid suppression. ACTH and cortisol are low or inappropriately normal; aldosterone is usually preserved. Hyperpigmentation and hyperkalemia are generally absent, and other pituitary deficits may coexist. Assess ACTH and other pituitary hormones, perform cosyntropin testing as appropriate, and evaluate the pituitary when indicated. Treat with glucocorticoid replacement and address the pituitary cause; fludrocortisone is generally unnecessary.</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="C732" t="inlineStr">
@@ -38903,16 +38698,6 @@
           <t>Enumerate risk factors of diabetic nephropathy &amp; how to screen &amp; treat.</t>
         </is>
       </c>
-      <c r="R732" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T732" t="inlineStr">
-        <is>
-          <t>Risk factors include long diabetes duration, poor glycemic control, hypertension, albuminuria, smoking, dyslipidemia, obesity, and family or genetic susceptibility. Screen with a spot urine albumin-to-creatinine ratio and serum creatinine with estimated GFR: at diagnosis and annually in type 2 diabetes, and beginning five years after diagnosis and annually in type 1 diabetes. Confirm persistent albuminuria with repeat testing. Treatment includes improved glycemic and blood-pressure control, an ACE inhibitor or ARB when hypertension and albuminuria are present, an SGLT2 inhibitor for eligible patients with type 2 diabetes and CKD, lipid management, smoking cessation, and nephrology referral for advanced or progressive disease.</t>
-        </is>
-      </c>
       <c r="V732" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -38936,6 +38721,11 @@
           <t>Exams, Final 2023</t>
         </is>
       </c>
+      <c r="AF732" t="inlineStr">
+        <is>
+          <t>Risk factors include long diabetes duration, poor glycemic control, hypertension, albuminuria, smoking, dyslipidemia, obesity, and family or genetic susceptibility. Screen with a spot urine albumin-to-creatinine ratio and serum creatinine with estimated GFR: at diagnosis and annually in type 2 diabetes, and beginning five years after diagnosis and annually in type 1 diabetes. Confirm persistent albuminuria with repeat testing. Treatment includes improved glycemic and blood-pressure control, an ACE inhibitor or ARB when hypertension and albuminuria are present, an SGLT2 inhibitor for eligible patients with type 2 diabetes and CKD, lipid management, smoking cessation, and nephrology referral for advanced or progressive disease.</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="C733" t="inlineStr">
@@ -38943,16 +38733,6 @@
           <t>Define precocious puberty, subclinical hypothyroidism &amp; metabolic syndrome.</t>
         </is>
       </c>
-      <c r="R733" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T733" t="inlineStr">
-        <is>
-          <t>Precocious puberty is the appearance of secondary sexual characteristics before age 8 years in girls or 9 years in boys. Subclinical hypothyroidism is an elevated serum TSH with a normal free T4 concentration. Metabolic syndrome is a cluster of cardiometabolic risk factors, commonly diagnosed when at least three are present: central obesity, elevated triglycerides, low HDL cholesterol, elevated blood pressure, and elevated fasting glucose.</t>
-        </is>
-      </c>
       <c r="V733" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -38976,6 +38756,11 @@
           <t>Exams, Final 2023</t>
         </is>
       </c>
+      <c r="AF733" t="inlineStr">
+        <is>
+          <t>Precocious puberty is the appearance of secondary sexual characteristics before age 8 years in girls or 9 years in boys. Subclinical hypothyroidism is an elevated serum TSH with a normal free T4 concentration. Metabolic syndrome is a cluster of cardiometabolic risk factors, commonly diagnosed when at least three are present: central obesity, elevated triglycerides, low HDL cholesterol, elevated blood pressure, and elevated fasting glucose.</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="C734" t="inlineStr">
@@ -38983,16 +38768,6 @@
           <t>Mention one clinical benefit of SGLT inhibitors, carbimazole, GLP-1 analogues &amp; pioglitazone.</t>
         </is>
       </c>
-      <c r="R734" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T734" t="inlineStr">
-        <is>
-          <t>SGLT2 inhibitors reduce heart-failure hospitalization and slow progression of diabetic kidney disease in appropriate patients. Carbimazole controls hyperthyroidism by inhibiting thyroid hormone synthesis. GLP-1 receptor agonists improve glycemic control and commonly promote weight loss, with cardiovascular benefit for selected agents. Pioglitazone improves insulin sensitivity and lowers blood glucose in type 2 diabetes.</t>
-        </is>
-      </c>
       <c r="V734" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39016,6 +38791,11 @@
           <t>Exams, Final 2023</t>
         </is>
       </c>
+      <c r="AF734" t="inlineStr">
+        <is>
+          <t>SGLT2 inhibitors reduce heart-failure hospitalization and slow progression of diabetic kidney disease in appropriate patients. Carbimazole controls hyperthyroidism by inhibiting thyroid hormone synthesis. GLP-1 receptor agonists improve glycemic control and commonly promote weight loss, with cardiovascular benefit for selected agents. Pioglitazone improves insulin sensitivity and lowers blood glucose in type 2 diabetes.</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="C735" t="inlineStr">
@@ -39023,16 +38803,6 @@
           <t>Enumerate manifestations of congenital hypothyroidism.</t>
         </is>
       </c>
-      <c r="R735" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T735" t="inlineStr">
-        <is>
-          <t>Manifestations include prolonged neonatal jaundice, poor feeding, lethargy, hypotonia, constipation, a hoarse cry, macroglossia, a large or protruding tongue, large fontanelles, umbilical hernia, dry or cool skin, delayed growth, and later developmental delay if untreated.</t>
-        </is>
-      </c>
       <c r="V735" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39056,6 +38826,11 @@
           <t>Exams, Final 2023</t>
         </is>
       </c>
+      <c r="AF735" t="inlineStr">
+        <is>
+          <t>Manifestations include prolonged neonatal jaundice, poor feeding, lethargy, hypotonia, constipation, a hoarse cry, macroglossia, a large or protruding tongue, large fontanelles, umbilical hernia, dry or cool skin, delayed growth, and later developmental delay if untreated.</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="C736" t="inlineStr">
@@ -39063,16 +38838,6 @@
           <t>Enumerate types &amp; clinical manifestations of malignant thyroid.</t>
         </is>
       </c>
-      <c r="R736" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T736" t="inlineStr">
-        <is>
-          <t>The main types are papillary, follicular, medullary, and anaplastic thyroid carcinoma. Presentation may include a painless thyroid nodule or goiter, cervical lymphadenopathy, hoarseness, dysphagia, dyspnea, or local invasion. Papillary carcinoma commonly spreads to cervical nodes; follicular carcinoma more often spreads hematogenously to bone or lung; medullary carcinoma may be associated with MEN2 and can cause diarrhea or flushing; anaplastic carcinoma typically causes a rapidly enlarging neck mass with compressive symptoms and a poor prognosis.</t>
-        </is>
-      </c>
       <c r="V736" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39096,6 +38861,11 @@
           <t>Exams, Final 2023</t>
         </is>
       </c>
+      <c r="AF736" t="inlineStr">
+        <is>
+          <t>The main types are papillary, follicular, medullary, and anaplastic thyroid carcinoma. Presentation may include a painless thyroid nodule or goiter, cervical lymphadenopathy, hoarseness, dysphagia, dyspnea, or local invasion. Papillary carcinoma commonly spreads to cervical nodes; follicular carcinoma more often spreads hematogenously to bone or lung; medullary carcinoma may be associated with MEN2 and can cause diarrhea or flushing; anaplastic carcinoma typically causes a rapidly enlarging neck mass with compressive symptoms and a poor prognosis.</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="C737" t="inlineStr">
@@ -39103,16 +38873,6 @@
           <t>Incretin based therapy in TTT of DM</t>
         </is>
       </c>
-      <c r="R737" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T737" t="inlineStr">
-        <is>
-          <t>Incretin-based therapy includes GLP-1 receptor agonists (for example, liraglutide, semaglutide, or dulaglutide) and DPP-4 inhibitors (for example, sitagliptin or linagliptin). GLP-1 agonists enhance glucose-dependent insulin secretion, suppress glucagon, slow gastric emptying, and reduce appetite and weight. DPP-4 inhibitors prolong endogenous GLP-1 and GIP activity, increasing glucose-dependent insulin secretion and reducing glucagon, with generally weight-neutral effects. Hypoglycemia is uncommon unless these drugs are combined with insulin or a sulfonylurea. GLP-1 agents commonly cause nausea and other gastrointestinal symptoms; pancreatitis and gallbladder disease are uncommon concerns. Select an agent according to glycemic needs, cardiovascular and kidney disease, weight goals, contraindications, and patient preference.</t>
-        </is>
-      </c>
       <c r="V737" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39136,6 +38896,11 @@
           <t>Exams, Final 2022</t>
         </is>
       </c>
+      <c r="AF737" t="inlineStr">
+        <is>
+          <t>Incretin-based therapy includes GLP-1 receptor agonists (for example, liraglutide, semaglutide, or dulaglutide) and DPP-4 inhibitors (for example, sitagliptin or linagliptin). GLP-1 agonists enhance glucose-dependent insulin secretion, suppress glucagon, slow gastric emptying, and reduce appetite and weight. DPP-4 inhibitors prolong endogenous GLP-1 and GIP activity, increasing glucose-dependent insulin secretion and reducing glucagon, with generally weight-neutral effects. Hypoglycemia is uncommon unless these drugs are combined with insulin or a sulfonylurea. GLP-1 agents commonly cause nausea and other gastrointestinal symptoms; pancreatitis and gallbladder disease are uncommon concerns. Select an agent according to glycemic needs, cardiovascular and kidney disease, weight goals, contraindications, and patient preference.</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="C738" t="inlineStr">
@@ -39143,16 +38908,6 @@
           <t>Clinical pictutre of Addison disease.</t>
         </is>
       </c>
-      <c r="R738" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T738" t="inlineStr">
-        <is>
-          <t>Primary adrenal insufficiency causes chronic fatigue, weakness, weight loss, anorexia, nausea, vomiting, abdominal pain, salt craving, and postural dizziness. Examination may show hypotension or volume depletion, diffuse hyperpigmentation of skin and mucosa, and sometimes vitiligo. Acute adrenal crisis can cause severe hypotension or shock, vomiting, abdominal pain, fever, confusion, and hypoglycemia. Typical laboratory findings include hyponatremia, hyperkalemia, low glucose, and sometimes mild hypercalcemia; primary disease has low cortisol with high ACTH and often high plasma renin with low aldosterone.</t>
-        </is>
-      </c>
       <c r="V738" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39176,6 +38931,11 @@
           <t>Exams, Final 2022</t>
         </is>
       </c>
+      <c r="AF738" t="inlineStr">
+        <is>
+          <t>Primary adrenal insufficiency causes chronic fatigue, weakness, weight loss, anorexia, nausea, vomiting, abdominal pain, salt craving, and postural dizziness. Examination may show hypotension or volume depletion, diffuse hyperpigmentation of skin and mucosa, and sometimes vitiligo. Acute adrenal crisis can cause severe hypotension or shock, vomiting, abdominal pain, fever, confusion, and hypoglycemia. Typical laboratory findings include hyponatremia, hyperkalemia, low glucose, and sometimes mild hypercalcemia; primary disease has low cortisol with high ACTH and often high plasma renin with low aldosterone.</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="C739" t="inlineStr">
@@ -39183,16 +38943,6 @@
           <t>Case of hypothyroidism and approach to diagnosis.</t>
         </is>
       </c>
-      <c r="R739" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T739" t="inlineStr">
-        <is>
-          <t>Suspect hypothyroidism with fatigue, cold intolerance, weight gain, constipation, dry skin, hoarse voice, bradycardia, delayed relaxation of reflexes, menstrual disturbance, or goiter, and assess relevant history such as thyroid surgery, radioiodine, neck irradiation, autoimmune disease, and lithium or amiodarone use. Screen with serum TSH in a stable patient with an intact pituitary; an elevated TSH prompts free T4 measurement. Confirm primary overt hypothyroidism with high TSH and low free T4; high TSH with normal free T4 indicates subclinical disease. Low free T4 with low or inappropriately normal TSH suggests central hypothyroidism and requires evaluation of other pituitary axes. Identify the cause with thyroid peroxidase antibodies, medication and treatment history, examination, and, when central disease is suspected, pituitary hormone testing and pituitary MRI. Assess for adrenal insufficiency before starting levothyroxine when pituitary disease is possible.</t>
-        </is>
-      </c>
       <c r="V739" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39216,6 +38966,11 @@
           <t>Exams, Final 2022</t>
         </is>
       </c>
+      <c r="AF739" t="inlineStr">
+        <is>
+          <t>Suspect hypothyroidism with fatigue, cold intolerance, weight gain, constipation, dry skin, hoarse voice, bradycardia, delayed relaxation of reflexes, menstrual disturbance, or goiter, and assess relevant history such as thyroid surgery, radioiodine, neck irradiation, autoimmune disease, and lithium or amiodarone use. Screen with serum TSH in a stable patient with an intact pituitary; an elevated TSH prompts free T4 measurement. Confirm primary overt hypothyroidism with high TSH and low free T4; high TSH with normal free T4 indicates subclinical disease. Low free T4 with low or inappropriately normal TSH suggests central hypothyroidism and requires evaluation of other pituitary axes. Identify the cause with thyroid peroxidase antibodies, medication and treatment history, examination, and, when central disease is suspected, pituitary hormone testing and pituitary MRI. Assess for adrenal insufficiency before starting levothyroxine when pituitary disease is possible.</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="C740" t="inlineStr">
@@ -39223,16 +38978,6 @@
           <t>Drug causes Hyperprolactinemia?</t>
         </is>
       </c>
-      <c r="R740" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T740" t="inlineStr">
-        <is>
-          <t>Drugs that can raise prolactin include dopamine D2 antagonists, especially antipsychotics such as risperidone, paliperidone, amisulpride, and haloperidol; prokinetics such as metoclopramide and domperidone; some antidepressants; opioids; verapamil; methyldopa; estrogens; and, less commonly, H2 blockers such as cimetidine. Review the medication list and timing before diagnosing a prolactinoma.</t>
-        </is>
-      </c>
       <c r="V740" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39256,6 +39001,11 @@
           <t>Exams, Final 2022</t>
         </is>
       </c>
+      <c r="AF740" t="inlineStr">
+        <is>
+          <t>Drugs that can raise prolactin include dopamine D2 antagonists, especially antipsychotics such as risperidone, paliperidone, amisulpride, and haloperidol; prokinetics such as metoclopramide and domperidone; some antidepressants; opioids; verapamil; methyldopa; estrogens; and, less commonly, H2 blockers such as cimetidine. Review the medication list and timing before diagnosing a prolactinoma.</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="C741" t="inlineStr">
@@ -39263,16 +39013,6 @@
           <t>Pituitary causes hypogonadism?</t>
         </is>
       </c>
-      <c r="R741" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T741" t="inlineStr">
-        <is>
-          <t>Pituitary causes include prolactinoma or other hyperprolactinemia suppressing hypothalamic GnRH; a nonfunctioning pituitary macroadenoma compressing gonadotrophs or the stalk; hypopituitarism from pituitary tumors, apoplexy, Sheehan syndrome, trauma, surgery, radiotherapy, infiltrative disease, or hypophysitis; and congenital or genetic pituitary hormone deficiencies. The resulting low LH and FSH cause secondary hypogonadism.</t>
-        </is>
-      </c>
       <c r="V741" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39296,6 +39036,11 @@
           <t>Exams, Final 2022</t>
         </is>
       </c>
+      <c r="AF741" t="inlineStr">
+        <is>
+          <t>Pituitary causes include prolactinoma or other hyperprolactinemia suppressing hypothalamic GnRH; a nonfunctioning pituitary macroadenoma compressing gonadotrophs or the stalk; hypopituitarism from pituitary tumors, apoplexy, Sheehan syndrome, trauma, surgery, radiotherapy, infiltrative disease, or hypophysitis; and congenital or genetic pituitary hormone deficiencies. The resulting low LH and FSH cause secondary hypogonadism.</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="C742" t="inlineStr">
@@ -39308,16 +39053,6 @@
           <t>Images/21_Q11.png</t>
         </is>
       </c>
-      <c r="R742" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T742" t="inlineStr">
-        <is>
-          <t>In children, growth hormone deficiency causes reduced height velocity and proportionate short stature, delayed bone age and dentition, a relatively immature facial appearance, and increased central adiposity; intelligence is usually normal. Neonates may have hypoglycemia and boys may have micropenis. In adults, features include reduced lean mass and exercise capacity, increased visceral fat, reduced bone density, adverse lipid changes, fatigue, and impaired quality of life; these findings are nonspecific and require biochemical confirmation.</t>
-        </is>
-      </c>
       <c r="V742" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39341,6 +39076,11 @@
           <t>Exams, Final 2022</t>
         </is>
       </c>
+      <c r="AF742" t="inlineStr">
+        <is>
+          <t>In children, growth hormone deficiency causes reduced height velocity and proportionate short stature, delayed bone age and dentition, a relatively immature facial appearance, and increased central adiposity; intelligence is usually normal. Neonates may have hypoglycemia and boys may have micropenis. In adults, features include reduced lean mass and exercise capacity, increased visceral fat, reduced bone density, adverse lipid changes, fatigue, and impaired quality of life; these findings are nonspecific and require biochemical confirmation.</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="C743" t="inlineStr">
@@ -39348,16 +39088,6 @@
           <t>Enumerate functional adrenal neoplasms.</t>
         </is>
       </c>
-      <c r="R743" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T743" t="inlineStr">
-        <is>
-          <t>Functional adrenal neoplasms include cortisol-secreting cortical adenomas or carcinomas causing Cushing syndrome; aldosterone-producing adenomas causing primary aldosteronism; androgen- or estrogen-secreting cortical tumors causing virilization or feminization; and catecholamine-secreting adrenal medullary pheochromocytomas. Some cortical tumors can secrete more than one steroid class.</t>
-        </is>
-      </c>
       <c r="V743" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39381,6 +39111,11 @@
           <t>Exams, Final 2022</t>
         </is>
       </c>
+      <c r="AF743" t="inlineStr">
+        <is>
+          <t>Functional adrenal neoplasms include cortisol-secreting cortical adenomas or carcinomas causing Cushing syndrome; aldosterone-producing adenomas causing primary aldosteronism; androgen- or estrogen-secreting cortical tumors causing virilization or feminization; and catecholamine-secreting adrenal medullary pheochromocytomas. Some cortical tumors can secrete more than one steroid class.</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="C744" t="inlineStr">
@@ -39388,16 +39123,6 @@
           <t>Causes of panhypopituitarism.</t>
         </is>
       </c>
-      <c r="R744" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T744" t="inlineStr">
-        <is>
-          <t>Causes include pituitary macroadenoma or other sellar tumors; surgery or radiotherapy; pituitary apoplexy; postpartum ischemic necrosis (Sheehan syndrome); traumatic brain injury; infiltrative or inflammatory disease such as sarcoidosis, tuberculosis, hemochromatosis, or hypophysitis; metastasis or infection; and congenital or genetic defects affecting the pituitary or hypothalamus. A lesion affecting the gland or stalk can impair multiple anterior pituitary axes; posterior pituitary involvement may also cause diabetes insipidus.</t>
-        </is>
-      </c>
       <c r="V744" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39421,6 +39146,11 @@
           <t>Exams, Final 2022</t>
         </is>
       </c>
+      <c r="AF744" t="inlineStr">
+        <is>
+          <t>Causes include pituitary macroadenoma or other sellar tumors; surgery or radiotherapy; pituitary apoplexy; postpartum ischemic necrosis (Sheehan syndrome); traumatic brain injury; infiltrative or inflammatory disease such as sarcoidosis, tuberculosis, hemochromatosis, or hypophysitis; metastasis or infection; and congenital or genetic defects affecting the pituitary or hypothalamus. A lesion affecting the gland or stalk can impair multiple anterior pituitary axes; posterior pituitary involvement may also cause diabetes insipidus.</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="C745" t="inlineStr">
@@ -39428,16 +39158,6 @@
           <t>a. Compare between type 1 and type 2 diabetes mellitus regarding epidemiology, main pathophysiology, clinical and laboratory characteristics b. Explain the measures for prevention the macrovascular complications of DM</t>
         </is>
       </c>
-      <c r="R745" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T745" t="inlineStr">
-        <is>
-          <t>Type 1 diabetes usually begins in childhood or young adulthood and is caused by autoimmune beta-cell destruction, producing absolute insulin deficiency. It often presents abruptly with weight loss or ketoacidosis; islet autoantibodies are often present and C-peptide is low. Type 2 diabetes usually develops gradually, often with central obesity and other insulin-resistance features; insulin resistance is followed by beta-cell dysfunction, C-peptide is initially preserved or high, and islet autoantibodies are absent. For macrovascular prevention: stop smoking, promote regular physical activity and weight control, individualize glycemic targets, control blood pressure, and use statin therapy according to cardiovascular risk. Use antiplatelet therapy for established atherosclerotic disease and, in type 2 diabetes with ASCVD, heart failure, or kidney disease, include a cardioprotective SGLT2 inhibitor and/or GLP-1 receptor agonist when appropriate.</t>
-        </is>
-      </c>
       <c r="V745" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39461,6 +39181,11 @@
           <t>Exams, Final 2026</t>
         </is>
       </c>
+      <c r="AF745" t="inlineStr">
+        <is>
+          <t>Type 1 diabetes usually begins in childhood or young adulthood and is caused by autoimmune beta-cell destruction, producing absolute insulin deficiency. It often presents abruptly with weight loss or ketoacidosis; islet autoantibodies are often present and C-peptide is low. Type 2 diabetes usually develops gradually, often with central obesity and other insulin-resistance features; insulin resistance is followed by beta-cell dysfunction, C-peptide is initially preserved or high, and islet autoantibodies are absent. For macrovascular prevention: stop smoking, promote regular physical activity and weight control, individualize glycemic targets, control blood pressure, and use statin therapy according to cardiovascular risk. Use antiplatelet therapy for established atherosclerotic disease and, in type 2 diabetes with ASCVD, heart failure, or kidney disease, include a cardioprotective SGLT2 inhibitor and/or GLP-1 receptor agonist when appropriate.</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="C746" t="inlineStr">
@@ -39468,16 +39193,6 @@
           <t>Explain the clinical picture and treatment of adrenal crisis</t>
         </is>
       </c>
-      <c r="R746" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T746" t="inlineStr">
-        <is>
-          <t>Adrenal crisis presents with severe weakness, nausea or vomiting, abdominal pain, fever, dehydration, hypotension or shock, and sometimes confusion. Primary adrenal failure may cause hyponatremia and hyperkalemia; hypoglycemia can occur. Treat immediately: hydrocortisone 100 mg IV or IM, then 200 mg over 24 hours by infusion or 50 mg every 6 hours; rapidly give isotonic saline, add dextrose for hypoglycemia, monitor glucose and electrolytes, and treat the precipitating illness. Do not delay treatment for test results. Once stable, transition to oral glucocorticoid replacement; add fludrocortisone for primary adrenal insufficiency when stress-dose hydrocortisone has been reduced.</t>
-        </is>
-      </c>
       <c r="V746" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39501,6 +39216,11 @@
           <t>Exams, Final 2026</t>
         </is>
       </c>
+      <c r="AF746" t="inlineStr">
+        <is>
+          <t>Adrenal crisis presents with severe weakness, nausea or vomiting, abdominal pain, fever, dehydration, hypotension or shock, and sometimes confusion. Primary adrenal failure may cause hyponatremia and hyperkalemia; hypoglycemia can occur. Treat immediately: hydrocortisone 100 mg IV or IM, then 200 mg over 24 hours by infusion or 50 mg every 6 hours; rapidly give isotonic saline, add dextrose for hypoglycemia, monitor glucose and electrolytes, and treat the precipitating illness. Do not delay treatment for test results. Once stable, transition to oral glucocorticoid replacement; add fludrocortisone for primary adrenal insufficiency when stress-dose hydrocortisone has been reduced.</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="C747" t="inlineStr">
@@ -39508,16 +39228,6 @@
           <t>Summarize the a. Clinical manifestations of Carcinoid syndrome b. Clinical presentations of osteoporosis c. Clinical presentations of primary hyperparathyroidism d. Side effects of SGLT 2 inhibitors</t>
         </is>
       </c>
-      <c r="R747" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T747" t="inlineStr">
-        <is>
-          <t>Carcinoid syndrome: episodic flushing, secretory watery diarrhea, abdominal cramps, bronchospasm, and right-sided valvular disease (especially tricuspid and pulmonary valves); prolonged serotonin excess may cause niacin deficiency and pellagra. Osteoporosis: often silent until a fragility fracture; vertebral compression fractures cause acute or chronic back pain, height loss, and kyphosis, while hip and distal-radius fractures are other common presentations. Primary hyperparathyroidism: may be asymptomatic or present with renal stones/nephrocalcinosis, bone pain or fragility fractures, muscle weakness, constipation, abdominal discomfort, polyuria/polydipsia, and neurocognitive or mood symptoms. SGLT2-inhibitor adverse effects include genital mycotic infections, volume depletion and hypotension, and rare euglycemic diabetic ketoacidosis; counsel about sick-day interruption and perioperative withholding. Rare serious events include Fournier gangrene; fracture or amputation signals have been agent-specific.</t>
-        </is>
-      </c>
       <c r="V747" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39541,6 +39251,11 @@
           <t>Exams, Final 2026</t>
         </is>
       </c>
+      <c r="AF747" t="inlineStr">
+        <is>
+          <t>Carcinoid syndrome: episodic flushing, secretory watery diarrhea, abdominal cramps, bronchospasm, and right-sided valvular disease (especially tricuspid and pulmonary valves); prolonged serotonin excess may cause niacin deficiency and pellagra. Osteoporosis: often silent until a fragility fracture; vertebral compression fractures cause acute or chronic back pain, height loss, and kyphosis, while hip and distal-radius fractures are other common presentations. Primary hyperparathyroidism: may be asymptomatic or present with renal stones/nephrocalcinosis, bone pain or fragility fractures, muscle weakness, constipation, abdominal discomfort, polyuria/polydipsia, and neurocognitive or mood symptoms. SGLT2-inhibitor adverse effects include genital mycotic infections, volume depletion and hypotension, and rare euglycemic diabetic ketoacidosis; counsel about sick-day interruption and perioperative withholding. Rare serious events include Fournier gangrene; fracture or amputation signals have been agent-specific.</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="C748" t="inlineStr">
@@ -39548,16 +39263,6 @@
           <t>Enumerate a, Indications of insulin therapy b. Causes of thyrotoxicosis c, Causes of pituitary hypogonadism</t>
         </is>
       </c>
-      <c r="R748" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T748" t="inlineStr">
-        <is>
-          <t>Insulin is indicated for all type 1 diabetes; diabetic ketoacidosis or hyperosmolar crisis; severe symptomatic hyperglycemia, catabolism, or marked weight loss; type 2 diabetes inadequately controlled with non-insulin therapy or when those drugs are unsuitable; pregnancy or gestational diabetes when targets are not met with lifestyle measures; and temporary control during severe illness, surgery, or glucocorticoid-related hyperglycemia. Causes of thyrotoxicosis include Graves disease, toxic multinodular goiter, toxic adenoma, thyroiditis (subacute, painless, or postpartum), excess iodine or amiodarone, exogenous thyroid hormone, hCG-mediated disease, a TSH-secreting pituitary adenoma, struma ovarii, and functioning metastatic thyroid carcinoma. Causes of pituitary (secondary) hypogonadism include pituitary tumors or surgery/radiation, Sheehan syndrome or apoplexy, head trauma, infiltrative disease (e.g., hemochromatosis or sarcoidosis), hyperprolactinemia, congenital GnRH deficiency (including Kallmann syndrome), and functional suppression from chronic illness, malnutrition, or excessive exercise.</t>
-        </is>
-      </c>
       <c r="V748" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39581,6 +39286,11 @@
           <t>Exams, Final 2026</t>
         </is>
       </c>
+      <c r="AF748" t="inlineStr">
+        <is>
+          <t>Insulin is indicated for all type 1 diabetes; diabetic ketoacidosis or hyperosmolar crisis; severe symptomatic hyperglycemia, catabolism, or marked weight loss; type 2 diabetes inadequately controlled with non-insulin therapy or when those drugs are unsuitable; pregnancy or gestational diabetes when targets are not met with lifestyle measures; and temporary control during severe illness, surgery, or glucocorticoid-related hyperglycemia. Causes of thyrotoxicosis include Graves disease, toxic multinodular goiter, toxic adenoma, thyroiditis (subacute, painless, or postpartum), excess iodine or amiodarone, exogenous thyroid hormone, hCG-mediated disease, a TSH-secreting pituitary adenoma, struma ovarii, and functioning metastatic thyroid carcinoma. Causes of pituitary (secondary) hypogonadism include pituitary tumors or surgery/radiation, Sheehan syndrome or apoplexy, head trauma, infiltrative disease (e.g., hemochromatosis or sarcoidosis), hyperprolactinemia, congenital GnRH deficiency (including Kallmann syndrome), and functional suppression from chronic illness, malnutrition, or excessive exercise.</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="C749" t="inlineStr">
@@ -39588,16 +39298,6 @@
           <t>A.Causes Of Short child ' B.Diagnosis Of Diabetic Keto Acidosis</t>
         </is>
       </c>
-      <c r="R749" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T749" t="inlineStr">
-        <is>
-          <t>Causes of short stature include normal variants (familial short stature and constitutional delay); prenatal growth restriction/small-for-gestational-age birth; malnutrition; chronic renal, gastrointestinal, cardiac, pulmonary, hepatic, or inflammatory disease; endocrine disorders (growth-hormone deficiency, hypothyroidism, glucocorticoid excess, and poorly controlled diabetes); genetic or chromosomal conditions (e.g., Turner, Noonan, or Down syndrome); skeletal dysplasia; and psychosocial or idiopathic short stature. Diagnose diabetic ketoacidosis when diabetes/hyperglycemia (glucose at least 200 mg/dL or a prior diabetes diagnosis) is accompanied by ketosis (beta-hydroxybutyrate at least 3 mmol/L or urine ketones at least 2+) and metabolic acidosis (venous pH below 7.3 and/or bicarbonate below 18 mmol/L).</t>
-        </is>
-      </c>
       <c r="V749" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39621,6 +39321,11 @@
           <t>Exams, Final 2026</t>
         </is>
       </c>
+      <c r="AF749" t="inlineStr">
+        <is>
+          <t>Causes of short stature include normal variants (familial short stature and constitutional delay); prenatal growth restriction/small-for-gestational-age birth; malnutrition; chronic renal, gastrointestinal, cardiac, pulmonary, hepatic, or inflammatory disease; endocrine disorders (growth-hormone deficiency, hypothyroidism, glucocorticoid excess, and poorly controlled diabetes); genetic or chromosomal conditions (e.g., Turner, Noonan, or Down syndrome); skeletal dysplasia; and psychosocial or idiopathic short stature. Diagnose diabetic ketoacidosis when diabetes/hyperglycemia (glucose at least 200 mg/dL or a prior diabetes diagnosis) is accompanied by ketosis (beta-hydroxybutyrate at least 3 mmol/L or urine ketones at least 2+) and metabolic acidosis (venous pH below 7.3 and/or bicarbonate below 18 mmol/L).</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="C750" t="inlineStr">
@@ -39628,16 +39333,6 @@
           <t>a. Classifications of adrenal tumors, Management of adrenocortical carcinoma b. surgical anatomy of thyroid gland and its relationship</t>
         </is>
       </c>
-      <c r="R750" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T750" t="inlineStr">
-        <is>
-          <t>Adrenal tumors may be classified by origin as cortical (adenoma or carcinoma) or medullary (pheochromocytoma; extra-adrenal chromaffin tumors are paragangliomas), and by function as hormone-secreting or nonfunctioning. Adrenocortical carcinoma requires hormonal and staging assessment and multidisciplinary care. For localized resectable disease, perform complete en-bloc adrenalectomy with periadrenal tissue, avoiding tumor rupture; use an open oncologic approach when malignancy or invasion is strongly suspected. Consider adjuvant mitotane for high-risk disease; advanced disease may require mitotane-based systemic therapy and selected local treatment. Thyroid: two lateral lobes joined by an isthmus, lying anterior to the trachea and enclosed by pretracheal fascia; Berry ligament anchors it to the larynx/trachea. Important relations are the strap muscles anteriorly, trachea and esophagus medially/posteriorly, recurrent laryngeal nerves in the tracheoesophageal grooves, external branches of the superior laryngeal nerves near the superior thyroid pedicles, and parathyroid glands on the posterior surface. The superior thyroid arteries arise from the external carotids and the inferior thyroid arteries from the thyrocervical trunks; preserve the laryngeal nerves and parathyroids during surgery.</t>
-        </is>
-      </c>
       <c r="V750" t="inlineStr">
         <is>
           <t>QROC</t>
@@ -39661,6 +39356,11 @@
           <t>Exams, Final 2026</t>
         </is>
       </c>
+      <c r="AF750" t="inlineStr">
+        <is>
+          <t>Adrenal tumors may be classified by origin as cortical (adenoma or carcinoma) or medullary (pheochromocytoma; extra-adrenal chromaffin tumors are paragangliomas), and by function as hormone-secreting or nonfunctioning. Adrenocortical carcinoma requires hormonal and staging assessment and multidisciplinary care. For localized resectable disease, perform complete en-bloc adrenalectomy with periadrenal tissue, avoiding tumor rupture; use an open oncologic approach when malignancy or invasion is strongly suspected. Consider adjuvant mitotane for high-risk disease; advanced disease may require mitotane-based systemic therapy and selected local treatment. Thyroid: two lateral lobes joined by an isthmus, lying anterior to the trachea and enclosed by pretracheal fascia; Berry ligament anchors it to the larynx/trachea. Important relations are the strap muscles anteriorly, trachea and esophagus medially/posteriorly, recurrent laryngeal nerves in the tracheoesophageal grooves, external branches of the superior laryngeal nerves near the superior thyroid pedicles, and parathyroid glands on the posterior surface. The superior thyroid arteries arise from the external carotids and the inferior thyroid arteries from the thyrocervical trunks; preserve the laryngeal nerves and parathyroids during surgery.</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="C751" t="inlineStr">
@@ -40143,7 +39843,7 @@
       </c>
       <c r="AC758" t="inlineStr">
         <is>
-          <t>Exams, Formative 2023</t>
+          <t>Exams, Formative 2023, External, Endocrine Surgery</t>
         </is>
       </c>
     </row>
@@ -41308,12 +41008,32 @@
           <t>Images/25_Q15.png</t>
         </is>
       </c>
-      <c r="R778" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T778" t="inlineStr">
+      <c r="V778" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W778" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X778" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AA778" t="inlineStr">
+        <is>
+          <t>Pediatrics</t>
+        </is>
+      </c>
+      <c r="AC778" t="inlineStr">
+        <is>
+          <t>Professor, Dr Mogy</t>
+        </is>
+      </c>
+      <c r="AF778" t="inlineStr">
         <is>
           <t>a- Acquired hypothyroidism: curve 2
 b- Growth hormone deficiency: curve 5
@@ -41322,31 +41042,6 @@
 e- Constitutional delay in growth and puberty: curve 4</t>
         </is>
       </c>
-      <c r="V778" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W778" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X778" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AA778" t="inlineStr">
-        <is>
-          <t>Pediatrics</t>
-        </is>
-      </c>
-      <c r="AC778" t="inlineStr">
-        <is>
-          <t>Professor, Dr Mogy</t>
-        </is>
-      </c>
     </row>
     <row r="779">
       <c r="C779" t="inlineStr">
@@ -45626,34 +45321,29 @@
           <t>About the thyroid gland, one statement only Is true: AThyroid follcular tissue arises from the third pharyngeal pouch. COPYRIGHT 2011- Prof. AHMED EL-BISHRY &amp; Prof. AMR MOHSEN Page 41 URGERY The parafollicular C cells arise from the floor of the developing pharynx. The thyroglossal duct is normally patent during the first few years of life. Thyroglobulin is stored in colloid that is present inside the thyroid follicies. D. The thyrold develops as praliferatlon of epithelial cells in the floor of the developing The parafollicular cells secrete thyroid stimulating hormone. FO pharynx (the thyroglossal duct) at a point that Iis indicated by the foramen caecum depresslon at the base of the tongue. As the thyroid primordium descends, It unites ultimobran:bial body whlch arises on either side from the (fourth) pharynp Parafollicular (C-cells) are derived from the neural crest and reach the thy ultimabranchlal body. After the thyroid reaches its definltlve location In the lov connecting thyroglossal duct undergoes obliteration. The thyrold follicles secrete thyroid hormones. They are stored as thyroglobulin that is present in theses follicles. The parafollicular C cells secrete the hormone calciton. 4 Ahout snatomu of the thur. URGERY The parafollcular C cells arise from the floor of the developing pharynx. The thyroglossal duct is normally patent during the first few years of life. D. Thyroglobulin is stored in colloid that is present inside the thyroid follicles. EThe parafollicular cells secrete thyroid stimulating hormone. D. The thyrold develops as proliferatlon of epithelial cells In the floor of the developing pharynx (the thyroglossal duct) at a polnt that is indicated by the foramen caecum, a depression at the base of the tongue. As the thyroid primordium descends, it unites with the ultimobrancbial body which arises on either side from the (fourth) pharyngeal pouch. Parafolliculiar (C-cells) are derived from the neural crest and reach the thyroid via the ultimobranchial body. After the thyroid reaches its definitive locatlon in the lower neck, the connecting thyroglossal duct undergoes obliteration. The thyrold follicles secrete thyroid hormones. They are stored as thyroglobulln In a colloid that is present In theses follicles. The parafollicular C cells secrete the hormone calcitonin.</t>
         </is>
       </c>
-      <c r="R853" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T853" t="inlineStr">
+      <c r="V853" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W853" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X853" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC853" t="inlineStr">
+        <is>
+          <t>External, Endocrine Surgery</t>
+        </is>
+      </c>
+      <c r="AF853" t="inlineStr">
         <is>
           <t>Thyroglobulin is stored in the colloid inside thyroid follicles. Thyroid follicular cells arise from endoderm of the pharyngeal floor near the foramen caecum and descend to the lower neck; the thyroglossal duct normally obliterates. Parafollicular C cells derive from neural crest via the ultimobranchial body and secrete calcitonin.</t>
-        </is>
-      </c>
-      <c r="V853" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W853" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X853" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC853" t="inlineStr">
-        <is>
-          <t>External, Endocrine Surgery</t>
         </is>
       </c>
     </row>
@@ -45935,22 +45625,42 @@
     <row r="859">
       <c r="C859" t="inlineStr">
         <is>
-          <t>About the aetiology of simple goitre, all the following statements are true, except: APendred's syndrome is characterized by hypothyroidism, goitre and blindness. Pencred's syndrome is caused by deficiency of peroxidase enzyme. LC. Deficiency of lodine causes simple goltre. .Pregnancy raises the need for lodine. E.Thiocyanates in cabbages are goitrogenic.</t>
+          <t>About the aetiology of simple goitre, all the following statements are true, except:</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Pendred's syndrome is characterized by hypothyroidism, goitre and blindness.</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>Pendred's syndrome is caused by deficiency of peroxidase enzyme.</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>Deficiency of iodine causes simple goitre.</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>Pregnancy raises the need for iodine.</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>Thiocyanates in cabbages are goitrogenic.</t>
         </is>
       </c>
       <c r="R859" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T859" t="inlineStr">
-        <is>
-          <t>blind. The commonest cause of a simple gaitre, however, is deficlency of lodine. Simple goltre Is endemic in regions with low lodide content of water and food as in mountains and desert areas away from seas. Relative deficiency of lodine occurs during periods of stress. Females t during the menarche, pregnancy and lactation are susceptible to this problem.</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V859" t="inlineStr">
         <is>
-          <t>QROC</t>
+          <t>QCS</t>
         </is>
       </c>
       <c r="W859" t="inlineStr">
@@ -46255,34 +45965,29 @@
           <t>In most of cases surgery does not require a thoracotomy.</t>
         </is>
       </c>
-      <c r="R865" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T865" t="inlineStr">
+      <c r="V865" t="inlineStr">
+        <is>
+          <t>QROC</t>
+        </is>
+      </c>
+      <c r="W865" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X865" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC865" t="inlineStr">
+        <is>
+          <t>External, Endocrine Surgery</t>
+        </is>
+      </c>
+      <c r="AF865" t="inlineStr">
         <is>
           <t>In most cases, surgery for a retrosternal goitre does not require thoracotomy.</t>
-        </is>
-      </c>
-      <c r="V865" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W865" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X865" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC865" t="inlineStr">
-        <is>
-          <t>External, Endocrine Surgery</t>
         </is>
       </c>
     </row>
@@ -46393,22 +46098,47 @@
     <row r="868">
       <c r="C868" t="inlineStr">
         <is>
-          <t>Medullary carcinoma of the thyrold. Carcinoma of the parathyroid.</t>
+          <t>About papillary thyroid cancer, all the following are true, except:</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>It is the commonest thyroid cancer.</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>It usually affects teen-agers.</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>It usually spreads by lymphatics.</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>A high TSH helps its growth. It secretes calcitonin.</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>It secretes calcitonin.</t>
         </is>
       </c>
       <c r="R868" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="T868" t="inlineStr">
         <is>
-          <t>total thyroidectomy.</t>
+          <t>Papillary and follicular thyroid cancers are collectively called "differentiated thyroid cancer". They secrete thyroid hormones, not calcitonin. It is medullary carcinoma that secretes calcitonin. Calcitonin is the tumour marker for medullary carcinoma. Thyroglobulin is the marker for differentiated thyroid cancer.</t>
         </is>
       </c>
       <c r="V868" t="inlineStr">
         <is>
-          <t>QROC</t>
+          <t>QCS</t>
         </is>
       </c>
       <c r="W868" t="inlineStr">
@@ -46430,42 +46160,37 @@
     <row r="869">
       <c r="C869" t="inlineStr">
         <is>
-          <t>About papillary thyroid cancer, all the following are true, except:</t>
+          <t>About the types of thyrotoxicosis, all the following statements are true, except:</t>
         </is>
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>It is the commonest thyroid cancer.</t>
+          <t>In Graves' disease the gland has no nodularity.</t>
         </is>
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>It usually affects teen-agers.</t>
+          <t>Plummer's disease is thyrotoxicosis that develops on top of a multinodular goitre.</t>
         </is>
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>It usually spreads by lymphatics.</t>
+          <t>Graves' disease is characterized by huge enlargement of the thyroid gland.</t>
         </is>
       </c>
       <c r="I869" t="inlineStr">
         <is>
-          <t>A high TSH helps its growth. It secretes calcitonin.</t>
+          <t>A solitary hyperactive thyrold nodule can cause thyrotoxicosis.</t>
         </is>
       </c>
       <c r="J869" t="inlineStr">
         <is>
-          <t>It secretes calcitonin.</t>
+          <t>Hashimoto's disease and subacute thyroiditis can cause transient hyperthyroidism.</t>
         </is>
       </c>
       <c r="R869" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="T869" t="inlineStr">
-        <is>
-          <t>Papillary and follicular thyroid cancers are collectively called "differentiated thyroid cancer". They secrete thyroid hormones, not calcitonin. It is medullary carcinoma that secretes calcitonin. Calcitonin is the tumour marker for medullary carcinoma. Thyroglobulin is the marker for differentiated thyroid cancer.</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V869" t="inlineStr">
@@ -46492,24 +46217,42 @@
     <row r="870">
       <c r="C870" t="inlineStr">
         <is>
-          <t>**Correct Answer:** -
-**Source Pages:** 6
-**EXP:** Follicular cells can be also obtained from a follicular adenoma. The dlagnosls of follicular carclnoma depends upon the demonstration of capsular o: blood vessel invasion on histopathological examination of excised tissue. If a follcular carcinoma Is suspected a hemithyroidectomy is the minimum excision biopsy that Is done. COPYRIGHT 2O11- FrOf. AHMED EL-BISHEY &amp; PrOf. AMR MOHSEN Page 46 Chapter (7 ) ENDOCRINE SURGERY On the other hand, the fInding of papllary structures on FNA is dlagnostic of papillary carclnoma because there is no such thing as papillary adenoma</t>
+          <t>About thyrotoxic crisis, all the following statements are true, except:</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>It follows surgery on uncontrolled thyrotoxicosis.</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>If untreated it can be fatal.</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>It is caused by marked elevation of serum thyroid stimulating hormone (TSH).</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>Hyperthermia and tachycardia are present.</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>Treatment should be carried out in ICU.</t>
         </is>
       </c>
       <c r="R870" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T870" t="inlineStr">
-        <is>
-          <t>Follicular cells can be also obtained from a follicular adenoma. The dlagnosls of follicular carclnoma depends upon the demonstration of capsular o: blood vessel invasion on histopathological examination of excised tissue. If a follcular carcinoma Is suspected a hemithyroidectomy is the minimum excision biopsy that Is done. COPYRIGHT 2O11- FrOf. AHMED EL-BISHEY &amp; PrOf. AMR MOHSEN Page 46 Chapter (7 ) ENDOCRINE SURGERY On the other hand, the fInding of papllary structures on FNA is dlagnostic of papillary carclnoma because there is no such thing as papillary adenoma</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V870" t="inlineStr">
         <is>
-          <t>QROC</t>
+          <t>QCS</t>
         </is>
       </c>
       <c r="W870" t="inlineStr">
@@ -46531,37 +46274,37 @@
     <row r="871">
       <c r="C871" t="inlineStr">
         <is>
-          <t>About the types of thyrotoxicosis, all the following statements are true, except:</t>
+          <t>About anatomy of the parathyrold glands, all the following statements are true, except:</t>
         </is>
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>In Graves' disease the gland has no nodularity.</t>
+          <t>There are always four parathyroid glands.</t>
         </is>
       </c>
       <c r="G871" t="inlineStr">
         <is>
-          <t>Plummer's disease is thyrotoxicosis that develops on top of a multinodular goitre.</t>
+          <t>The superior parathyrolds are derived from the fourth branchlal pouches while the inferior glands are derived from the third pouches.</t>
         </is>
       </c>
       <c r="H871" t="inlineStr">
         <is>
-          <t>Graves' disease is characterized by huge enlargement of the thyroid gland.</t>
+          <t>The blood supply of the parathyroid glands is mainly from the inferior thyrold arteries.</t>
         </is>
       </c>
       <c r="I871" t="inlineStr">
         <is>
-          <t>A solitary hyperactive thyrold nodule can cause thyrotoxicosis.</t>
+          <t>The Inferlor parathyrold glands may be present in the mediastInum.</t>
         </is>
       </c>
       <c r="J871" t="inlineStr">
         <is>
-          <t>Hashimoto's disease and subacute thyroiditis can cause transient hyperthyroidism.</t>
+          <t>The Inferior parathyroid gland Is usually found near the intersectlon of the</t>
         </is>
       </c>
       <c r="R871" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V871" t="inlineStr">
@@ -46588,22 +46331,37 @@
     <row r="872">
       <c r="C872" t="inlineStr">
         <is>
-          <t>prior to surgery.</t>
+          <t>Inferlor thyrold artery and the recurrent laryngeal nerve.</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Only In so% of cases there are 4 glands which are symmetrical In position on both sldes. In the remalning cases there can be more than 4 asymmetrically placed glands, or sometimes only 3 giands. The Inferior glands are more variable in posltion than the superlor ones. They may migrate with the thymus gland to the medlastinum as both are derived from the third branchlal dim pouches. 26. About primary hyperparathyroidism, one statement only Is true: A.Commonest pathology Is parathyrold hyperplasla.</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>Serum calclum is reduced.</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>Serum calcitonin Is reduced. .Osteoporosis Is one of Its consequences. 1 EMain line of treatment is chemotherapy.</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>The commonest pathology In cases of prlmary hyperparathyroldism is a parathyrold</t>
         </is>
       </c>
       <c r="R872" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T872" t="inlineStr">
-        <is>
-          <t>during pregnancy. It also tends to worsen exopthalmos. The indications for surgery Include: Failure or complications of conservative measures. Suspicion of malignancy. Large goitre, which Is unusual in cases of Graves' disease. Whether to do total or subtotal thyroidectomy is still a matter of debate among surgeons. Whatever the operation, thyrotoxicity should be controlled prior to surgery, by antl-thyroid COPYRIGHT 2011- Prof. AHMED EL-BISHRY &amp; Prnf asAD AAr SURGERY drugs to bring the patient to a euthyroid status. Operating on uncontrolled thyrotoxicosis carrles the risk of causing a fatal thyrotoxic crisls.</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V872" t="inlineStr">
         <is>
-          <t>QROC</t>
+          <t>QCS</t>
         </is>
       </c>
       <c r="W872" t="inlineStr">
@@ -46625,22 +46383,42 @@
     <row r="873">
       <c r="C873" t="inlineStr">
         <is>
-          <t>drugs to bring the patient to a euthyrold status. Operating on uncontrolled thyrotoxicosls carries the risk of causing a fatal thyrotoxic crisls. 22. About toxic multinodular goitre, all the following statements are true, except: AIt usually affects patients at an older age than those with Graves' disease. BExopthalmos is more prominent than In patients with Graves' disease. CHeart failure is more likely to occur than in patlents with Graves' disease. Goitre is usually sizable. E.The first-line treatment is thyroidectomy. B. Usually there is no exopthalmos in these patients. Because It affects patients at an older age than primary thyrotoxicosls, they are more likely to develop heart failure. Goltre Is usually sizable because thyrotoxicity develops on top of a multinodular gland. Anti-thyroid drugs tend to increase the size of the gland because they ralse the level of the suppressed TSH. Radio-iodine therapy can control toxlclty but causes little, If any, reduction In gland size. Thyroidectomy Is the only method that controls both the slze and toxicity of the gland. 2. About stridor in the postoperative perlod after thyroidectomy, all the fofllowing statements are true, except: ① Unilateral recurrent laryngeal nerve injury causes stridor. B. Dyspnoea due to deep neck haematoma should be immediately evacuated. c. Laryngeal oedema is a cause of stridor. D. Tracheal collapse due to tracheomalacia is a rare cause of stridor. E.External laryngeal nerve injury does not cause stridor.</t>
+          <t>The manifestations of primary hyperparathyroidism Include all the following, excert:</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Bony pains.</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>Renal colic.</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>Epigastric pain.</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>Easy fatigue.</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>Normal serum calcium and high PTH.</t>
         </is>
       </c>
       <c r="R873" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T873" t="inlineStr">
-        <is>
-          <t>A deep neck haematoma that causes stridor should be evacuated Immediately, even as a bed- side procedure. The sutures are removed to evacuate the compressing haematoma. The patient is then taken to the operating theatre for proper haemostasls. Injury of the external branch of superior laryngeal nerve causes loss of high pitched voice.</t>
+          <t>E</t>
         </is>
       </c>
       <c r="V873" t="inlineStr">
         <is>
-          <t>QROC</t>
+          <t>QCS</t>
         </is>
       </c>
       <c r="W873" t="inlineStr">
@@ -46662,22 +46440,42 @@
     <row r="874">
       <c r="C874" t="inlineStr">
         <is>
-          <t>About thyrotoxic crisis, all the following statements are true, except: It follows surgery on uncontrolled thyrotoxicosis. If untreated it can be fatal. CIt is caused by marked elevation of serum thyroid stimulating hormone (TSH). LD. Hyperthermia and tachycardia are present. Treatment should be carried out in ICU.</t>
+          <t>The differential diagnoses of hypercalcaemia include all the following, except:</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Primary hyperparathyroidism</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>Bone metastases</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>Multiple myeloma</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>Sarcoidosis</t>
         </is>
       </c>
       <c r="R874" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T874" t="inlineStr">
-        <is>
-          <t>The conditlon Is highly fatal. It should be urgently managed In ICU. Treatment Includes: Intravenous flulds. COPYRIGHT 2011- Prof. AHMED EL-BISHRY &amp; Prof. AMR MOHSEN Page 48 Chapter (7 ) ENDOCRINE SURGERY Cooling the patient, e.g. Ice packs. Oxygen. Digoxin for heart failure. Sedation. Intravenous hydrocortisone. Carbimazole 15-20 mg/6 hours. Lugot's lodine 10 drops/8 hours or Na- or K-lodide Intravenously as a drip. Propranolol 40 mg/6 hours orally or I mg intravenously as a drip to be repeated If needed. Chapter (7 ) ENDOCRINE SURGERY Cooling the patient, e.g. Ice packs. Oxygen. Digoadn for heart fallure. Sedation. Intravenous hydrocortIsone. Carbimazole 15-20 mg/6 hours. Lugof's lodine 10 drops/8 hours or Na- or K-lodide intravenously as a drip. Propranolol 40 mg/6 hours orally or 1 mg Intravenousty as a drlp to be repeated If needed.</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V874" t="inlineStr">
         <is>
-          <t>QROC</t>
+          <t>QCS</t>
         </is>
       </c>
       <c r="W874" t="inlineStr">
@@ -46699,37 +46497,32 @@
     <row r="875">
       <c r="C875" t="inlineStr">
         <is>
-          <t>About anatomy of the parathyrold glands, all the following statements are true, except:</t>
+          <t>About the Investigations for cllnically-suspected hyperparathyroidism, all the following statements are true, except:</t>
         </is>
       </c>
       <c r="F875" t="inlineStr">
         <is>
-          <t>There are always four parathyroid glands.</t>
+          <t>A.</t>
         </is>
       </c>
       <c r="G875" t="inlineStr">
         <is>
-          <t>The superior parathyrolds are derived from the fourth branchlal pouches while the inferior glands are derived from the third pouches.</t>
+          <t>High serum calclum Is present in patients with primary hyperparathyroidism.</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>The blood supply of the parathyroid glands is mainly from the inferior thyrold arteries.</t>
+          <t>Estimating PTH is necessary for the diagnosls of hyperparathyroldism. Estimating serum calcitonin is necessary for diagnosis. Ultrasound scan is used for localization of the adenoma. Sistamibl scan is used for localization of the adenoma.</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
         <is>
-          <t>The Inferlor parathyrold glands may be present in the mediastInum.</t>
-        </is>
-      </c>
-      <c r="J875" t="inlineStr">
-        <is>
-          <t>The Inferior parathyroid gland Is usually found near the intersectlon of the</t>
+          <t>Serum calcitonin level Is not needed for the diagnosis of hyperparathyroldism.</t>
         </is>
       </c>
       <c r="R875" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V875" t="inlineStr">
@@ -46756,27 +46549,32 @@
     <row r="876">
       <c r="C876" t="inlineStr">
         <is>
-          <t>Inferlor thyrold artery and the recurrent laryngeal nerve.</t>
+          <t>About post-thyroldectomy hypoparathyroldism, all the. following statements are true, except:</t>
         </is>
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>Only In so% of cases there are 4 glands which are symmetrical In position on both sldes. In the remalning cases there can be more than 4 asymmetrically placed glands, or sometimes only 3 giands. The Inferior glands are more variable in posltion than the superlor ones. They may migrate with the thymus gland to the medlastinum as both are derived from the third branchlal dim pouches. 26. About primary hyperparathyroidism, one statement only Is true: A.Commonest pathology Is parathyrold hyperplasla.</t>
+          <t>It may be caused by Inadvertent removal of the parathyroid glands at thyroidectomy.</t>
         </is>
       </c>
       <c r="G876" t="inlineStr">
         <is>
-          <t>Serum calclum is reduced.</t>
+          <t>It may be caused by devascularization of the parathyroid glands at operation.</t>
         </is>
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>Serum calcitonin Is reduced. .Osteoporosis Is one of Its consequences. 1 EMain line of treatment is chemotherapy.</t>
+          <t>The condition usually presents about two weeks after thyroldectomy.</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
         <is>
-          <t>The commonest pathology In cases of prlmary hyperparathyroldism is a parathyrold</t>
+          <t>The earlest symptom is facial and peripheral numbness.</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>Tetany may be manifest or latent.</t>
         </is>
       </c>
       <c r="R876" t="inlineStr">
@@ -46808,37 +46606,42 @@
     <row r="877">
       <c r="C877" t="inlineStr">
         <is>
-          <t>The manifestations of primary hyperparathyroidism Include all the following, excert:</t>
+          <t>About anatomy of the adrenal glands, allthe following statements are true, except:</t>
         </is>
       </c>
       <c r="F877" t="inlineStr">
         <is>
-          <t>Bony pains.</t>
+          <t>The right adrenal gland is closely related to the inferior vena cava.</t>
         </is>
       </c>
       <c r="G877" t="inlineStr">
         <is>
-          <t>Renal colic.</t>
+          <t>The right adrenal vein ends in the inferior vena cava.</t>
         </is>
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>Epigastric pain.</t>
+          <t>The left adrenal vein ends in the left renal vein.</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
         <is>
-          <t>Easy fatigue.</t>
+          <t>The left adrenal vein is shorter than the right vein.</t>
         </is>
       </c>
       <c r="J877" t="inlineStr">
         <is>
-          <t>Normal serum calcium and high PTH.</t>
+          <t>The middle adrenal artery is a branch of the abdominal aorta.</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>D. The right adrenal veln is very short (about Smm) and ends In the Inferior vena cav. The right veln is, therefore, diffcult to ligate and divide, and is easlly avulsed from the cav? which makes right adrenalectomy more serlous than the left.</t>
         </is>
       </c>
       <c r="R877" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V877" t="inlineStr">
@@ -46865,32 +46668,32 @@
     <row r="878">
       <c r="C878" t="inlineStr">
         <is>
-          <t>The differential diagnoses of hypercalcaemia include all the following, except:</t>
+          <t>About physiology of the adrenal gland, allthe following statements are true except:</t>
         </is>
       </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>Primary hyperparathyroidism</t>
+          <t>Aldosterone is secreted by the zona glomerulosa of the adrenal cortex.</t>
         </is>
       </c>
       <c r="G878" t="inlineStr">
         <is>
-          <t>Bone metastases</t>
+          <t>Aldosterone secretion is under control of the rennin-angiotensin syste m.</t>
         </is>
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>Multiple myeloma</t>
+          <t>A high serum cortisol level Inhibits the secretion of ACTH from she anterior pituitary.</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>The adrenal medulia is under control by the anterior pituitary gland.</t>
         </is>
       </c>
       <c r="J878" t="inlineStr">
         <is>
-          <t>Sarcoidosis</t>
+          <t>The adrenal medulla secretes adrenaline and noradrenaline. D. The adrenal medulla is controlled by the sympathetic nervous system.</t>
         </is>
       </c>
       <c r="R878" t="inlineStr">
@@ -46922,32 +46725,32 @@
     <row r="879">
       <c r="C879" t="inlineStr">
         <is>
-          <t>About the Investigations for cllnically-suspected hyperparathyroidism, all the following statements are true, except:</t>
+          <t>About Conn's syndrome, allthe following statements are true, except:</t>
         </is>
       </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t>A.</t>
+          <t>The syndrome is caused by an aldosterone-secreting tuniour of the adrenal cortex. Hypertension is the main feature of the syndrome. CHyperkalaemia is a feature of the syndrome. COPYRICUT 2O_ b E SURGERY</t>
         </is>
       </c>
       <c r="G879" t="inlineStr">
         <is>
-          <t>High serum calclum Is present in patients with primary hyperparathyroidism.</t>
+          <t>Conn's syndrome is primary hyperaldosteronlsm. The high aldosterone level causes sodlum and water retention (hypertenslon) and renat foss of potassium (hypokalaemla).</t>
         </is>
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>Estimating PTH is necessary for the diagnosls of hyperparathyroldism. Estimating serum calcitonin is necessary for diagnosis. Ultrasound scan is used for localization of the adenoma. Sistamibl scan is used for localization of the adenoma.</t>
+          <t>CT and MRl are the imaging studies of choice for tumour localization.</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
         <is>
-          <t>Serum calcitonin level Is not needed for the diagnosis of hyperparathyroldism.</t>
+          <t>Adrenalectomy is the main line of treatment.</t>
         </is>
       </c>
       <c r="R879" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V879" t="inlineStr">
@@ -46974,32 +46777,32 @@
     <row r="880">
       <c r="C880" t="inlineStr">
         <is>
-          <t>About post-thyroldectomy hypoparathyroldism, all the. following statements are true, except:</t>
+          <t>A 53 year old man is accidentally discovered to have a well-defined 2.5cm right adrenal inass on CT scan that Is done for some other reason. Hormonal studies are all normal. The proper management is:</t>
         </is>
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t>It may be caused by Inadvertent removal of the parathyroid glands at thyroidectomy.</t>
+          <t>FNAC.</t>
         </is>
       </c>
       <c r="G880" t="inlineStr">
         <is>
-          <t>It may be caused by devascularization of the parathyroid glands at operation.</t>
+          <t>Adrenalectomy.</t>
         </is>
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>The condition usually presents about two weeks after thyroldectomy.</t>
+          <t>Radiological follow-up.</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
         <is>
-          <t>The earlest symptom is facial and peripheral numbness.</t>
+          <t>Radiotherapy.</t>
         </is>
       </c>
       <c r="J880" t="inlineStr">
         <is>
-          <t>Tetany may be manifest or latent.</t>
+          <t>Radiographically-gulded embolization of the feeding arteries.</t>
         </is>
       </c>
       <c r="R880" t="inlineStr">
@@ -47031,37 +46834,32 @@
     <row r="881">
       <c r="C881" t="inlineStr">
         <is>
-          <t>About anatomy of the adrenal glands, allthe following statements are true, except:</t>
+          <t>What statement Is true of phaeochromocytoma?</t>
         </is>
       </c>
       <c r="F881" t="inlineStr">
         <is>
-          <t>The right adrenal gland is closely related to the inferior vena cava.</t>
+          <t>It is a neuroendocrine tumour of the adrenal cortex.</t>
         </is>
       </c>
       <c r="G881" t="inlineStr">
         <is>
-          <t>The right adrenal vein ends in the inferior vena cava.</t>
+          <t>It is associated with MEN I.</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>The left adrenal vein ends in the left renal vein.</t>
+          <t>It is malignant in 90% of cases.</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
         <is>
-          <t>The left adrenal vein is shorter than the right vein.</t>
+          <t>Extra-adrenal pheochromocytomas account for about 10% of cases.</t>
         </is>
       </c>
       <c r="J881" t="inlineStr">
         <is>
-          <t>The middle adrenal artery is a branch of the abdominal aorta.</t>
-        </is>
-      </c>
-      <c r="K881" t="inlineStr">
-        <is>
-          <t>D. The right adrenal veln is very short (about Smm) and ends In the Inferior vena cav. The right veln is, therefore, diffcult to ligate and divide, and is easlly avulsed from the cav? which makes right adrenalectomy more serlous than the left.</t>
+          <t>It Is bllateral in 90% of cases.</t>
         </is>
       </c>
       <c r="R881" t="inlineStr">
@@ -47093,32 +46891,32 @@
     <row r="882">
       <c r="C882" t="inlineStr">
         <is>
-          <t>About physiology of the adrenal gland, allthe following statements are true except:</t>
+          <t>For the pre and intraoperative preparation of a phaeochromocytoma patient, all the following are used, except:</t>
         </is>
       </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t>Aldosterone is secreted by the zona glomerulosa of the adrenal cortex.</t>
+          <t>Alpha adrenergic blockers.</t>
         </is>
       </c>
       <c r="G882" t="inlineStr">
         <is>
-          <t>Aldosterone secretion is under control of the rennin-angiotensin syste m.</t>
+          <t>Beta adrenergic blockers.</t>
         </is>
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>A high serum cortisol level Inhibits the secretion of ACTH from she anterior pituitary.</t>
+          <t>Correction of deficient blood volume.</t>
         </is>
       </c>
       <c r="I882" t="inlineStr">
         <is>
-          <t>The adrenal medulia is under control by the anterior pituitary gland.</t>
+          <t>Correction of hypokalaemia.</t>
         </is>
       </c>
       <c r="J882" t="inlineStr">
         <is>
-          <t>The adrenal medulla secretes adrenaline and noradrenaline. D. The adrenal medulla is controlled by the sympathetic nervous system.</t>
+          <t>Insertion of arterial cannula for intra-operative monitoring.</t>
         </is>
       </c>
       <c r="R882" t="inlineStr">
@@ -47150,32 +46948,37 @@
     <row r="883">
       <c r="C883" t="inlineStr">
         <is>
-          <t>About Conn's syndrome, allthe following statements are true, except:</t>
+          <t>About Cushing's syndrome, all the following statements are true, except:</t>
         </is>
       </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t>The syndrome is caused by an aldosterone-secreting tuniour of the adrenal cortex. Hypertension is the main feature of the syndrome. CHyperkalaemia is a feature of the syndrome. COPYRICUT 2O_ b E SURGERY</t>
+          <t>Cushing's disease is caused by an anterior pituitary adenoma.</t>
         </is>
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>Conn's syndrome is primary hyperaldosteronlsm. The high aldosterone level causes sodlum and water retention (hypertenslon) and renat foss of potassium (hypokalaemla).</t>
+          <t>With adrenal Cushing's syndrome ACTH level is elevated.</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>CT and MRl are the imaging studies of choice for tumour localization.</t>
+          <t>Truncal obesity is one of the manifestations of the syndrome.</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
         <is>
-          <t>Adrenalectomy is the main line of treatment.</t>
+          <t>These patients tend to be hypertensive.</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>These patients are prone to develop diabetes mellitus.</t>
         </is>
       </c>
       <c r="R883" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V883" t="inlineStr">
@@ -47202,37 +47005,37 @@
     <row r="884">
       <c r="C884" t="inlineStr">
         <is>
-          <t>A 53 year old man is accidentally discovered to have a well-defined 2.5cm right adrenal inass on CT scan that Is done for some other reason. Hormonal studies are all normal. The proper management is:</t>
+          <t>The risks of adrenalectomy for Cushing's syndrome are Increased by all the following, except:</t>
         </is>
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>FNAC.</t>
+          <t>Hypertension.</t>
         </is>
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>Adrenalectomy.</t>
+          <t>Diabetes mellitus.</t>
         </is>
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>Radiological follow-up.</t>
+          <t>Delayed wound healing.</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
         <is>
-          <t>Radiotherapy.</t>
+          <t>Tendency to gastro-duodenal ulceration.</t>
         </is>
       </c>
       <c r="J884" t="inlineStr">
         <is>
-          <t>Radiographically-gulded embolization of the feeding arteries.</t>
+          <t>Bronchospasm.</t>
         </is>
       </c>
       <c r="R884" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="V884" t="inlineStr">
@@ -47259,37 +47062,32 @@
     <row r="885">
       <c r="C885" t="inlineStr">
         <is>
-          <t>What statement Is true of phaeochromocytoma?</t>
+          <t>The most common position of the RIGHT recurrent laryngeal nerve is</t>
         </is>
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>It is a neuroendocrine tumour of the adrenal cortex.</t>
+          <t>Anterior to the inferior thyroid artery</t>
         </is>
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>It is associated with MEN I.</t>
+          <t>Posterior to the inferior thyroid artery</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>It is malignant in 90% of cases.</t>
+          <t>Between the branches of the inferior thyroid artery</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
         <is>
-          <t>Extra-adrenal pheochromocytomas account for about 10% of cases.</t>
-        </is>
-      </c>
-      <c r="J885" t="inlineStr">
-        <is>
-          <t>It Is bllateral in 90% of cases.</t>
+          <t>Absent (nonrecurrent laryngeal nerve)</t>
         </is>
       </c>
       <c r="R885" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V885" t="inlineStr">
@@ -47309,44 +47107,39 @@
       </c>
       <c r="AC885" t="inlineStr">
         <is>
-          <t>External, Endocrine Surgery</t>
+          <t>External, Schwartz</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="C886" t="inlineStr">
         <is>
-          <t>For the pre and intraoperative preparation of a phaeochromocytoma patient, all the following are used, except:</t>
+          <t>Thyroid hormone receptors</t>
         </is>
       </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>Alpha adrenergic blockers.</t>
+          <t>Bind T4</t>
         </is>
       </c>
       <c r="G886" t="inlineStr">
         <is>
-          <t>Beta adrenergic blockers.</t>
+          <t>Bind T3</t>
         </is>
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>Correction of deficient blood volume.</t>
+          <t>Are present in the mitochondria</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
         <is>
-          <t>Correction of hypokalaemia.</t>
-        </is>
-      </c>
-      <c r="J886" t="inlineStr">
-        <is>
-          <t>Insertion of arterial cannula for intra-operative monitoring.</t>
+          <t>Are present on the cell membrane</t>
         </is>
       </c>
       <c r="R886" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V886" t="inlineStr">
@@ -47366,44 +47159,39 @@
       </c>
       <c r="AC886" t="inlineStr">
         <is>
-          <t>External, Endocrine Surgery</t>
+          <t>External, Schwartz</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="C887" t="inlineStr">
         <is>
-          <t>About Cushing's syndrome, all the following statements are true, except:</t>
+          <t>The inferior parathyroid glands are derived from the</t>
         </is>
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>Cushing's disease is caused by an anterior pituitary adenoma.</t>
+          <t>1st branchial pouch</t>
         </is>
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>With adrenal Cushing's syndrome ACTH level is elevated.</t>
+          <t>2nd branchial pouch</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>Truncal obesity is one of the manifestations of the syndrome.</t>
+          <t>3rd branchial pouch</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
         <is>
-          <t>These patients tend to be hypertensive.</t>
-        </is>
-      </c>
-      <c r="J887" t="inlineStr">
-        <is>
-          <t>These patients are prone to develop diabetes mellitus.</t>
+          <t>4th branchial pouch</t>
         </is>
       </c>
       <c r="R887" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V887" t="inlineStr">
@@ -47423,44 +47211,44 @@
       </c>
       <c r="AC887" t="inlineStr">
         <is>
-          <t>External, Endocrine Surgery</t>
+          <t>External, Schwartz</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="C888" t="inlineStr">
         <is>
-          <t>The risks of adrenalectomy for Cushing's syndrome are Increased by all the following, except:</t>
+          <t>Which of the following receptors has the greatest affinity for epinephrine?</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>Hypertension.</t>
+          <t>α adrenergic receptor</t>
         </is>
       </c>
       <c r="G888" t="inlineStr">
         <is>
-          <t>Diabetes mellitus.</t>
+          <t>β1 adrenergic receptor</t>
         </is>
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>Delayed wound healing.</t>
+          <t>β2 adrenergic receptor</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
         <is>
-          <t>Tendency to gastro-duodenal ulceration.</t>
-        </is>
-      </c>
-      <c r="J888" t="inlineStr">
-        <is>
-          <t>Bronchospasm.</t>
+          <t>γ adrenergic receptor</t>
         </is>
       </c>
       <c r="R888" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T888" t="inlineStr">
+        <is>
+          <t>Free thyroid hormone enters the cell membrane by diffusion or by specific carriers and is carried to the nuclear membrane by binding to specific proteins. T4 is deiodinated to T, and enters the nucleus via active transport, where it binds to the thyroid hormone receptor. The T3 receptor is similar to the nuclear receptors for glucocorticoids, mineralocorticoids, es- trogens, vitamin D, and retinoic acid. In humans, two types of T3 receptor genes (α and β) are located on chromosomes 3 and 17. (See Schwartz 9thed., p 1348.) In humans, the superior parathyroid glands are derived from the fourth branchial pouch, which also gives rise to the thy- roid gland. The third branchial pouches give rise to the infe- rior parathyroid glands and the thymus. (See Schwartz 9th ed., p1374.) The parathyroid cells rely on a Gprotein coupled membrane receptor, designated the calcium-sensing receptor (CASR), to regulate PTH secretion by sensing extracellular calci- um levels. PTH secretion also is stimulated by low levels of 1,25-dihydroxy vitamin D, catecholamines, and hypomag- nesemia. (See Schwartz 9thed., p1376.) Adrenergic receptorsare transmembrane-spanningmol- ecules, which are coupled to G proteins. They may be subdivided into α and β subtypes, which are localized in different tissues, have varying affinity to various cate- cholamines, and mediate distinct biologic effects (Table 38</t>
         </is>
       </c>
       <c r="V888" t="inlineStr">
@@ -47480,34 +47268,34 @@
       </c>
       <c r="AC888" t="inlineStr">
         <is>
-          <t>External, Endocrine Surgery</t>
+          <t>External, Schwartz</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="C889" t="inlineStr">
         <is>
-          <t>The most common position of the RIGHT recurrent laryngeal nerve is</t>
+          <t>The left adrenal vein drains into the</t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>Anterior to the inferior thyroid artery</t>
+          <t>IVC</t>
         </is>
       </c>
       <c r="G889" t="inlineStr">
         <is>
-          <t>Posterior to the inferior thyroid artery</t>
+          <t>Left renal vein</t>
         </is>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>Between the branches of the inferior thyroid artery</t>
+          <t>Left gonadal vein</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
         <is>
-          <t>Absent (nonrecurrent laryngeal nerve)</t>
+          <t>Splenic vein</t>
         </is>
       </c>
       <c r="R889" t="inlineStr">
@@ -47539,32 +47327,32 @@
     <row r="890">
       <c r="C890" t="inlineStr">
         <is>
-          <t>Thyroid hormone receptors</t>
+          <t>Which of the following is an effect of thyroid hormones?</t>
         </is>
       </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>Bind T4</t>
+          <t>Positive inotropic effect on the heart</t>
         </is>
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>Bind T3</t>
+          <t>Maintenance of the normal hypoxic drive to breathe</t>
         </is>
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>Are present in the mitochondria</t>
+          <t>Increased protein turnover</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
         <is>
-          <t>Are present on the cell membrane</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="R890" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V890" t="inlineStr">
@@ -47591,32 +47379,37 @@
     <row r="891">
       <c r="C891" t="inlineStr">
         <is>
-          <t>The inferior parathyroid glands are derived from the</t>
+          <t>The origin of the superior thyroid artery is</t>
         </is>
       </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t>1st branchial pouch</t>
+          <t>Internal carotid artery</t>
         </is>
       </c>
       <c r="G891" t="inlineStr">
         <is>
-          <t>2nd branchial pouch</t>
+          <t>External carotid artery</t>
         </is>
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>3rd branchial pouch</t>
+          <t>Thyrocervical trunk</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
         <is>
-          <t>4th branchial pouch</t>
+          <t>Innominate artery</t>
         </is>
       </c>
       <c r="R891" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T891" t="inlineStr">
+        <is>
+          <t>In contrast to the arterial supply, each adrenal usually is drained by a single, major adrenal vein. The right adrenal vein is usually short and drains into the IVC, whereas the left adrenal vein is longer and empties into the left renal vein after joining the inferior phrenic vein. (See Schwartz 9th ed., p 1389.) Thyroid hormones affect almost every system in the body. They are important for fetal brain development and skel- etal maturation. T increases oxygen consumption, basal CHAPTER 38 metabolic rate, and heat production by stimulation of Na⁺/ K⁺ ATPase in various tissues. It also has positive inotropic and chronotropic effects on the heart by increasing tran- scription of the Ca2² ATPase in the sarcoplasmic reticu- lum and increasing levels of beta-adrenergic receptors and concentration of G proteins. Myocardial alpha receptors are decreased and actions of catecholamines are amplified. Thyroid hormones are responsible for maintaining the nor- mal hypoxic and hypercapnic drive in the respiratory cen- ter of the brain. They also increase GI motility, leading to diarrhea in hyperthyroidism and constipation in hypothy- Thyroid, Parathyroid, and Adrenal roidism. Thyroid hormones also increase bone and protein turnover and the speed of muscle contraction and relax- ation. They also increase glycogenolysis, hepatic gluco- neogenesis, intestinal glucose absorption, and cholesterol synthesis and degradation. (See Schwartz 9th ed., p 1349.) The superior thyroid arteries arise from the ipsilateral ex- ternal carotid arteries and divide into anterior and poste- rior branches at the apices of the thyroid lobes. The inferior thyroid arteries arise from the thyrocervical trunk shortly after their origin from the subclavian arteries. The inferior thyroid arteries travel upward in the neck posterior to the carotid sheath to enter the thyroid lobes at their midpoint. A thyroidea ima artery arises directly from the aorta or innominate in 1 to 4% of individuals to enter the isthmus or replace a missing inferior thyroid artery. (See Schwartz 9th ed., p 1345, and Fig. 38-2.) Thyroid Ext. carotid a. cartilage Pyramidal lobe Sup. thyroid a. and v. Int. jugular v. Middle thyroid v. Common carotid a. Inf. thyroid v. Thyrocervical CHAPTER 38 trunk Recurrent laryngeal n. Thyroidea ima a. Vagus n. (variable) Vagus n. Arch of aorta Thyroid, Parathyroid, and Adrenal A Thyroid gland Trachea Strap muscles Sternocleido- mastoid m. Int. jugular v. Vagus n. Common carotid a. Inf. thyroid a. Vertebral laryngeal n. Recurrent B V. and a. 9.The most common location of the superior parathyroid glands is</t>
         </is>
       </c>
       <c r="V891" t="inlineStr">
@@ -47643,37 +47436,32 @@
     <row r="892">
       <c r="C892" t="inlineStr">
         <is>
-          <t>Which of the following receptors has the greatest affinity for epinephrine?</t>
+          <t>The most common location of the superior parathyroid glands is</t>
         </is>
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>α adrenergic receptor</t>
+          <t>Dorsal to the recurrent laryngeal nerve (RLN), within 1 cm of the junction of the RLN and inferior thyroid artery</t>
         </is>
       </c>
       <c r="G892" t="inlineStr">
         <is>
-          <t>β1 adrenergic receptor</t>
+          <t>Ventral to the recurrent laryngeal nerve (RLN), within 1 cm of the junction of the RLN and inferior thyroid artery</t>
         </is>
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>β2 adrenergic receptor</t>
+          <t>Dorsal to the recurrent laryngeal nerve (RLN), within 3 cm of the junction of the RLN and inferior thyroid artery</t>
         </is>
       </c>
       <c r="I892" t="inlineStr">
         <is>
-          <t>γ adrenergic receptor</t>
+          <t>Ventral to the recurrent laryngeal nerve (RLN), within 3 cm of the junction of the RLN and inferior thyroid artery</t>
         </is>
       </c>
       <c r="R892" t="inlineStr">
         <is>
           <t>A</t>
-        </is>
-      </c>
-      <c r="T892" t="inlineStr">
-        <is>
-          <t>Free thyroid hormone enters the cell membrane by diffusion or by specific carriers and is carried to the nuclear membrane by binding to specific proteins. T4 is deiodinated to T, and enters the nucleus via active transport, where it binds to the thyroid hormone receptor. The T3 receptor is similar to the nuclear receptors for glucocorticoids, mineralocorticoids, es- trogens, vitamin D, and retinoic acid. In humans, two types of T3 receptor genes (α and β) are located on chromosomes 3 and 17. (See Schwartz 9thed., p 1348.) In humans, the superior parathyroid glands are derived from the fourth branchial pouch, which also gives rise to the thy- roid gland. The third branchial pouches give rise to the infe- rior parathyroid glands and the thymus. (See Schwartz 9th ed., p1374.) The parathyroid cells rely on a Gprotein coupled membrane receptor, designated the calcium-sensing receptor (CASR), to regulate PTH secretion by sensing extracellular calci- um levels. PTH secretion also is stimulated by low levels of 1,25-dihydroxy vitamin D, catecholamines, and hypomag- nesemia. (See Schwartz 9thed., p1376.) Adrenergic receptorsare transmembrane-spanningmol- ecules, which are coupled to G proteins. They may be subdivided into α and β subtypes, which are localized in different tissues, have varying affinity to various cate- cholamines, and mediate distinct biologic effects (Table 38</t>
         </is>
       </c>
       <c r="V892" t="inlineStr">
@@ -47700,32 +47488,32 @@
     <row r="893">
       <c r="C893" t="inlineStr">
         <is>
-          <t>The left adrenal vein drains into the</t>
+          <t>Secreted parathormone has a half-life of</t>
         </is>
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>IVC</t>
+          <t>2-4 minutes</t>
         </is>
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>Left renal vein</t>
+          <t>45-60 minutes</t>
         </is>
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>Left gonadal vein</t>
+          <t>3 hours</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
         <is>
-          <t>Splenic vein</t>
+          <t>8 hours</t>
         </is>
       </c>
       <c r="R893" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V893" t="inlineStr">
@@ -47752,32 +47540,37 @@
     <row r="894">
       <c r="C894" t="inlineStr">
         <is>
-          <t>Which of the following is an effect of thyroid hormones?</t>
+          <t>Which of the following is the substrate for allcate- cholamines?</t>
         </is>
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>Positive inotropic effect on the heart</t>
+          <t>Alanine</t>
         </is>
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>Maintenance of the normal hypoxic drive to breathe</t>
+          <t>Leucine</t>
         </is>
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>Increased protein turnover</t>
+          <t>Tryptophan</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Tyrosine</t>
         </is>
       </c>
       <c r="R894" t="inlineStr">
         <is>
           <t>D</t>
+        </is>
+      </c>
+      <c r="T894" t="inlineStr">
+        <is>
+          <t>Recurrent laryngeal n. Thyroid, Parathyroid, and Adrenal Secreted PTH has a half-life of 2 to 4 minutes. In the liver, PTH is metabolized into the active N-terminal compo- nent and the relatively inactive C-terminal fraction. The C-terminal component is excreted by the kidneys and ac- cumulates in chronic renal failure. (See Schwartz 9thed., p1376.) Catecholamine hormones (epinephrine, norepinephrine, and dopamine) are produced not only in the central and sympa- thetic nervous system but also in the adrenal medulla. The substrate, tyrosine, is converted to catecholamines via a series of steps shown in Fig. 38-4. (See Schwartz 9th ed., p 1392.) CHAPTER 38 Thyroid, Parathyroid, and Adrenal 12.The adrenal cortex arises from</t>
         </is>
       </c>
       <c r="V894" t="inlineStr">
@@ -47804,37 +47597,32 @@
     <row r="895">
       <c r="C895" t="inlineStr">
         <is>
-          <t>The origin of the superior thyroid artery is</t>
+          <t>The adrenal cortex arises from</t>
         </is>
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>Internal carotid artery</t>
+          <t>Ectoderm</t>
         </is>
       </c>
       <c r="G895" t="inlineStr">
         <is>
-          <t>External carotid artery</t>
+          <t>Mesoderm</t>
         </is>
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>Thyrocervical trunk</t>
+          <t>Endoderm</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
         <is>
-          <t>Innominate artery</t>
+          <t>Neural crest</t>
         </is>
       </c>
       <c r="R895" t="inlineStr">
         <is>
           <t>B</t>
-        </is>
-      </c>
-      <c r="T895" t="inlineStr">
-        <is>
-          <t>In contrast to the arterial supply, each adrenal usually is drained by a single, major adrenal vein. The right adrenal vein is usually short and drains into the IVC, whereas the left adrenal vein is longer and empties into the left renal vein after joining the inferior phrenic vein. (See Schwartz 9th ed., p 1389.) Thyroid hormones affect almost every system in the body. They are important for fetal brain development and skel- etal maturation. T increases oxygen consumption, basal CHAPTER 38 metabolic rate, and heat production by stimulation of Na⁺/ K⁺ ATPase in various tissues. It also has positive inotropic and chronotropic effects on the heart by increasing tran- scription of the Ca2² ATPase in the sarcoplasmic reticu- lum and increasing levels of beta-adrenergic receptors and concentration of G proteins. Myocardial alpha receptors are decreased and actions of catecholamines are amplified. Thyroid hormones are responsible for maintaining the nor- mal hypoxic and hypercapnic drive in the respiratory cen- ter of the brain. They also increase GI motility, leading to diarrhea in hyperthyroidism and constipation in hypothy- Thyroid, Parathyroid, and Adrenal roidism. Thyroid hormones also increase bone and protein turnover and the speed of muscle contraction and relax- ation. They also increase glycogenolysis, hepatic gluco- neogenesis, intestinal glucose absorption, and cholesterol synthesis and degradation. (See Schwartz 9th ed., p 1349.) The superior thyroid arteries arise from the ipsilateral ex- ternal carotid arteries and divide into anterior and poste- rior branches at the apices of the thyroid lobes. The inferior thyroid arteries arise from the thyrocervical trunk shortly after their origin from the subclavian arteries. The inferior thyroid arteries travel upward in the neck posterior to the carotid sheath to enter the thyroid lobes at their midpoint. A thyroidea ima artery arises directly from the aorta or innominate in 1 to 4% of individuals to enter the isthmus or replace a missing inferior thyroid artery. (See Schwartz 9th ed., p 1345, and Fig. 38-2.) Thyroid Ext. carotid a. cartilage Pyramidal lobe Sup. thyroid a. and v. Int. jugular v. Middle thyroid v. Common carotid a. Inf. thyroid v. Thyrocervical CHAPTER 38 trunk Recurrent laryngeal n. Thyroidea ima a. Vagus n. (variable) Vagus n. Arch of aorta Thyroid, Parathyroid, and Adrenal A Thyroid gland Trachea Strap muscles Sternocleido- mastoid m. Int. jugular v. Vagus n. Common carotid a. Inf. thyroid a. Vertebral laryngeal n. Recurrent B V. and a. 9.The most common location of the superior parathyroid glands is</t>
         </is>
       </c>
       <c r="V895" t="inlineStr">
@@ -47861,32 +47649,37 @@
     <row r="896">
       <c r="C896" t="inlineStr">
         <is>
-          <t>The most common location of the superior parathyroid glands is</t>
+          <t>The inferior adrenal artery originates from the</t>
         </is>
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>Dorsal to the recurrent laryngeal nerve (RLN), within 1 cm of the junction of the RLN and inferior thyroid artery</t>
+          <t>Phrenic artery</t>
         </is>
       </c>
       <c r="G896" t="inlineStr">
         <is>
-          <t>Ventral to the recurrent laryngeal nerve (RLN), within 1 cm of the junction of the RLN and inferior thyroid artery</t>
+          <t>Splenic artery</t>
         </is>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>Dorsal to the recurrent laryngeal nerve (RLN), within 3 cm of the junction of the RLN and inferior thyroid artery</t>
+          <t>Renal artery</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
         <is>
-          <t>Ventral to the recurrent laryngeal nerve (RLN), within 3 cm of the junction of the RLN and inferior thyroid artery</t>
+          <t>Aorta</t>
         </is>
       </c>
       <c r="R896" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T896" t="inlineStr">
+        <is>
+          <t>Which of the following is NOT an effect of glucocorticos- teroids?</t>
         </is>
       </c>
       <c r="V896" t="inlineStr">
@@ -47913,32 +47706,32 @@
     <row r="897">
       <c r="C897" t="inlineStr">
         <is>
-          <t>Secreted parathormone has a half-life of</t>
+          <t>Which of the following is NOT an effect of glucocorticosteroids?</t>
         </is>
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>2-4 minutes</t>
+          <t>Decreased muscle protein synthesis</t>
         </is>
       </c>
       <c r="G897" t="inlineStr">
         <is>
-          <t>45-60 minutes</t>
+          <t>Decreased lipolysis</t>
         </is>
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>3 hours</t>
+          <t>Inhibition of bone formation</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
         <is>
-          <t>8 hours</t>
+          <t>Increased cardiac output</t>
         </is>
       </c>
       <c r="R897" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V897" t="inlineStr">
@@ -47965,27 +47758,27 @@
     <row r="898">
       <c r="C898" t="inlineStr">
         <is>
-          <t>Which of the following is the substrate for allcate- cholamines?</t>
+          <t>The RET proto-oncogene is associated with</t>
         </is>
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>Alanine</t>
+          <t>Papillary thyroid cancer</t>
         </is>
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t>Leucine</t>
+          <t>Hirschsprung's disease</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>Tryptophan</t>
+          <t>Pheochomocytoma</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
         <is>
-          <t>Tyrosine</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="R898" t="inlineStr">
@@ -47995,7 +47788,7 @@
       </c>
       <c r="T898" t="inlineStr">
         <is>
-          <t>Recurrent laryngeal n. Thyroid, Parathyroid, and Adrenal Secreted PTH has a half-life of 2 to 4 minutes. In the liver, PTH is metabolized into the active N-terminal compo- nent and the relatively inactive C-terminal fraction. The C-terminal component is excreted by the kidneys and ac- cumulates in chronic renal failure. (See Schwartz 9thed., p1376.) Catecholamine hormones (epinephrine, norepinephrine, and dopamine) are produced not only in the central and sympa- thetic nervous system but also in the adrenal medulla. The substrate, tyrosine, is converted to catecholamines via a series of steps shown in Fig. 38-4. (See Schwartz 9th ed., p 1392.) CHAPTER 38 Thyroid, Parathyroid, and Adrenal 12.The adrenal cortex arises from</t>
+          <t>Glucocorticoids have important functions in intermediary metabolism but also affect connective tissue, bone, immune, cardiovascular, renal, and central nervous systems, as outlined in Table 38-2. (See Schwartz 9thed., p 1391.) TABLE 38-2 Functions of glucocorticoid hormones Function/System Effects Glucose metabolism Increased hepatic glycogen deposition, gluconeogenesis, decreased muscle glucose Protein metabolism Decreased muscle protein synthesis, increased uptake and metabolism CHAPTER 38 catabolism Fat metabolism Increased lipolysis in adipose tissue Connective tissue Inhibition of fibroblasts, loss of collagen, thinning of skin, striae formation Skeletal system Inhibition of bone formation, increased osteoclast activity, potentiate the action of PTH Immune system Increases circulation of polymorphonuclear cells, decreases numbers of lymphocytes, mono- cytes, and eosinophils, reduces migration of inflammatory cells to sites of injury Cardiovascular Increases cardiac output and peripheral vascular Renal system system Sodium retention, hypokalemia, hypertension via tone Thyroid, Parathyroid, and Adrenal mineralocorticoid effect, increased glomerular filtration via glucocorticoid effects Endocrine system Inhibits TSH synthesis and release, decreased TBG levels, decreased conversion ofT, to T PTH = parathyroid hormone; T = 3,5;3-triiodothyronine; T = thyroxine; TBG = thyroxine-binding globulin; TSH = thyroid-stimulating hormone. The RET proto-oncogene plays a significant role in the pathogenesis of thyroid cancers. It is located on chromo- some 10 and encodes a receptor tyrosine kinase, which binds several growth factors such as glial-derived neu- rotrophic factor and neurturin. The RET protein is ex- pressed in tissues derived from the embryonic nervous and excretory systems. Therefore, RET disruption can lead to developmental abnormalities in organs derived from these systems, such as the enteric nervous system (Hirschsprung's disease) and kidney. Germline mutations in the RET proto- oncogene are known to predispose to MEN2A, MEN2B, and familial MTCs, and somatic mutations have been dem- onstrated in tumors derived from the neural crest, such as MTCs (30%) and pheochromocytomas. (See Schwartz 9thed., p 1361, and Table 38-3.) CHAPTER 38 Thyroid, Parathyroid, and Adrenal 16.Thyroxine (T4) is composed of</t>
         </is>
       </c>
       <c r="V898" t="inlineStr">
@@ -48022,32 +47815,37 @@
     <row r="899">
       <c r="C899" t="inlineStr">
         <is>
-          <t>The adrenal cortex arises from</t>
+          <t>Thyroxine (T4) is composed of</t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t>Ectoderm</t>
+          <t>Two Diiodotyrosine (DIT) molecules</t>
         </is>
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>Mesoderm</t>
+          <t>One Diiodotyrosine (DIT) molecules and two monoiodohyrosin (MIT) molecules</t>
         </is>
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>Endoderm</t>
+          <t>Four monoiodohyrosin (MIT) molecules</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
         <is>
-          <t>Neural crest</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="R899" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T899" t="inlineStr">
+        <is>
+          <t>The synthesis of thyroid hormone consists of several steps. The first, iodide trapping, involves active (ATP-dependent) transport of iodide across the basement membrane of the thy- rocyte via an intrinsic membrane protein, the sodium/iodine (Na⁺/I-) symporter. Thyroglobulin (Tg)is a large (660 kDa) glycoprotein, which is present in thyroid follicles and has four tyrosyl residues. The second step in thyroid hormone synthe- sis involves oxidation of iodide to iodine and iodination of ty- rosine residues on Tg, to form monoiodotyrosines (MIT) and diiodotyrosines (DIT). Both processes are catalyzed by thy- roid peroxidase (TPO). A recently identified protein, pendrin, is thought to mediate iodine efflux at the apical membrane. The third step leads to coupling of two DIT molecules to form tetra-iodothyronine or thyroxine (T4), and one DIT molecule with one MIT molecule to form 3,5,3'-triiodothyronine (T3) or 3,3',5'-triiodothyronine reverse (rT, See Schwartz 9thed., p1348.) Which of the following is a function of aldosterone?</t>
         </is>
       </c>
       <c r="V899" t="inlineStr">
@@ -48074,37 +47872,32 @@
     <row r="900">
       <c r="C900" t="inlineStr">
         <is>
-          <t>The inferior adrenal artery originates from the</t>
+          <t>Which of the following is a function of aldosterone?</t>
         </is>
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>Phrenic artery</t>
+          <t>Increased potassium absorption</t>
         </is>
       </c>
       <c r="G900" t="inlineStr">
         <is>
-          <t>Splenic artery</t>
+          <t>Increased hydrogen ion absorption</t>
         </is>
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>Renal artery</t>
+          <t>Increased sodium absorption</t>
         </is>
       </c>
       <c r="I900" t="inlineStr">
         <is>
-          <t>Aorta</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="R900" t="inlineStr">
         <is>
           <t>C</t>
-        </is>
-      </c>
-      <c r="T900" t="inlineStr">
-        <is>
-          <t>Which of the following is NOT an effect of glucocorticos- teroids?</t>
         </is>
       </c>
       <c r="V900" t="inlineStr">
@@ -48131,27 +47924,27 @@
     <row r="901">
       <c r="C901" t="inlineStr">
         <is>
-          <t>Which of the following is NOT an effect of glucocorticosteroids?</t>
+          <t>Glucocorticoids are produced in the</t>
         </is>
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>Decreased muscle protein synthesis</t>
+          <t>Zona glomerulosa</t>
         </is>
       </c>
       <c r="G901" t="inlineStr">
         <is>
-          <t>Decreased lipolysis</t>
+          <t>Zona fasciculate</t>
         </is>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>Inhibition of bone formation</t>
+          <t>Zona reticularis</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
         <is>
-          <t>Increased cardiac output</t>
+          <t>Adrenal medulla</t>
         </is>
       </c>
       <c r="R901" t="inlineStr">
@@ -48183,37 +47976,32 @@
     <row r="902">
       <c r="C902" t="inlineStr">
         <is>
-          <t>The RET proto-oncogene is associated with</t>
+          <t>The paired lateral thyroid anlages fuse with the median thyroid anlage in the 5th week of gestation. These paired lateral anlages originate from</t>
         </is>
       </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t>Papillary thyroid cancer</t>
+          <t>Ectoderm</t>
         </is>
       </c>
       <c r="G902" t="inlineStr">
         <is>
-          <t>Hirschsprung's disease</t>
+          <t>Mesoderm</t>
         </is>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>Pheochomocytoma</t>
+          <t>Endoderm</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Neural crest</t>
         </is>
       </c>
       <c r="R902" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="T902" t="inlineStr">
-        <is>
-          <t>Glucocorticoids have important functions in intermediary metabolism but also affect connective tissue, bone, immune, cardiovascular, renal, and central nervous systems, as outlined in Table 38-2. (See Schwartz 9thed., p 1391.) TABLE 38-2 Functions of glucocorticoid hormones Function/System Effects Glucose metabolism Increased hepatic glycogen deposition, gluconeogenesis, decreased muscle glucose Protein metabolism Decreased muscle protein synthesis, increased uptake and metabolism CHAPTER 38 catabolism Fat metabolism Increased lipolysis in adipose tissue Connective tissue Inhibition of fibroblasts, loss of collagen, thinning of skin, striae formation Skeletal system Inhibition of bone formation, increased osteoclast activity, potentiate the action of PTH Immune system Increases circulation of polymorphonuclear cells, decreases numbers of lymphocytes, mono- cytes, and eosinophils, reduces migration of inflammatory cells to sites of injury Cardiovascular Increases cardiac output and peripheral vascular Renal system system Sodium retention, hypokalemia, hypertension via tone Thyroid, Parathyroid, and Adrenal mineralocorticoid effect, increased glomerular filtration via glucocorticoid effects Endocrine system Inhibits TSH synthesis and release, decreased TBG levels, decreased conversion ofT, to T PTH = parathyroid hormone; T = 3,5;3-triiodothyronine; T = thyroxine; TBG = thyroxine-binding globulin; TSH = thyroid-stimulating hormone. The RET proto-oncogene plays a significant role in the pathogenesis of thyroid cancers. It is located on chromo- some 10 and encodes a receptor tyrosine kinase, which binds several growth factors such as glial-derived neu- rotrophic factor and neurturin. The RET protein is ex- pressed in tissues derived from the embryonic nervous and excretory systems. Therefore, RET disruption can lead to developmental abnormalities in organs derived from these systems, such as the enteric nervous system (Hirschsprung's disease) and kidney. Germline mutations in the RET proto- oncogene are known to predispose to MEN2A, MEN2B, and familial MTCs, and somatic mutations have been dem- onstrated in tumors derived from the neural crest, such as MTCs (30%) and pheochromocytomas. (See Schwartz 9thed., p 1361, and Table 38-3.) CHAPTER 38 Thyroid, Parathyroid, and Adrenal 16.Thyroxine (T4) is composed of</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V902" t="inlineStr">
@@ -48240,37 +48028,32 @@
     <row r="903">
       <c r="C903" t="inlineStr">
         <is>
-          <t>Thyroxine (T4) is composed of</t>
+          <t>Cholesterol is the precursor of all hormones produced in the adrenal gland. The first step in the synthesis of all adrenal hormones is to cleave cholesterol to produce</t>
         </is>
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>Two Diiodotyrosine (DIT) molecules</t>
+          <t>Progesterone</t>
         </is>
       </c>
       <c r="G903" t="inlineStr">
         <is>
-          <t>One Diiodotyrosine (DIT) molecules and two monoiodohyrosin (MIT) molecules</t>
+          <t>Pregnenolone</t>
         </is>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>Four monoiodohyrosin (MIT) molecules</t>
+          <t>17α-hydroxypregnenolone</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>11-deoxy-corticosterone</t>
         </is>
       </c>
       <c r="R903" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="T903" t="inlineStr">
-        <is>
-          <t>The synthesis of thyroid hormone consists of several steps. The first, iodide trapping, involves active (ATP-dependent) transport of iodide across the basement membrane of the thy- rocyte via an intrinsic membrane protein, the sodium/iodine (Na⁺/I-) symporter. Thyroglobulin (Tg)is a large (660 kDa) glycoprotein, which is present in thyroid follicles and has four tyrosyl residues. The second step in thyroid hormone synthe- sis involves oxidation of iodide to iodine and iodination of ty- rosine residues on Tg, to form monoiodotyrosines (MIT) and diiodotyrosines (DIT). Both processes are catalyzed by thy- roid peroxidase (TPO). A recently identified protein, pendrin, is thought to mediate iodine efflux at the apical membrane. The third step leads to coupling of two DIT molecules to form tetra-iodothyronine or thyroxine (T4), and one DIT molecule with one MIT molecule to form 3,5,3'-triiodothyronine (T3) or 3,3',5'-triiodothyronine reverse (rT, See Schwartz 9thed., p1348.) Which of the following is a function of aldosterone?</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V903" t="inlineStr">
@@ -48297,32 +48080,37 @@
     <row r="904">
       <c r="C904" t="inlineStr">
         <is>
-          <t>Which of the following is a function of aldosterone?</t>
+          <t>Propylthiouracil</t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>Increased potassium absorption</t>
+          <t>Can be given once a day in patients with hyperthyroidism</t>
         </is>
       </c>
       <c r="G904" t="inlineStr">
         <is>
-          <t>Increased hydrogen ion absorption</t>
+          <t>Can cause agranulocytosis</t>
         </is>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>Increased sodium absorption</t>
+          <t>Does not affect the peripheral conversion of T4 to T3</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Does not cross the placenta</t>
         </is>
       </c>
       <c r="R904" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T904" t="inlineStr">
+        <is>
+          <t>Antithyroid medications generally are administered in prepa- ration for RAI ablation or surgery. The drugs commonly used are propylthiouracil (PTU, 100 to 300 mg three times daily) and methimazole (10 to 30 mg three times daily, then once daily). Methimazole has a longer half-life and can be dosed once daily. Both drugs reduce thyroid hormone production by inhibiting the organic binding of iodine and the coupling of iodotyrosines (mediated by TPO). In addition, PTU also in- hibits the peripheral conversion of T4 to Tz, making it useful for the treatment of thyroid storm. Both drugs can cross the placenta, inhibiting fetal thyroid function, and are excreted in breast milk, although PTU has a lower risk of transplacental transfer. Methimazole also has been associated with congeni- tal aplasia; therefore, PTU is preferred in pregnant and breast- feeding women. Side effects of treatment include reversible granulocytopenia, skin rashes, fever, peripheral neuritis, pol- yarteritis, vasculitis, and, rarely, agranulocytosis and aplastic anemia. Patients should be monitored for these possible com- plications and should always be warned to stop PTU or me- thimazole immediately and seek medical advice should they develop a sore throat or fever. Treatment of agranulocytosis in- volves admission to the hospital, discontinuation of the drug, and broad-spectrum antibiotic therapy. Surgery should be postponed until the granulocyte count reaches 1000 cells/m3. (See Schwartz 9thed., p1354.) Which of the following is NOT commonly seen in patients with MEN1 syndrome?</t>
         </is>
       </c>
       <c r="V904" t="inlineStr">
@@ -48349,32 +48137,32 @@
     <row r="905">
       <c r="C905" t="inlineStr">
         <is>
-          <t>Glucocorticoids are produced in the</t>
+          <t>Which of the following is NOT commonly seen in patients with MEN1 syndrome?</t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
         <is>
-          <t>Zona glomerulosa</t>
+          <t>Gastrinoma</t>
         </is>
       </c>
       <c r="G905" t="inlineStr">
         <is>
-          <t>Zona fasciculate</t>
+          <t>Insulinoma</t>
         </is>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>Zona reticularis</t>
+          <t>Prolactinoma</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
         <is>
-          <t>Adrenal medulla</t>
+          <t>Pheochromocytoma</t>
         </is>
       </c>
       <c r="R905" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V905" t="inlineStr">
@@ -48401,27 +48189,27 @@
     <row r="906">
       <c r="C906" t="inlineStr">
         <is>
-          <t>The paired lateral thyroid anlages fuse with the median thyroid anlage in the 5th week of gestation. These paired lateral anlages originate from</t>
+          <t>Painful subacute thyroiditis</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
         <is>
-          <t>Ectoderm</t>
+          <t>Results in hypothyroidism in &gt;80% of patients</t>
         </is>
       </c>
       <c r="G906" t="inlineStr">
         <is>
-          <t>Mesoderm</t>
+          <t>Occurs most commonly in women &gt;70 years of age</t>
         </is>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>Endoderm</t>
+          <t>Is often preceded by an upper respiratory tract infection</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
         <is>
-          <t>Neural crest</t>
+          <t>Requires thyroidectomy for relief of symptoms in &gt;50% of patients</t>
         </is>
       </c>
       <c r="R906" t="inlineStr">
@@ -48453,32 +48241,37 @@
     <row r="907">
       <c r="C907" t="inlineStr">
         <is>
-          <t>Cholesterol is the precursor of all hormones produced in the adrenal gland. The first step in the synthesis of all adrenal hormones is to cleave cholesterol to produce</t>
+          <t>Which of the following tests has the highest sensitivity in localizing parathyroid adenomas?</t>
         </is>
       </c>
       <c r="F907" t="inlineStr">
         <is>
-          <t>Progesterone</t>
+          <t>Ultrasound</t>
         </is>
       </c>
       <c r="G907" t="inlineStr">
         <is>
-          <t>Pregnenolone</t>
+          <t>Fine cut CT scan</t>
         </is>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>17α-hydroxypregnenolone</t>
+          <t>PET scan</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
         <is>
-          <t>11-deoxy-corticosterone</t>
+          <t>Sestamibi scan</t>
         </is>
       </c>
       <c r="R907" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T907" t="inlineStr">
+        <is>
+          <t>Pheochromocytomas are seen in patients with MEN2 syn- drome.PHPTis the earliest and most common manifesta- tion of MEN1 59 and develops in 80 to 100% of patients by age 40 years old. These patients also are prone to pancreatic neu- roendocrine tumors and pituitary adenomas and, less com- monly, to adrenocortical tumors, lipomas, skin angiomas, and carcinoid tumors of the bronchus, thymus, or stomach. About 50% of patients develop gastrinomas, which often are multiple and metastatic at diagnosis. Insulinomas develop in 10 to 15% of cases, whereas many patients have nonfunctional pancre- atic endocrine tumors. Prolactinomas occur in 10 to 50% of CHAPTER 38 MEN1 patients and constitute the most common pituitary le- sion. (See Schwartz 9thed., p 1377.) Painful thyroiditis most commonly occurs in 30- to 40-year-old women and is characterized by the sudden or gradual onset of neck pain, which may radiate toward the mandible or ear. History of a preceding upper respiratory tract infection often can be elicited. The gland is enlarged, exquisitely tender, and firm. The disorder classically progresses through four stages. An initial hyperthyroid phase, due to release of thyroid hor- Thyroid, Parathyroid, and Adrenal mone, is followed by a second, euthyroid phase. The third phase, hypothyroidism, occurs in about 20 to 30% of patients and is followed by resolution and return to the euthyroid state in &gt;90% of patients. A few patients develop recurrent disease. Painful thyroiditis is self-limited, and therefore, treatment is primarily symptomatic. Aspirin and other NSAIDs are used for pain relief, but steroids may be indicated in more severe cases. Short-term thyroid replacement may be needed and may shorten the duration of symptoms. Thyroidectomy is reserved for the rare patient who has a prolonged course not responsive to medical measures or for recurrent disease. (See Schwartz 9th ed., p 1356.) 99mTc-labeled sestamibi is the most widely used and accurate modality with a sensitivity &gt;80% for detection of parathyroid adenomas. Sestamibi (Cardiolite) initially was introduced for cardiac imaging and is concentrated in mitochondria-rich tissue. It was subsequently noted to be useful for parathyroid localization due to the delayed washout of the radionuclide from hypercellular parathyroid tissue compared to thyroid tissue. Sestamibi scans generally are complemented by neck ultrasound, which can identify adenomas with &gt;75% sensi- tivity in experienced centers, and are most useful in identi- fying intrathyroidalparathyroids. Single-photon emission computed tomography, particularly when used with CT, has been shown to be superior to other nuclear medicine-based imaging. Specifically, single-photon emission computed to- mography can indicate whether an adenoma is located in the anterior or posterior mediastinum (aortopulmonary win- dow), thus enabling the surgeon to modify the operative ap- proach accordingly. CT and MRI scans are less sensitive than sestamibi scans, but are helpful in localizing large paraesoph- ageal and mediastinal glands. (See Schwartz 9th ed., p 1381.)</t>
         </is>
       </c>
       <c r="V907" t="inlineStr">
@@ -48505,37 +48298,32 @@
     <row r="908">
       <c r="C908" t="inlineStr">
         <is>
-          <t>Propylthiouracil</t>
+          <t>Which of the following drugs can cause thyroid storm in patients with hyperthyroidism?</t>
         </is>
       </c>
       <c r="F908" t="inlineStr">
         <is>
-          <t>Can be given once a day in patients with hyperthyroidism</t>
+          <t>Amiodarone</t>
         </is>
       </c>
       <c r="G908" t="inlineStr">
         <is>
-          <t>Can cause agranulocytosis</t>
+          <t>Labetalol</t>
         </is>
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>Does not affect the peripheral conversion of T4 to T3</t>
+          <t>Corticosteroids</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
         <is>
-          <t>Does not cross the placenta</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="R908" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="T908" t="inlineStr">
-        <is>
-          <t>Antithyroid medications generally are administered in prepa- ration for RAI ablation or surgery. The drugs commonly used are propylthiouracil (PTU, 100 to 300 mg three times daily) and methimazole (10 to 30 mg three times daily, then once daily). Methimazole has a longer half-life and can be dosed once daily. Both drugs reduce thyroid hormone production by inhibiting the organic binding of iodine and the coupling of iodotyrosines (mediated by TPO). In addition, PTU also in- hibits the peripheral conversion of T4 to Tz, making it useful for the treatment of thyroid storm. Both drugs can cross the placenta, inhibiting fetal thyroid function, and are excreted in breast milk, although PTU has a lower risk of transplacental transfer. Methimazole also has been associated with congeni- tal aplasia; therefore, PTU is preferred in pregnant and breast- feeding women. Side effects of treatment include reversible granulocytopenia, skin rashes, fever, peripheral neuritis, pol- yarteritis, vasculitis, and, rarely, agranulocytosis and aplastic anemia. Patients should be monitored for these possible com- plications and should always be warned to stop PTU or me- thimazole immediately and seek medical advice should they develop a sore throat or fever. Treatment of agranulocytosis in- volves admission to the hospital, discontinuation of the drug, and broad-spectrum antibiotic therapy. Surgery should be postponed until the granulocyte count reaches 1000 cells/m3. (See Schwartz 9thed., p1354.) Which of the following is NOT commonly seen in patients with MEN1 syndrome?</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V908" t="inlineStr">
@@ -48562,32 +48350,32 @@
     <row r="909">
       <c r="C909" t="inlineStr">
         <is>
-          <t>Which of the following is NOT commonly seen in patients with MEN1 syndrome?</t>
+          <t>In patients with elevated thyroglobulin after total thyroidectomy for thyroid cancer, many physicians recommend a dose of 100 mCi of ¹³¹I. Which of the following is a reported complication of this treatment?</t>
         </is>
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>Gastrinoma</t>
+          <t>Sialadenitis</t>
         </is>
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>Insulinoma</t>
+          <t>Cerebral edema</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>Prolactinoma</t>
+          <t>Bone marrow suppression</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
         <is>
-          <t>Pheochromocytoma</t>
+          <t>Vocal cord paralysis</t>
         </is>
       </c>
       <c r="R909" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V909" t="inlineStr">
@@ -48614,32 +48402,32 @@
     <row r="910">
       <c r="C910" t="inlineStr">
         <is>
-          <t>Painful subacute thyroiditis</t>
+          <t>Surgery is indicated in which of the following asymptomatic patients with primary hyperparathyroidism?</t>
         </is>
       </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t>Results in hypothyroidism in &gt;80% of patients</t>
+          <t>Mildly elevated urinary calcium excretion (&gt;100 mg/dl)</t>
         </is>
       </c>
       <c r="G910" t="inlineStr">
         <is>
-          <t>Occurs most commonly in women &gt;70 years of age</t>
+          <t>Reduction in creatinine clearance by 10%</t>
         </is>
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>Is often preceded by an upper respiratory tract infection</t>
+          <t>Serum calcium &gt;0.8 above the upper limits of normal</t>
         </is>
       </c>
       <c r="I910" t="inlineStr">
         <is>
-          <t>Requires thyroidectomy for relief of symptoms in &gt;50% of patients</t>
+          <t>Age &lt;50 years</t>
         </is>
       </c>
       <c r="R910" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V910" t="inlineStr">
@@ -48666,37 +48454,32 @@
     <row r="911">
       <c r="C911" t="inlineStr">
         <is>
-          <t>Which of the following tests has the highest sensitivity in localizing parathyroid adenomas?</t>
+          <t>A patient with a 1-cm medullary carcinoma of the right thyroid and no clinically significant adenopathy is best treated with</t>
         </is>
       </c>
       <c r="F911" t="inlineStr">
         <is>
-          <t>Ultrasound</t>
+          <t>Right thyroid lobectomy and isthmusectomy</t>
         </is>
       </c>
       <c r="G911" t="inlineStr">
         <is>
-          <t>Fine cut CT scan</t>
+          <t>Right thyroid lobectomy and subtotal left thyroidectomy</t>
         </is>
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>PET scan</t>
+          <t>Total thyroidectomy</t>
         </is>
       </c>
       <c r="I911" t="inlineStr">
         <is>
-          <t>Sestamibi scan</t>
+          <t>Total thyroidectomy with central lymph node dissection</t>
         </is>
       </c>
       <c r="R911" t="inlineStr">
         <is>
           <t>D</t>
-        </is>
-      </c>
-      <c r="T911" t="inlineStr">
-        <is>
-          <t>Pheochromocytomas are seen in patients with MEN2 syn- drome.PHPTis the earliest and most common manifesta- tion of MEN1 59 and develops in 80 to 100% of patients by age 40 years old. These patients also are prone to pancreatic neu- roendocrine tumors and pituitary adenomas and, less com- monly, to adrenocortical tumors, lipomas, skin angiomas, and carcinoid tumors of the bronchus, thymus, or stomach. About 50% of patients develop gastrinomas, which often are multiple and metastatic at diagnosis. Insulinomas develop in 10 to 15% of cases, whereas many patients have nonfunctional pancre- atic endocrine tumors. Prolactinomas occur in 10 to 50% of CHAPTER 38 MEN1 patients and constitute the most common pituitary le- sion. (See Schwartz 9thed., p 1377.) Painful thyroiditis most commonly occurs in 30- to 40-year-old women and is characterized by the sudden or gradual onset of neck pain, which may radiate toward the mandible or ear. History of a preceding upper respiratory tract infection often can be elicited. The gland is enlarged, exquisitely tender, and firm. The disorder classically progresses through four stages. An initial hyperthyroid phase, due to release of thyroid hor- Thyroid, Parathyroid, and Adrenal mone, is followed by a second, euthyroid phase. The third phase, hypothyroidism, occurs in about 20 to 30% of patients and is followed by resolution and return to the euthyroid state in &gt;90% of patients. A few patients develop recurrent disease. Painful thyroiditis is self-limited, and therefore, treatment is primarily symptomatic. Aspirin and other NSAIDs are used for pain relief, but steroids may be indicated in more severe cases. Short-term thyroid replacement may be needed and may shorten the duration of symptoms. Thyroidectomy is reserved for the rare patient who has a prolonged course not responsive to medical measures or for recurrent disease. (See Schwartz 9th ed., p 1356.) 99mTc-labeled sestamibi is the most widely used and accurate modality with a sensitivity &gt;80% for detection of parathyroid adenomas. Sestamibi (Cardiolite) initially was introduced for cardiac imaging and is concentrated in mitochondria-rich tissue. It was subsequently noted to be useful for parathyroid localization due to the delayed washout of the radionuclide from hypercellular parathyroid tissue compared to thyroid tissue. Sestamibi scans generally are complemented by neck ultrasound, which can identify adenomas with &gt;75% sensi- tivity in experienced centers, and are most useful in identi- fying intrathyroidalparathyroids. Single-photon emission computed tomography, particularly when used with CT, has been shown to be superior to other nuclear medicine-based imaging. Specifically, single-photon emission computed to- mography can indicate whether an adenoma is located in the anterior or posterior mediastinum (aortopulmonary win- dow), thus enabling the surgeon to modify the operative ap- proach accordingly. CT and MRI scans are less sensitive than sestamibi scans, but are helpful in localizing large paraesoph- ageal and mediastinal glands. (See Schwartz 9th ed., p 1381.)</t>
         </is>
       </c>
       <c r="V911" t="inlineStr">
@@ -48723,27 +48506,27 @@
     <row r="912">
       <c r="C912" t="inlineStr">
         <is>
-          <t>Which of the following drugs can cause thyroid storm in patients with hyperthyroidism?</t>
+          <t>The most common cause of primary hyperparathyroidism is</t>
         </is>
       </c>
       <c r="F912" t="inlineStr">
         <is>
-          <t>Amiodarone</t>
+          <t>Parathyroid adenoma</t>
         </is>
       </c>
       <c r="G912" t="inlineStr">
         <is>
-          <t>Labetalol</t>
+          <t>Multiple parathyroid adenomas</t>
         </is>
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>Corticosteroids</t>
+          <t>Parathyroid hyperplasia</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Parathyroid carcinoma</t>
         </is>
       </c>
       <c r="R912" t="inlineStr">
@@ -48768,39 +48551,39 @@
       </c>
       <c r="AC912" t="inlineStr">
         <is>
-          <t>External, Schwartz</t>
+          <t>External, Schwartz, Exams, End 2024</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="C913" t="inlineStr">
         <is>
-          <t>In patients with elevated thyroglobulin after total thyroidectomy for thyroid cancer, many physicians recommend a dose of 100 mCi of ¹³¹I. Which of the following is a reported complication of this treatment?</t>
+          <t>Which of the following can be seen in the ophthalmopathy of Graves' disease?</t>
         </is>
       </c>
       <c r="F913" t="inlineStr">
         <is>
-          <t>Sialadenitis</t>
+          <t>Chemosis</t>
         </is>
       </c>
       <c r="G913" t="inlineStr">
         <is>
-          <t>Cerebral edema</t>
+          <t>Proptosis</t>
         </is>
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t>Bone marrow suppression</t>
+          <t>Blindness</t>
         </is>
       </c>
       <c r="I913" t="inlineStr">
         <is>
-          <t>Vocal cord paralysis</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="R913" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V913" t="inlineStr">
@@ -48827,32 +48610,32 @@
     <row r="914">
       <c r="C914" t="inlineStr">
         <is>
-          <t>Surgery is indicated in which of the following asymptomatic patients with primary hyperparathyroidism?</t>
+          <t>Papillary cancer of the thyroid</t>
         </is>
       </c>
       <c r="F914" t="inlineStr">
         <is>
-          <t>Mildly elevated urinary calcium excretion (&gt;100 mg/dl)</t>
+          <t>Is uncommon in children</t>
         </is>
       </c>
       <c r="G914" t="inlineStr">
         <is>
-          <t>Reduction in creatinine clearance by 10%</t>
+          <t>Is the most common thyroid cancer in patients with a history of external radiation</t>
         </is>
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>Serum calcium &gt;0.8 above the upper limits of normal</t>
+          <t>Occurs more commonly in men</t>
         </is>
       </c>
       <c r="I914" t="inlineStr">
         <is>
-          <t>Age &lt;50 years</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="R914" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V914" t="inlineStr">
@@ -48879,32 +48662,37 @@
     <row r="915">
       <c r="C915" t="inlineStr">
         <is>
-          <t>A patient with a 1-cm medullary carcinoma of the right thyroid and no clinically significant adenopathy is best treated with</t>
+          <t>There are 7 compartments of lymph nodes in the neck. Metastases from thyroid cancer are uncommon in</t>
         </is>
       </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t>Right thyroid lobectomy and isthmusectomy</t>
+          <t>Level I nodes</t>
         </is>
       </c>
       <c r="G915" t="inlineStr">
         <is>
-          <t>Right thyroid lobectomy and subtotal left thyroidectomy</t>
+          <t>Level III nodes</t>
         </is>
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>Total thyroidectomy</t>
+          <t>Level V nodes</t>
         </is>
       </c>
       <c r="I915" t="inlineStr">
         <is>
-          <t>Total thyroidectomy with central lymph node dissection</t>
+          <t>Level VII nodes</t>
         </is>
       </c>
       <c r="R915" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T915" t="inlineStr">
+        <is>
+          <t>Total thyroidectomy is the treatment of choice for patients with MTC because of the high incidence of multicentricity the more aggressive course, and the fact that131I therapy usu- ally is not effective. Central compartment nodes frequently are involved early in the disease process, so that a bilateral cen- tral neck node dissection should be routinely performed. In patients with palpable cervical nodes or involved central neck nodes, ipsilateral or bilateral, modified radical neck dissection is recommended. (See Schwartz 9thed., p 1368.) PHPT results from the enlargement of a single gland or parathyroid adenoma in approximately 80% of cases, mul- tiple adenomas or hyperplasia in 15 to 20% of patients, and parathyroid carcinoma in 1% of patients. (See Schwartz 9th ed., p 1377.) Approximately 50% of patients with Graves' disease develop clinically evident ophthalmopathy. Eye symptoms include lid lag (von Graefe's sign), spasm of the upper eyelid revealing the sclera above the corneoscleral limbus (Dalrymple's sign), and a prominent stare, due to catecholamine excess. True in- filtrative eye disease results in periorbital edema, conjunctival swelling and congestion (chemosis), proptosis, limitation of upward and lateral gaze (from involvement of the inferior and medial rectus muscles, respectively), keratitis, and even blind- ness due to optic nerve involvement. The etiology of Graves' ophthalmopathy is not completely known; however, orbital fibroblasts and muscles are thought to share a common an- tigen, the TSHR. Ophthalmopathy is thought to result from inflammation caused by cytokines released from sensitized killer T lymphocytes and cytotoxic antibodies. (See Schwartz 9th ed., p 1353.) Papillary carcinoma accounts for 80% of all thyroid malignan- cies in iodine-sufficient areas and is the predominant thyroid cancer in children and individuals exposed to external radia- tion. Papillary carcinoma occurs more often in women, with a 2:1 female-to-male ratio, and the mean age at presentation is 30 to 40 years. (See Schwartz 9th ed., p 1362.) The thyroid gland is endowed with an extensive network of lymphatics. Intraglandular lymphatic vessels connect both thy- roid lobes through the isthmus and also drain to perithyroidal structures and lymph nodes. Regional lymph nodes include pretracheal, paratracheal, perithyroidal, RLN, superior medi- astinal, retropharyngeal, esophageal, and upper, middle, and lower jugular chain nodes. These lymph nodes can be classified into seven levels as depicted in Fig. 38-6. The central compart- ment includes nodes located in the area between the two carotid sheaths, whereas nodes lateral to the vessels are present in the lateral compartment. Thyroid cancers may metastasize to any of these regions, although metastases to submaxillary nodes (level I) are rare (&lt;1%). There also can be 'skip' metastases to nodes in the ipsilateral neck. (See Schwartz 9th ed., p 1347.) External jugular node Sternocleido- mastoid m. Spinal accessory n. Jugulodigastric node Deep lateral nodes Intercalated node Transverse cervical chain of nodes A Upper jugular nodes Trapezius m. Sternocleidomastoid m. Posterior triangle FG.38-6. A and B. Lymph nodes in e neck can be divided into six regions. evelVIl. m. = muscle; n. = nerve. oper mediastinal nodes constitute B 14 A patient with hypertension is diagnosed with hyperaldos- Answer:C teronism. A CT scan shows bilaterally enlarged adrenals If adrenal hyperplasia is suspected, the algorithm depicted in without a mass. The most appropriate next intervention is Fig. 38-7 is useful. Selective venous catheterization and adre</t>
         </is>
       </c>
       <c r="V915" t="inlineStr">
@@ -48931,32 +48719,32 @@
     <row r="916">
       <c r="C916" t="inlineStr">
         <is>
-          <t>The most common cause of primary hyperparathyroidism is</t>
+          <t>A patient with hypertension is diagnosed with hyperaldosteronism. A CT scan shows bilaterally enlarged adrenals without a mass. The most appropriate next intervention is</t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t>Parathyroid adenoma</t>
+          <t>Unilateral adrenalectomy</t>
         </is>
       </c>
       <c r="G916" t="inlineStr">
         <is>
-          <t>Multiple parathyroid adenomas</t>
+          <t>Bilateral adrenalectomy</t>
         </is>
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>Parathyroid hyperplasia</t>
+          <t>Selective venous catheterization</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
         <is>
-          <t>Parathyroid carcinoma</t>
+          <t>Medical management</t>
         </is>
       </c>
       <c r="R916" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V916" t="inlineStr">
@@ -48976,34 +48764,34 @@
       </c>
       <c r="AC916" t="inlineStr">
         <is>
-          <t>External, Schwartz, Exams, End 2024</t>
+          <t>External, Schwartz</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="C917" t="inlineStr">
         <is>
-          <t>Which of the following can be seen in the ophthalmopathy of Graves' disease?</t>
+          <t>Papillary thyroid cancer of the clear cell variant is associated with</t>
         </is>
       </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t>Chemosis</t>
+          <t>Cowden's syndrome</t>
         </is>
       </c>
       <c r="G917" t="inlineStr">
         <is>
-          <t>Proptosis</t>
+          <t>Familial adenomatous polyposis</t>
         </is>
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>Blindness</t>
+          <t>Werner's syndrome</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>McCune-Albright syndrome</t>
         </is>
       </c>
       <c r="R917" t="inlineStr">
@@ -49035,32 +48823,37 @@
     <row r="918">
       <c r="C918" t="inlineStr">
         <is>
-          <t>Papillary cancer of the thyroid</t>
+          <t>The initial treatment of choice for Riedel's thyroiditis is</t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t>Is uncommon in children</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="G918" t="inlineStr">
         <is>
-          <t>Is the most common thyroid cancer in patients with a history of external radiation</t>
+          <t>Antibiotics</t>
         </is>
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>Occurs more commonly in men</t>
+          <t>Corticosteroids</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="R918" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T918" t="inlineStr">
+        <is>
+          <t>Nonmedullary thyroid cancers can occur in association with other known familial cancer syndromes such as Cowden's syndrome, Werner's (adult progeroid syndrome), and famil- ial adenomatous polyposis (Table 38-7 See Schwartz 9th ed., p1360.) Thyroid Tumor FTC, rarely PTC and Hürthle cell tumors PTC cribriform growth pattern PTC, FTC, anaplastic cancer PTC, FTC PTC clear cell 6 The initial treatment of choice for Riedel's thyroiditis is</t>
         </is>
       </c>
       <c r="V918" t="inlineStr">
@@ -49087,37 +48880,32 @@
     <row r="919">
       <c r="C919" t="inlineStr">
         <is>
-          <t>There are 7 compartments of lymph nodes in the neck. Metastases from thyroid cancer are uncommon in</t>
+          <t>Which of the following should be the first drug to be started in a patient with a symptomatic pheochromocytoma?</t>
         </is>
       </c>
       <c r="F919" t="inlineStr">
         <is>
-          <t>Level I nodes</t>
+          <t>ACE inhibitor</t>
         </is>
       </c>
       <c r="G919" t="inlineStr">
         <is>
-          <t>Level III nodes</t>
+          <t>Alpha blocker</t>
         </is>
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>Level V nodes</t>
+          <t>Beta blocker</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
         <is>
-          <t>Level VII nodes</t>
+          <t>Calcium channel blocker</t>
         </is>
       </c>
       <c r="R919" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="T919" t="inlineStr">
-        <is>
-          <t>Total thyroidectomy is the treatment of choice for patients with MTC because of the high incidence of multicentricity the more aggressive course, and the fact that131I therapy usu- ally is not effective. Central compartment nodes frequently are involved early in the disease process, so that a bilateral cen- tral neck node dissection should be routinely performed. In patients with palpable cervical nodes or involved central neck nodes, ipsilateral or bilateral, modified radical neck dissection is recommended. (See Schwartz 9thed., p 1368.) PHPT results from the enlargement of a single gland or parathyroid adenoma in approximately 80% of cases, mul- tiple adenomas or hyperplasia in 15 to 20% of patients, and parathyroid carcinoma in 1% of patients. (See Schwartz 9th ed., p 1377.) Approximately 50% of patients with Graves' disease develop clinically evident ophthalmopathy. Eye symptoms include lid lag (von Graefe's sign), spasm of the upper eyelid revealing the sclera above the corneoscleral limbus (Dalrymple's sign), and a prominent stare, due to catecholamine excess. True in- filtrative eye disease results in periorbital edema, conjunctival swelling and congestion (chemosis), proptosis, limitation of upward and lateral gaze (from involvement of the inferior and medial rectus muscles, respectively), keratitis, and even blind- ness due to optic nerve involvement. The etiology of Graves' ophthalmopathy is not completely known; however, orbital fibroblasts and muscles are thought to share a common an- tigen, the TSHR. Ophthalmopathy is thought to result from inflammation caused by cytokines released from sensitized killer T lymphocytes and cytotoxic antibodies. (See Schwartz 9th ed., p 1353.) Papillary carcinoma accounts for 80% of all thyroid malignan- cies in iodine-sufficient areas and is the predominant thyroid cancer in children and individuals exposed to external radia- tion. Papillary carcinoma occurs more often in women, with a 2:1 female-to-male ratio, and the mean age at presentation is 30 to 40 years. (See Schwartz 9th ed., p 1362.) The thyroid gland is endowed with an extensive network of lymphatics. Intraglandular lymphatic vessels connect both thy- roid lobes through the isthmus and also drain to perithyroidal structures and lymph nodes. Regional lymph nodes include pretracheal, paratracheal, perithyroidal, RLN, superior medi- astinal, retropharyngeal, esophageal, and upper, middle, and lower jugular chain nodes. These lymph nodes can be classified into seven levels as depicted in Fig. 38-6. The central compart- ment includes nodes located in the area between the two carotid sheaths, whereas nodes lateral to the vessels are present in the lateral compartment. Thyroid cancers may metastasize to any of these regions, although metastases to submaxillary nodes (level I) are rare (&lt;1%). There also can be 'skip' metastases to nodes in the ipsilateral neck. (See Schwartz 9th ed., p 1347.) External jugular node Sternocleido- mastoid m. Spinal accessory n. Jugulodigastric node Deep lateral nodes Intercalated node Transverse cervical chain of nodes A Upper jugular nodes Trapezius m. Sternocleidomastoid m. Posterior triangle FG.38-6. A and B. Lymph nodes in e neck can be divided into six regions. evelVIl. m. = muscle; n. = nerve. oper mediastinal nodes constitute B 14 A patient with hypertension is diagnosed with hyperaldos- Answer:C teronism. A CT scan shows bilaterally enlarged adrenals If adrenal hyperplasia is suspected, the algorithm depicted in without a mass. The most appropriate next intervention is Fig. 38-7 is useful. Selective venous catheterization and adre</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V919" t="inlineStr">
@@ -49144,32 +48932,32 @@
     <row r="920">
       <c r="C920" t="inlineStr">
         <is>
-          <t>A patient with hypertension is diagnosed with hyperaldosteronism. A CT scan shows bilaterally enlarged adrenals without a mass. The most appropriate next intervention is</t>
+          <t>Following a total thyroidectomy for differentiated thyroid cancer, radioactive iodine ablation would be offered for all of the following patients EXCEPT</t>
         </is>
       </c>
       <c r="F920" t="inlineStr">
         <is>
-          <t>Unilateral adrenalectomy</t>
+          <t>Stage III disease</t>
         </is>
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>Bilateral adrenalectomy</t>
+          <t>Stage II disease &lt;45 years of age</t>
         </is>
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>Selective venous catheterization</t>
+          <t>Stage 1 disease with multifocal disease</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
         <is>
-          <t>Medical management</t>
+          <t>Stage 1 disease &lt;45 years of age</t>
         </is>
       </c>
       <c r="R920" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V920" t="inlineStr">
@@ -49196,32 +48984,37 @@
     <row r="921">
       <c r="C921" t="inlineStr">
         <is>
-          <t>Papillary thyroid cancer of the clear cell variant is associated with</t>
+          <t>Which of the following organisms is a common cause of acute (suppurative) thyroiditis?</t>
         </is>
       </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t>Cowden's syndrome</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>Familial adenomatous polyposis</t>
+          <t>Pseudomonas aeruginous</t>
         </is>
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>Werner's syndrome</t>
+          <t>Streptococcus species</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
         <is>
-          <t>McCune-Albright syndrome</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="R921" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T921" t="inlineStr">
+        <is>
+          <t>Riedel's thyroiditis is a rare variant of thyroiditis also known as Riedel's struma or invasive fibrous thyroiditis that is character- ized by the replacement of all or part of the thyroid parenchy- ma by fibrous tissue, which also invades into adjacent tissues. Surgery is the mainstay of the treatment for Riedel's thy- roiditis. The chief goal of operation is to decompress the tra- chea by wedge excision of the thyroid isthmus and to make a tissue diagnosis. More extensive resections are not advised due to the infiltrative nature of the fibrotic process that ob- scures usual landmarks and structures. Hypothyroid patients are treated with thyroid hormone replacement. Some patients CHAPTER 38 who remain symptomatic have been reported to experience dramatic improvement after treatment with corticosteroids and tamoxifen. (See Schwartz 9thed., p 1357.) Alpha blockers such as phenoxybenzamine are started 1 to 3 weeks before surgery at doses of 10 mg twice daily, which may be increased to 300 to 400 mg/d with rehydration. Patients should be warned about orthostatic hypotension. Other alpha blockers such as prazosin and other classes of drugs such as ACE inhibitors and calcium channel blockers are also useful. Thyroid, Parathyroid, and Adrenal Beta blockers such as propranolol at doses of 10 to 40 mg every 6 to 8 hours often need to be added preoperatively in patients who have persistent tachycardia and arrhythmias. Beta block- ers should only be instituted after adequate alpha blockade and hydration to avoid the effects of unopposed alpha stimulation, (i.e., hypertensive crisis and congestive heart failure). Patients also should be volume repleted preoperatively to avoid post- operative hypotension, which ensues with the loss of vasocon- striction after tumor removal. (See Schwartz 9th ed., p 1399.) RAI ablation currently is recommended for allpatients with stage III or IV disease, all patients with stage II disease younger than 45 years old, most patients 45 years or older with stage II disease, and patients with stage I disease who have aggres- sive histologies, nodal metastases, multifocal disease, and ex- trathyroid or vascular invasion. (See Schwartz 9th ed., p 1365.) The thyroid gland is inherently resistant to infection due to its extensive blood and lymphatic supply, high iodide content, and fibrous capsule. However, infectious agents can seed it (a) via the hematogenous or lymphatic route, (b) via direct spread from persistent pyriform sinus fistu- lae or thyroglossal duct cysts, (c) as a result of penetrating trauma to the thyroid gland, or (d) due to immunosuppres- sion. Streptococcus and anaerobes account for about 70% of cases; however, other species also have been cultured. Acute suppurative thyroiditis is more common in children and often is preceded by an upper respiratory tract infec- tion or otitis media. It is characterized by severe neck pain radiating to the jaws or ear, fever, chills, odynophagia, and dysphonia. Complications such as systemic sepsis, tracheal or esophageal rupture, jugular vein thrombosis, laryngeal chondritis, and perichondritis or sympathetic trunk paral- ysis may also occur. (See Schwartz 9th ed., p 1356.) 20. Thyroidectomy should be recommended for patients with Graves' disease who</t>
         </is>
       </c>
       <c r="V921" t="inlineStr">
@@ -49248,37 +49041,32 @@
     <row r="922">
       <c r="C922" t="inlineStr">
         <is>
-          <t>The initial treatment of choice for Riedel's thyroiditis is</t>
+          <t>Thyroidectomy should be recommended for patients with Graves' disease who</t>
         </is>
       </c>
       <c r="F922" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Are of the male gender</t>
         </is>
       </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>Antibiotics</t>
+          <t>Are &gt;55 years of age</t>
         </is>
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>Corticosteroids</t>
+          <t>Have large asymptomatic goiters</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>Have a suspicious thyroid nodule</t>
         </is>
       </c>
       <c r="R922" t="inlineStr">
         <is>
           <t>D</t>
-        </is>
-      </c>
-      <c r="T922" t="inlineStr">
-        <is>
-          <t>Nonmedullary thyroid cancers can occur in association with other known familial cancer syndromes such as Cowden's syndrome, Werner's (adult progeroid syndrome), and famil- ial adenomatous polyposis (Table 38-7 See Schwartz 9th ed., p1360.) Thyroid Tumor FTC, rarely PTC and Hürthle cell tumors PTC cribriform growth pattern PTC, FTC, anaplastic cancer PTC, FTC PTC clear cell 6 The initial treatment of choice for Riedel's thyroiditis is</t>
         </is>
       </c>
       <c r="V922" t="inlineStr">
@@ -49305,32 +49093,32 @@
     <row r="923">
       <c r="C923" t="inlineStr">
         <is>
-          <t>Which of the following should be the first drug to be started in a patient with a symptomatic pheochromocytoma?</t>
+          <t>Which of the following is an indication for surgery in patients with secondary hyperparathyroidism?</t>
         </is>
       </c>
       <c r="F923" t="inlineStr">
         <is>
-          <t>ACE inhibitor</t>
+          <t>Calciphylaxis</t>
         </is>
       </c>
       <c r="G923" t="inlineStr">
         <is>
-          <t>Alpha blocker</t>
+          <t>PTH&gt;250</t>
         </is>
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>Beta blocker</t>
+          <t>Progressive renal failure</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
         <is>
-          <t>Calcium channel blocker</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="R923" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V923" t="inlineStr">
@@ -49357,32 +49145,37 @@
     <row r="924">
       <c r="C924" t="inlineStr">
         <is>
-          <t>Following a total thyroidectomy for differentiated thyroid cancer, radioactive iodine ablation would be offered for all of the following patients EXCEPT</t>
+          <t>Thyroglossal duct cysts are most commonly located</t>
         </is>
       </c>
       <c r="F924" t="inlineStr">
         <is>
-          <t>Stage III disease</t>
+          <t>On the anterior border of the sternocleidomastoid muscle</t>
         </is>
       </c>
       <c r="G924" t="inlineStr">
         <is>
-          <t>Stage II disease &lt;45 years of age</t>
+          <t>In the midline at the level of the hyoid</t>
         </is>
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>Stage 1 disease with multifocal disease</t>
+          <t>Over the medial clavicular head</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
         <is>
-          <t>Stage 1 disease &lt;45 years of age</t>
+          <t>In the midline just superior to the thyroid gland</t>
         </is>
       </c>
       <c r="R924" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T924" t="inlineStr">
+        <is>
+          <t>In North America, surgery is recommended when RAI is con- traindicated as in patients who (a) have confirmed cancer or suspicious thyroid nodules, (b) are young, (c) are pregnant or desire to conceive soon after treatment, (d) have had severe reactions to antithyroid medications, (e) have large goiters causing compressive symptoms, and (f) are reluctant to un- dergo RAI therapy. Relative indications for thyroidectomy include patients, particularly smokers, with moderate to se- vere Graves' ophthalmopathy, those desiring rapid control of hyperthyroidism with a chance of being euthyroid, and those demonstrating poor compliance to antithyroid medications. (See Schwartz 9thed., p 1355.) Surgical treatment in secondary hyperparathyroidism was traditionally recommended for patients with bone pain, pru- ritus, and (a) a calcium-phosphate product ≥70, (b) calcium &gt;11 mg/dL with markedly elevated PTH, (c) calciphylaxis, (d) progressive renal osteodystrophy, and Thyroglossal duct cysts are the most commonly encountered congenital cervical anomalies. During the fifth week of gesta- tion, the thyroglossal duct lumen starts to obliterate, and the duct disappears by the eighth week of gestation. Rarely, the thyroglossal duct may persist in whole, or in part. Thyroglossa duct cysts may occur anywhere along the migratory path the thyroid although 80% are found in juxtaposition to the hyoid bone. The thyroid gland arises as an outpouching of the primitiv foregut around the third week of gestation. It originates at the base of the tongue at the foramen cecum. Endoderm cells i the floor of the pharyngeal anlage thicken to form the media thyroid anlage (Fig. 38-8) that descends in the neck anterior structures that form the hyoid bone and larynx. During its d scent, the anlage remains connected to the foramen cecum an epithelial-lined tube known as the thyroglossal duct. (S Schwartz 9thed., p 1344.) 3rd pouch FIG. 38-8. Thyroid embryology-early development of the median thyroid anlage as a pharyngeal pouch. (Reproduced with permission from Embryology and developmental abnormalities, in Cady B, Rossi R (eds): Surgery of the Thyroid and Parathyroid Glands. Philadelphia: WB Saunders, 1991, p 6.) 23. Which of the following syndromes is NOT typically Answer: A associated with an increased risk of pheochromocytoma? Pheochromocytomas occur in families with MEN2A and</t>
         </is>
       </c>
       <c r="V924" t="inlineStr">
@@ -49409,37 +49202,32 @@
     <row r="925">
       <c r="C925" t="inlineStr">
         <is>
-          <t>Which of the following organisms is a common cause of acute (suppurative) thyroiditis?</t>
+          <t>Which of the following syndromes is NOT typically associated with an increased risk of pheochromocytoma?</t>
         </is>
       </c>
       <c r="F925" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Familial adenomatous polyposis syndrome</t>
         </is>
       </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginous</t>
+          <t>Carney's syndrome</t>
         </is>
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t>Streptococcus species</t>
+          <t>von Hippel-Lindau syndrome</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Sturge-Weber syndrome</t>
         </is>
       </c>
       <c r="R925" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="T925" t="inlineStr">
-        <is>
-          <t>Riedel's thyroiditis is a rare variant of thyroiditis also known as Riedel's struma or invasive fibrous thyroiditis that is character- ized by the replacement of all or part of the thyroid parenchy- ma by fibrous tissue, which also invades into adjacent tissues. Surgery is the mainstay of the treatment for Riedel's thy- roiditis. The chief goal of operation is to decompress the tra- chea by wedge excision of the thyroid isthmus and to make a tissue diagnosis. More extensive resections are not advised due to the infiltrative nature of the fibrotic process that ob- scures usual landmarks and structures. Hypothyroid patients are treated with thyroid hormone replacement. Some patients CHAPTER 38 who remain symptomatic have been reported to experience dramatic improvement after treatment with corticosteroids and tamoxifen. (See Schwartz 9thed., p 1357.) Alpha blockers such as phenoxybenzamine are started 1 to 3 weeks before surgery at doses of 10 mg twice daily, which may be increased to 300 to 400 mg/d with rehydration. Patients should be warned about orthostatic hypotension. Other alpha blockers such as prazosin and other classes of drugs such as ACE inhibitors and calcium channel blockers are also useful. Thyroid, Parathyroid, and Adrenal Beta blockers such as propranolol at doses of 10 to 40 mg every 6 to 8 hours often need to be added preoperatively in patients who have persistent tachycardia and arrhythmias. Beta block- ers should only be instituted after adequate alpha blockade and hydration to avoid the effects of unopposed alpha stimulation, (i.e., hypertensive crisis and congestive heart failure). Patients also should be volume repleted preoperatively to avoid post- operative hypotension, which ensues with the loss of vasocon- striction after tumor removal. (See Schwartz 9th ed., p 1399.) RAI ablation currently is recommended for allpatients with stage III or IV disease, all patients with stage II disease younger than 45 years old, most patients 45 years or older with stage II disease, and patients with stage I disease who have aggres- sive histologies, nodal metastases, multifocal disease, and ex- trathyroid or vascular invasion. (See Schwartz 9th ed., p 1365.) The thyroid gland is inherently resistant to infection due to its extensive blood and lymphatic supply, high iodide content, and fibrous capsule. However, infectious agents can seed it (a) via the hematogenous or lymphatic route, (b) via direct spread from persistent pyriform sinus fistu- lae or thyroglossal duct cysts, (c) as a result of penetrating trauma to the thyroid gland, or (d) due to immunosuppres- sion. Streptococcus and anaerobes account for about 70% of cases; however, other species also have been cultured. Acute suppurative thyroiditis is more common in children and often is preceded by an upper respiratory tract infec- tion or otitis media. It is characterized by severe neck pain radiating to the jaws or ear, fever, chills, odynophagia, and dysphonia. Complications such as systemic sepsis, tracheal or esophageal rupture, jugular vein thrombosis, laryngeal chondritis, and perichondritis or sympathetic trunk paral- ysis may also occur. (See Schwartz 9th ed., p 1356.) 20. Thyroidectomy should be recommended for patients with Graves' disease who</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V925" t="inlineStr">
@@ -49466,32 +49254,32 @@
     <row r="926">
       <c r="C926" t="inlineStr">
         <is>
-          <t>Thyroidectomy should be recommended for patients with Graves' disease who</t>
+          <t>The most common cause of hyperthyroidism is</t>
         </is>
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t>Are of the male gender</t>
+          <t>Graves' disease</t>
         </is>
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>Are &gt;55 years of age</t>
+          <t>Toxic multinodular goiter</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>Have large asymptomatic goiters</t>
+          <t>Plummer's disease</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
         <is>
-          <t>Have a suspicious thyroid nodule</t>
+          <t>Thyroiditis</t>
         </is>
       </c>
       <c r="R926" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V926" t="inlineStr">
@@ -49518,32 +49306,32 @@
     <row r="927">
       <c r="C927" t="inlineStr">
         <is>
-          <t>Which of the following is an indication for surgery in patients with secondary hyperparathyroidism?</t>
+          <t>The most common adrenal mass incidentally found on CT scan (adrenal incidentaloma) is</t>
         </is>
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t>Calciphylaxis</t>
+          <t>Adrenal cyst</t>
         </is>
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>PTH&gt;250</t>
+          <t>Adrenal hemorrhage</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>Progressive renal failure</t>
+          <t>Cortical adenoma</t>
         </is>
       </c>
       <c r="I927" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Myelolipoma</t>
         </is>
       </c>
       <c r="R927" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V927" t="inlineStr">
@@ -49570,27 +49358,27 @@
     <row r="928">
       <c r="C928" t="inlineStr">
         <is>
-          <t>Thyroglossal duct cysts are most commonly located</t>
+          <t>Which of the following would be the best initial treatment of a symptomatic lingual thyroid?</t>
         </is>
       </c>
       <c r="F928" t="inlineStr">
         <is>
-          <t>On the anterior border of the sternocleidomastoid muscle</t>
+          <t>Intravenous thyroxine</t>
         </is>
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>In the midline at the level of the hyoid</t>
+          <t>Radioactive iodine ablation</t>
         </is>
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>Over the medial clavicular head</t>
+          <t>External beam radiation</t>
         </is>
       </c>
       <c r="I928" t="inlineStr">
         <is>
-          <t>In the midline just superior to the thyroid gland</t>
+          <t>Local surgical excision</t>
         </is>
       </c>
       <c r="R928" t="inlineStr">
@@ -49600,7 +49388,7 @@
       </c>
       <c r="T928" t="inlineStr">
         <is>
-          <t>In North America, surgery is recommended when RAI is con- traindicated as in patients who (a) have confirmed cancer or suspicious thyroid nodules, (b) are young, (c) are pregnant or desire to conceive soon after treatment, (d) have had severe reactions to antithyroid medications, (e) have large goiters causing compressive symptoms, and (f) are reluctant to un- dergo RAI therapy. Relative indications for thyroidectomy include patients, particularly smokers, with moderate to se- vere Graves' ophthalmopathy, those desiring rapid control of hyperthyroidism with a chance of being euthyroid, and those demonstrating poor compliance to antithyroid medications. (See Schwartz 9thed., p 1355.) Surgical treatment in secondary hyperparathyroidism was traditionally recommended for patients with bone pain, pru- ritus, and (a) a calcium-phosphate product ≥70, (b) calcium &gt;11 mg/dL with markedly elevated PTH, (c) calciphylaxis, (d) progressive renal osteodystrophy, and Thyroglossal duct cysts are the most commonly encountered congenital cervical anomalies. During the fifth week of gesta- tion, the thyroglossal duct lumen starts to obliterate, and the duct disappears by the eighth week of gestation. Rarely, the thyroglossal duct may persist in whole, or in part. Thyroglossa duct cysts may occur anywhere along the migratory path the thyroid although 80% are found in juxtaposition to the hyoid bone. The thyroid gland arises as an outpouching of the primitiv foregut around the third week of gestation. It originates at the base of the tongue at the foramen cecum. Endoderm cells i the floor of the pharyngeal anlage thicken to form the media thyroid anlage (Fig. 38-8) that descends in the neck anterior structures that form the hyoid bone and larynx. During its d scent, the anlage remains connected to the foramen cecum an epithelial-lined tube known as the thyroglossal duct. (S Schwartz 9thed., p 1344.) 3rd pouch FIG. 38-8. Thyroid embryology-early development of the median thyroid anlage as a pharyngeal pouch. (Reproduced with permission from Embryology and developmental abnormalities, in Cady B, Rossi R (eds): Surgery of the Thyroid and Parathyroid Glands. Philadelphia: WB Saunders, 1991, p 6.) 23. Which of the following syndromes is NOT typically Answer: A associated with an increased risk of pheochromocytoma? Pheochromocytomas occur in families with MEN2A and</t>
+          <t>The differential diagnosis of adrenal incidentalomas is shown in Table 38-9. Nonfunctional cortical adenomas ac- count for the majority (36 to 94%) of adrenal incidentalo- mas in patients without a history of cancer. (See Schwartz 9th ed., p 1401.) TABLE 38-9 Differential diagnosis of adrenal incidentaloma Functioning Lesions Nonfunctioning Lesions Benign Benign Aldosteronoma Cortical adenoma Cortisol-producing adenoma Myelolipoma Sex-steroid-producing adenoma Cyst Pheochromocytoma Ganglioneuroma Hemorrhage Malignant Malignant Adrenocortical cancer Metastasis Malignant pheochromocytoma Adrenocortical cancer A lingual thyroid represents a failure of the median thyroid anlage to descend normally and may be the only thyroid tis- sue present. Intervention becomes necessary for obstructive symptoms such as choking, dysphagia, airway obstruction, or hemorrhage. Many of these patients develop hypothy- roidism. Medical treatment options include administration of exogenous oral thyroid hormone to suppress thyroid- stimulating hormone (TSH) and radioactive iodine (RAI) ablation followed by hormone replacement. Surgical exci- sion is rarely needed but, if required, should be preceded by an evaluation of normal thyroid tissue in the neck to avoid inadvertently rendering the patient hypothyroid. (See Schwartz 9thed., p 1345.) 27.A patient is noted to have an adrenal mass on CT scan. Which of the followingCT findings is most suggestive of adrenal cancer?</t>
         </is>
       </c>
       <c r="V928" t="inlineStr">
@@ -49627,32 +49415,32 @@
     <row r="929">
       <c r="C929" t="inlineStr">
         <is>
-          <t>Which of the following syndromes is NOT typically associated with an increased risk of pheochromocytoma?</t>
+          <t>A patient is noted to have an adrenal mass on CT scan. Which of the following CT findings is most suggestive of adrenal cancer?</t>
         </is>
       </c>
       <c r="F929" t="inlineStr">
         <is>
-          <t>Familial adenomatous polyposis syndrome</t>
+          <t>Tumor heterogeneity</t>
         </is>
       </c>
       <c r="G929" t="inlineStr">
         <is>
-          <t>Carney's syndrome</t>
+          <t>Adjacent lymphadenopathy</t>
         </is>
       </c>
       <c r="H929" t="inlineStr">
         <is>
-          <t>von Hippel-Lindau syndrome</t>
+          <t>Size &gt;6 cm</t>
         </is>
       </c>
       <c r="I929" t="inlineStr">
         <is>
-          <t>Sturge-Weber syndrome</t>
+          <t>Lesion enhancement</t>
         </is>
       </c>
       <c r="R929" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V929" t="inlineStr">
@@ -49679,32 +49467,32 @@
     <row r="930">
       <c r="C930" t="inlineStr">
         <is>
-          <t>The most common cause of hyperthyroidism is</t>
+          <t>The most sensitive test to diagnose a pheochromocytoma is</t>
         </is>
       </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t>Graves' disease</t>
+          <t>Plasma vanillylmandellic acid (VMA)</t>
         </is>
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>Toxic multinodular goiter</t>
+          <t>Urinary vanillylmandellic acid (VMA)</t>
         </is>
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>Plummer's disease</t>
+          <t>Plasma metanephrines</t>
         </is>
       </c>
       <c r="I930" t="inlineStr">
         <is>
-          <t>Thyroiditis</t>
+          <t>Urinary metanephrines</t>
         </is>
       </c>
       <c r="R930" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V930" t="inlineStr">
@@ -49731,32 +49519,32 @@
     <row r="931">
       <c r="C931" t="inlineStr">
         <is>
-          <t>The most common adrenal mass incidentally found on CT scan (adrenal incidentaloma) is</t>
+          <t>Thyroid hormone production is inhibited by</t>
         </is>
       </c>
       <c r="F931" t="inlineStr">
         <is>
-          <t>Adrenal cyst</t>
+          <t>Epinephrine</t>
         </is>
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>Adrenal hemorrhage</t>
+          <t>Glucocorticoids</t>
         </is>
       </c>
       <c r="H931" t="inlineStr">
         <is>
-          <t>Cortical adenoma</t>
+          <t>Human chorionic gonadotrophin</t>
         </is>
       </c>
       <c r="I931" t="inlineStr">
         <is>
-          <t>Myelolipoma</t>
+          <t>Alphafetoprotein</t>
         </is>
       </c>
       <c r="R931" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V931" t="inlineStr">
@@ -49783,37 +49571,37 @@
     <row r="932">
       <c r="C932" t="inlineStr">
         <is>
-          <t>Which of the following would be the best initial treatment of a symptomatic lingual thyroid?</t>
+          <t>Which of the following should be the first diagnostic test ordered in a patient with a solitary thyroid nodule?</t>
         </is>
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t>Intravenous thyroxine</t>
+          <t>Radioactive iodine scan</t>
         </is>
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>Radioactive iodine ablation</t>
+          <t>CT or MRI</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
         <is>
-          <t>External beam radiation</t>
+          <t>Fine needle aspiration</t>
         </is>
       </c>
       <c r="I932" t="inlineStr">
         <is>
-          <t>Local surgical excision</t>
+          <t>Core needle biopsy</t>
         </is>
       </c>
       <c r="R932" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="T932" t="inlineStr">
         <is>
-          <t>The differential diagnosis of adrenal incidentalomas is shown in Table 38-9. Nonfunctional cortical adenomas ac- count for the majority (36 to 94%) of adrenal incidentalo- mas in patients without a history of cancer. (See Schwartz 9th ed., p 1401.) TABLE 38-9 Differential diagnosis of adrenal incidentaloma Functioning Lesions Nonfunctioning Lesions Benign Benign Aldosteronoma Cortical adenoma Cortisol-producing adenoma Myelolipoma Sex-steroid-producing adenoma Cyst Pheochromocytoma Ganglioneuroma Hemorrhage Malignant Malignant Adrenocortical cancer Metastasis Malignant pheochromocytoma Adrenocortical cancer A lingual thyroid represents a failure of the median thyroid anlage to descend normally and may be the only thyroid tis- sue present. Intervention becomes necessary for obstructive symptoms such as choking, dysphagia, airway obstruction, or hemorrhage. Many of these patients develop hypothy- roidism. Medical treatment options include administration of exogenous oral thyroid hormone to suppress thyroid- stimulating hormone (TSH) and radioactive iodine (RAI) ablation followed by hormone replacement. Surgical exci- sion is rarely needed but, if required, should be preceded by an evaluation of normal thyroid tissue in the neck to avoid inadvertently rendering the patient hypothyroid. (See Schwartz 9thed., p 1345.) 27.A patient is noted to have an adrenal mass on CT scan. Which of the followingCT findings is most suggestive of adrenal cancer?</t>
+          <t>The size of the adrenal mass on imaging studies is the single most important criterion to help diagnose malignancy. In the series reported by Copeland, 92% of adrenal cancers were &gt;6 cm in diameter. The sensitivity, specificity, and like- lihood ratio of tumor size in predicting malignancy (based on Surveillance; Epidemiology, and End Results program data) was recently reported as 96%, 51%, and 2 for tumors ≥4 cm; and 90%, 78%, and 4.1 for tumors ≥6 cm. Other CT imaging characteristics suggesting malignancy include tu- mor heterogeneity, irregular margins, and the presence of hemorrhage and adjacent lymphadenopathy or liver metas- tases. Moderately bright signal intensity on Tz-weighted im- CHAPTER 38 ages (adrenal mass to liver ratio 1.2:2.8), significant lesion enhancement, and slow washout after injection of gado- linium contrast also indicate malignancy, as does evidence of local invasion into adjacent structures such as the liver, blood vessels (IVC), and distant metastases. (See Schwartz 9th ed., p 1397.) Recent studies have shown that plasma metanephrines are the most reliable tests to identify pheochromocytomas, with sen- Thyroid, Parathyroid, and Adrenal sitivity approaching 100%. Urinary metanephrines are 98% sensitive and also are high- ly specific for pheochromocytomas, whereas VMA measure- ments are slightly less sensitive and specific. False-positive VMA tests may result from ingestion of caffeine, raw fruits, or medications (α-methyldopa).Fractionated urinary cat- echolamines(norepinephrine, epinephrine, and dopamine) also are very sensitive but less specific for pheochromocy- tomas. (See Schwartz 9thed., p1399.) Epinephrine and human chorionic gonadotrophin hor- mones stimulate thyroid hormone production. Thus, el- evated thyroid hormone levels are found in pregnancy and gynecologic malignancies such as hydatidiform mole. In contrast, glucocorticoids inhibit thyroid hormone produc- tion. In severely ill patients, peripheral thyroid hormones may be reduced, without a compensatory increase in TSH levels, giving rise to the euthyroid sick syndrome. (See Schwartz 9thed., p 1348.) FNAB has become the single most important test in the evaluation of thyroid masses and can be performed with or without ultrasound guidance. (See Schwartz 9th ed., p 1360, and Fig. 38-9.) Solitary thyroid nodule FNAB a CHAPTER 38 Nondiagnostic Repeat FNAB Benign Cyst nodule Colloid Aspirate consider T4 therapy Observe Thyroid, Parathyroid, and Adrenal Reaccumulates ↓ X3 Continued growth compressive symptoms +/- FNAB Thyroidectomy FIG. 38-9. Management of a solitary thyroid nodule. a = except in patients with a history of external radiation exposure or a family history of thyroid cancer; FNAB = fine-needle aspiration biopsy; RAl = radioactive iodine; T = thyroxine. 31.Which of the following cancers does NOT occur in thy- roglossal duct cysts?</t>
         </is>
       </c>
       <c r="V932" t="inlineStr">
@@ -49840,32 +49628,37 @@
     <row r="933">
       <c r="C933" t="inlineStr">
         <is>
-          <t>A patient is noted to have an adrenal mass on CT scan. Which of the following CT findings is most suggestive of adrenal cancer?</t>
+          <t>Which of the following cancers does NOT occur in thyroglossal duct cysts?</t>
         </is>
       </c>
       <c r="F933" t="inlineStr">
         <is>
-          <t>Tumor heterogeneity</t>
+          <t>Papillary thyroid cancer</t>
         </is>
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>Adjacent lymphadenopathy</t>
+          <t>Follicular thyroid cancer</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
         <is>
-          <t>Size &gt;6 cm</t>
+          <t>Medullary thyroid cancer</t>
         </is>
       </c>
       <c r="I933" t="inlineStr">
         <is>
-          <t>Lesion enhancement</t>
+          <t>Hürthle cell cancer</t>
         </is>
       </c>
       <c r="R933" t="inlineStr">
         <is>
           <t>C</t>
+        </is>
+      </c>
+      <c r="T933" t="inlineStr">
+        <is>
+          <t>Approximately 1% of thyroglossal duct cysts are found to contain cancer, which is usually papillary (85%).The role of total thyroidectomy in this setting is controversial, but is advised in older patients with large tumors, particular- ly if there are additional thyroid nodules and evidence of cyst wall invasion or lymph node metastases. Squamous, Hürthle cell, and anaplastic cancers also have been reported but are rare. Medullary thyroid cancers (MTCs) are, how- ever, not found in thyroglossal duct cysts. (See Schwartz 9th ed., p1344.)</t>
         </is>
       </c>
       <c r="V933" t="inlineStr">
@@ -49892,37 +49685,12 @@
     <row r="934">
       <c r="C934" t="inlineStr">
         <is>
-          <t>The most sensitive test to diagnose a pheochromocytoma is</t>
-        </is>
-      </c>
-      <c r="F934" t="inlineStr">
-        <is>
-          <t>Plasma vanillylmandellic acid (VMA)</t>
-        </is>
-      </c>
-      <c r="G934" t="inlineStr">
-        <is>
-          <t>Urinary vanillylmandellic acid (VMA)</t>
-        </is>
-      </c>
-      <c r="H934" t="inlineStr">
-        <is>
-          <t>Plasma metanephrines</t>
-        </is>
-      </c>
-      <c r="I934" t="inlineStr">
-        <is>
-          <t>Urinary metanephrines</t>
-        </is>
-      </c>
-      <c r="R934" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>female lady presented with palpitation, loss of weight, anxiety 3 months duration on Examination: tremors, staring look and neck swelling [2nd 2017] a. What is the most likely diagnosis? (2marks) b. Mention other symptoms and signs that confirm the diagnosis? (3marks) c. Mention laboratory (4marks) and radiological investigations? (4marks) d. Mention lines of treatment? (5marks)</t>
         </is>
       </c>
       <c r="V934" t="inlineStr">
         <is>
-          <t>QCS</t>
+          <t>QROC</t>
         </is>
       </c>
       <c r="W934" t="inlineStr">
@@ -49937,44 +49705,24 @@
       </c>
       <c r="AC934" t="inlineStr">
         <is>
-          <t>External, Schwartz</t>
+          <t>External, Endocrine Written</t>
+        </is>
+      </c>
+      <c r="AF934" t="inlineStr">
+        <is>
+          <t>The most likely diagnosis is Graves disease causing thyrotoxicosis, given palpitations, weight loss, anxiety, tremor, stare and goitre. Other features include heat intolerance, sweating, increased appetite, frequent stools, proximal myopathy, lid retraction or lag, diffuse vascular goitre and possible thyroid bruit. Check TSH (suppressed), free T4 and T3 (raised), thyroid receptor antibodies; ECG and baseline blood count/liver tests before antithyroid medication. Ultrasound with Doppler or radionuclide uptake can characterize the gland. Treat with symptom control using a beta blocker and antithyroid medication such as carbimazole; definitive radioiodine or thyroidectomy is selected according to patient factors and local practice.</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="C935" t="inlineStr">
         <is>
-          <t>Thyroid hormone production is inhibited by</t>
-        </is>
-      </c>
-      <c r="F935" t="inlineStr">
-        <is>
-          <t>Epinephrine</t>
-        </is>
-      </c>
-      <c r="G935" t="inlineStr">
-        <is>
-          <t>Glucocorticoids</t>
-        </is>
-      </c>
-      <c r="H935" t="inlineStr">
-        <is>
-          <t>Human chorionic gonadotrophin</t>
-        </is>
-      </c>
-      <c r="I935" t="inlineStr">
-        <is>
-          <t>Alphafetoprotein</t>
-        </is>
-      </c>
-      <c r="R935" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>y female pt presented with fatigue, lethargy, hypersomnia, weight gain, cold intolerance &amp; sense of compression in the neck. On examination; pulse 56/m, Bl P 140/100 with pallor, puffiness and slow thick voice. Chest was free. She had a family history of a similar condition, but past history was irrelevant [1st 2017] a. Enumerate causes of bradycardia (2 marks) b. Enumerate causes of puffy eye lids (2 marks) c. What is your provisional diagnosis, why? (2 marks) d. How can you confirm this diagnosis? (1 mark) e. What are the types of anaemia in this case (2 marks) f. What can you find in the obstetric and gynecological history in this patient? (2 marks) g. Give 3 other signs in the hands (2 mark) h. Do you think that surgery may have a role in the treatment?(1 mark)</t>
         </is>
       </c>
       <c r="V935" t="inlineStr">
         <is>
-          <t>QCS</t>
+          <t>QROC</t>
         </is>
       </c>
       <c r="W935" t="inlineStr">
@@ -49989,49 +49737,24 @@
       </c>
       <c r="AC935" t="inlineStr">
         <is>
-          <t>External, Schwartz</t>
+          <t>External, Endocrine Written</t>
+        </is>
+      </c>
+      <c r="AF935" t="inlineStr">
+        <is>
+          <t>The likely diagnosis is primary hypothyroidism, probably autoimmune thyroiditis, with possible goitre. Bradycardia causes include hypothyroidism, high vagal tone, sinus node disease, AV block, inferior myocardial infarction, hypothermia, raised intracranial pressure, and drugs such as beta blockers or digoxin. Puffy eyelids may result from hypothyroidism, renal disease, heart failure, allergy, or local inflammation. Confirm with high TSH and low free T4; check thyroid peroxidase antibodies and ultrasound if a goitre or compression needs assessment. Anaemia may be normocytic, iron-deficiency from menorrhagia, or macrocytic from B12/folate deficiency or pernicious anaemia. Ask about menorrhagia, irregular or anovulatory cycles, infertility, miscarriage and reduced libido. Hand signs include cold dry skin, coarse skin, non-pitting swelling, slow relaxation of reflexes, carpal tunnel syndrome, and brittle nails. Surgery is not routine; it may be considered for a large compressive goitre, suspicious nodule, or malignancy.</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="C936" t="inlineStr">
         <is>
-          <t>Which of the following should be the first diagnostic test ordered in a patient with a solitary thyroid nodule?</t>
-        </is>
-      </c>
-      <c r="F936" t="inlineStr">
-        <is>
-          <t>Radioactive iodine scan</t>
-        </is>
-      </c>
-      <c r="G936" t="inlineStr">
-        <is>
-          <t>CT or MRI</t>
-        </is>
-      </c>
-      <c r="H936" t="inlineStr">
-        <is>
-          <t>Fine needle aspiration</t>
-        </is>
-      </c>
-      <c r="I936" t="inlineStr">
-        <is>
-          <t>Core needle biopsy</t>
-        </is>
-      </c>
-      <c r="R936" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="T936" t="inlineStr">
-        <is>
-          <t>The size of the adrenal mass on imaging studies is the single most important criterion to help diagnose malignancy. In the series reported by Copeland, 92% of adrenal cancers were &gt;6 cm in diameter. The sensitivity, specificity, and like- lihood ratio of tumor size in predicting malignancy (based on Surveillance; Epidemiology, and End Results program data) was recently reported as 96%, 51%, and 2 for tumors ≥4 cm; and 90%, 78%, and 4.1 for tumors ≥6 cm. Other CT imaging characteristics suggesting malignancy include tu- mor heterogeneity, irregular margins, and the presence of hemorrhage and adjacent lymphadenopathy or liver metas- tases. Moderately bright signal intensity on Tz-weighted im- CHAPTER 38 ages (adrenal mass to liver ratio 1.2:2.8), significant lesion enhancement, and slow washout after injection of gado- linium contrast also indicate malignancy, as does evidence of local invasion into adjacent structures such as the liver, blood vessels (IVC), and distant metastases. (See Schwartz 9th ed., p 1397.) Recent studies have shown that plasma metanephrines are the most reliable tests to identify pheochromocytomas, with sen- Thyroid, Parathyroid, and Adrenal sitivity approaching 100%. Urinary metanephrines are 98% sensitive and also are high- ly specific for pheochromocytomas, whereas VMA measure- ments are slightly less sensitive and specific. False-positive VMA tests may result from ingestion of caffeine, raw fruits, or medications (α-methyldopa).Fractionated urinary cat- echolamines(norepinephrine, epinephrine, and dopamine) also are very sensitive but less specific for pheochromocy- tomas. (See Schwartz 9thed., p1399.) Epinephrine and human chorionic gonadotrophin hor- mones stimulate thyroid hormone production. Thus, el- evated thyroid hormone levels are found in pregnancy and gynecologic malignancies such as hydatidiform mole. In contrast, glucocorticoids inhibit thyroid hormone produc- tion. In severely ill patients, peripheral thyroid hormones may be reduced, without a compensatory increase in TSH levels, giving rise to the euthyroid sick syndrome. (See Schwartz 9thed., p 1348.) FNAB has become the single most important test in the evaluation of thyroid masses and can be performed with or without ultrasound guidance. (See Schwartz 9th ed., p 1360, and Fig. 38-9.) Solitary thyroid nodule FNAB a CHAPTER 38 Nondiagnostic Repeat FNAB Benign Cyst nodule Colloid Aspirate consider T4 therapy Observe Thyroid, Parathyroid, and Adrenal Reaccumulates ↓ X3 Continued growth compressive symptoms +/- FNAB Thyroidectomy FIG. 38-9. Management of a solitary thyroid nodule. a = except in patients with a history of external radiation exposure or a family history of thyroid cancer; FNAB = fine-needle aspiration biopsy; RAl = radioactive iodine; T = thyroxine. 31.Which of the following cancers does NOT occur in thy- roglossal duct cysts?</t>
+          <t>y female pt presented with fatigue, lethargy, hypersomnia, (weight gain, cold intolerance and sense of compression in the neck. On examination; pulse 56 m, Bl P140/100 with pallor, puffiness and slow thick voice. Chest was free, She had a family history of a similar condition, but past history was irrelevant. [2nd 2017] a. Enumerate causes of bradycardia (2 marks). b. Enumerate causes of puffy eye lids (2) c. What is your provisional diagnosis why? (2 marks) d. How can you confirm this diagnosis? (1 mark) e. What are the types of anaemia in this case (2 marks) f. What can you find in the obstetric and gynecological history in this patient? (2 marks). g. Give other signs in the hands (2 mark) h. Do you think that surgery may have a role in the treatment? (1 mark)</t>
         </is>
       </c>
       <c r="V936" t="inlineStr">
         <is>
-          <t>QCS</t>
+          <t>QROC</t>
         </is>
       </c>
       <c r="W936" t="inlineStr">
@@ -50046,49 +49769,24 @@
       </c>
       <c r="AC936" t="inlineStr">
         <is>
-          <t>External, Schwartz</t>
+          <t>External, Endocrine Written</t>
+        </is>
+      </c>
+      <c r="AF936" t="inlineStr">
+        <is>
+          <t>The likely diagnosis is primary hypothyroidism, probably autoimmune thyroiditis, with possible goitre. Bradycardia causes include hypothyroidism, high vagal tone, sinus node disease, AV block, inferior myocardial infarction, hypothermia, raised intracranial pressure, and drugs such as beta blockers or digoxin. Puffy eyelids may result from hypothyroidism, renal disease, heart failure, allergy, or local inflammation. Confirm with high TSH and low free T4; check thyroid peroxidase antibodies and ultrasound if a goitre or compression needs assessment. Anaemia may be normocytic, iron-deficiency from menorrhagia, or macrocytic from B12/folate deficiency or pernicious anaemia. Ask about menorrhagia, irregular or anovulatory cycles, infertility, miscarriage and reduced libido. Hand signs include cold dry skin, coarse skin, non-pitting swelling, slow relaxation of reflexes, carpal tunnel syndrome, and brittle nails. Surgery is not routine; it may be considered for a large compressive goitre, suspicious nodule, or malignancy.</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="C937" t="inlineStr">
         <is>
-          <t>Which of the following cancers does NOT occur in thyroglossal duct cysts?</t>
-        </is>
-      </c>
-      <c r="F937" t="inlineStr">
-        <is>
-          <t>Papillary thyroid cancer</t>
-        </is>
-      </c>
-      <c r="G937" t="inlineStr">
-        <is>
-          <t>Follicular thyroid cancer</t>
-        </is>
-      </c>
-      <c r="H937" t="inlineStr">
-        <is>
-          <t>Medullary thyroid cancer</t>
-        </is>
-      </c>
-      <c r="I937" t="inlineStr">
-        <is>
-          <t>Hürthle cell cancer</t>
-        </is>
-      </c>
-      <c r="R937" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="T937" t="inlineStr">
-        <is>
-          <t>Approximately 1% of thyroglossal duct cysts are found to contain cancer, which is usually papillary (85%).The role of total thyroidectomy in this setting is controversial, but is advised in older patients with large tumors, particular- ly if there are additional thyroid nodules and evidence of cyst wall invasion or lymph node metastases. Squamous, Hürthle cell, and anaplastic cancers also have been reported but are rare. Medullary thyroid cancers (MTCs) are, how- ever, not found in thyroglossal duct cysts. (See Schwartz 9th ed., p1344.)</t>
+          <t>A 23-year old female patient presented with history of 2 months dyspnea, palpitation, anxiety, insomnia, and weight loss. Her past history is irrelevant, and her mother has a similar condition. [1st 2016] A. What is the most likely diagnosis? And why? (3 marks) B. What is the first possible etiology in this patient? Mention 3 other common etiologies C. What is expected in the appetite and menstrual history in this patient (2 marks) D. What is the most sensitive sign in the eye? (1 mark). Give 4 important signs in the hand E. What are expected in the laboratory and radiological investigations of this patient? F. Give 2 different drugs (of different classes), with their dosage, for the treatment</t>
         </is>
       </c>
       <c r="V937" t="inlineStr">
         <is>
-          <t>QCS</t>
+          <t>QROC</t>
         </is>
       </c>
       <c r="W937" t="inlineStr">
@@ -50103,24 +49801,19 @@
       </c>
       <c r="AC937" t="inlineStr">
         <is>
-          <t>External, Schwartz</t>
+          <t>External, Endocrine Written</t>
+        </is>
+      </c>
+      <c r="AF937" t="inlineStr">
+        <is>
+          <t>The most likely diagnosis is Graves disease (autoimmune thyrotoxicosis), supported by weight loss, dyspnoea, palpitations, anxiety, insomnia and a family history. The likely etiology is Graves disease; other causes include toxic multinodular goitre, toxic adenoma, thyroiditis, iodine or amiodarone exposure, and exogenous thyroid hormone. Appetite is often increased despite weight loss; menstrual cycles may be scanty or irregular, with reduced fertility. The most sensitive eye sign is lid retraction/lag. Hand signs include warm moist palms, fine tremor, onycholysis, thyroid acropachy, and palmar erythema. TSH is suppressed with raised free T4 and/or T3; TSH-receptor antibodies support Graves disease. Ultrasound may show diffuse enlargement and increased vascularity; uptake scanning shows diffuse increased uptake when indicated. Treat symptoms with a beta blocker and a thionamide (for example carbimazole 15-40 mg daily initially, titrated to response); another class option is propranolol 10-40 mg every 6-8 hours for symptoms. Definitive options are radioiodine or thyroidectomy when appropriate.</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="C938" t="inlineStr">
         <is>
-          <t>female lady presented with palpitation, loss of weight, anxiety 3 months duration on Examination: tremors, staring look and neck swelling [2nd 2017] a. What is the most likely diagnosis? (2marks) b. Mention other symptoms and signs that confirm the diagnosis? (3marks) c. Mention laboratory (4marks) and radiological investigations? (4marks) d. Mention lines of treatment? (5marks)</t>
-        </is>
-      </c>
-      <c r="R938" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T938" t="inlineStr">
-        <is>
-          <t>The most likely diagnosis is Graves disease causing thyrotoxicosis, given palpitations, weight loss, anxiety, tremor, stare and goitre. Other features include heat intolerance, sweating, increased appetite, frequent stools, proximal myopathy, lid retraction or lag, diffuse vascular goitre and possible thyroid bruit. Check TSH (suppressed), free T4 and T3 (raised), thyroid receptor antibodies; ECG and baseline blood count/liver tests before antithyroid medication. Ultrasound with Doppler or radionuclide uptake can characterize the gland. Treat with symptom control using a beta blocker and antithyroid medication such as carbimazole; definitive radioiodine or thyroidectomy is selected according to patient factors and local practice.</t>
+          <t>An 18 years old girl Presented with unintentional weight loss, nocturia, Polyuria and high blood glucose. On examination, there was abdominal pain, dehydration, Hypotension and mental confusion. [1st 2015] A- Most likely diagnosis B- Investigations C- treatment plan</t>
         </is>
       </c>
       <c r="V938" t="inlineStr">
@@ -50141,23 +49834,18 @@
       <c r="AC938" t="inlineStr">
         <is>
           <t>External, Endocrine Written</t>
+        </is>
+      </c>
+      <c r="AF938" t="inlineStr">
+        <is>
+          <t>This is diabetic ketoacidosis, likely new-onset type 1 diabetes. Check bedside and laboratory glucose, venous blood gas, serum bicarbonate and anion gap, blood or urine ketones, electrolytes (especially potassium), urea/creatinine, osmolality, ECG, urinalysis, and cultures or other infection studies when indicated. Begin isotonic IV crystalloid, assess and replace potassium before insulin if potassium is low, then give IV regular insulin with frequent glucose, potassium and ketone monitoring. Add dextrose when glucose falls while continuing insulin until ketoacidosis resolves. Identify and treat the precipitating cause; monitor mental state, fluid balance and cerebral oedema risk.</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="C939" t="inlineStr">
         <is>
-          <t>y female pt presented with fatigue, lethargy, hypersomnia, weight gain, cold intolerance &amp; sense of compression in the neck. On examination; pulse 56/m, Bl P 140/100 with pallor, puffiness and slow thick voice. Chest was free. She had a family history of a similar condition, but past history was irrelevant [1st 2017] a. Enumerate causes of bradycardia (2 marks) b. Enumerate causes of puffy eye lids (2 marks) c. What is your provisional diagnosis, why? (2 marks) d. How can you confirm this diagnosis? (1 mark) e. What are the types of anaemia in this case (2 marks) f. What can you find in the obstetric and gynecological history in this patient? (2 marks) g. Give 3 other signs in the hands (2 mark) h. Do you think that surgery may have a role in the treatment?(1 mark)</t>
-        </is>
-      </c>
-      <c r="R939" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T939" t="inlineStr">
-        <is>
-          <t>The likely diagnosis is primary hypothyroidism, probably autoimmune thyroiditis, with possible goitre. Bradycardia causes include hypothyroidism, high vagal tone, sinus node disease, AV block, inferior myocardial infarction, hypothermia, raised intracranial pressure, and drugs such as beta blockers or digoxin. Puffy eyelids may result from hypothyroidism, renal disease, heart failure, allergy, or local inflammation. Confirm with high TSH and low free T4; check thyroid peroxidase antibodies and ultrasound if a goitre or compression needs assessment. Anaemia may be normocytic, iron-deficiency from menorrhagia, or macrocytic from B12/folate deficiency or pernicious anaemia. Ask about menorrhagia, irregular or anovulatory cycles, infertility, miscarriage and reduced libido. Hand signs include cold dry skin, coarse skin, non-pitting swelling, slow relaxation of reflexes, carpal tunnel syndrome, and brittle nails. Surgery is not routine; it may be considered for a large compressive goitre, suspicious nodule, or malignancy.</t>
+          <t>A male patient 38 old presenting by easy fatigability, dizziness on standing and recurrent vomiting blood pressure 90/60. There is skin hyperpigmentation of recent onset and patchy of buccal mucosa hyperpigmentation [2nd 2015] a. What is the most likely diagnosis? b. Discuss the investigations needed to reach the diagnosis c. Discuss the appropriate treatment.</t>
         </is>
       </c>
       <c r="V939" t="inlineStr">
@@ -50178,23 +49866,18 @@
       <c r="AC939" t="inlineStr">
         <is>
           <t>External, Endocrine Written</t>
+        </is>
+      </c>
+      <c r="AF939" t="inlineStr">
+        <is>
+          <t>The likely diagnosis is primary adrenal insufficiency (Addison disease), suggested by postural hypotension, vomiting and mucocutaneous hyperpigmentation. Confirm with morning cortisol and ACTH, electrolytes, glucose, plasma renin and aldosterone, and a short Synacthen stimulation test when the patient is stable; ACTH is high and cortisol response is inadequate. Check 21-hydroxylase antibodies and consider adrenal imaging or tests for infection when indicated. In adrenal crisis, draw blood if this does not delay treatment, then give IV hydrocortisone 100 mg immediately followed by 200 mg over 24 hours and rapid isotonic saline, with dextrose if hypoglycaemic. Long-term treatment is oral hydrocortisone in divided doses plus fludrocortisone, sick-day dose education and emergency steroid access.</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="C940" t="inlineStr">
         <is>
-          <t>y female pt presented with fatigue, lethargy, hypersomnia, (weight gain, cold intolerance and sense of compression in the neck. On examination; pulse 56 m, Bl P140/100 with pallor, puffiness and slow thick voice. Chest was free, She had a family history of a similar condition, but past history was irrelevant. [2nd 2017] a. Enumerate causes of bradycardia (2 marks). b. Enumerate causes of puffy eye lids (2) c. What is your provisional diagnosis why? (2 marks) d. How can you confirm this diagnosis? (1 mark) e. What are the types of anaemia in this case (2 marks) f. What can you find in the obstetric and gynecological history in this patient? (2 marks). g. Give other signs in the hands (2 mark) h. Do you think that surgery may have a role in the treatment? (1 mark)</t>
-        </is>
-      </c>
-      <c r="R940" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T940" t="inlineStr">
-        <is>
-          <t>The likely diagnosis is primary hypothyroidism, probably autoimmune thyroiditis, with possible goitre. Bradycardia causes include hypothyroidism, high vagal tone, sinus node disease, AV block, inferior myocardial infarction, hypothermia, raised intracranial pressure, and drugs such as beta blockers or digoxin. Puffy eyelids may result from hypothyroidism, renal disease, heart failure, allergy, or local inflammation. Confirm with high TSH and low free T4; check thyroid peroxidase antibodies and ultrasound if a goitre or compression needs assessment. Anaemia may be normocytic, iron-deficiency from menorrhagia, or macrocytic from B12/folate deficiency or pernicious anaemia. Ask about menorrhagia, irregular or anovulatory cycles, infertility, miscarriage and reduced libido. Hand signs include cold dry skin, coarse skin, non-pitting swelling, slow relaxation of reflexes, carpal tunnel syndrome, and brittle nails. Surgery is not routine; it may be considered for a large compressive goitre, suspicious nodule, or malignancy.</t>
+          <t>A 17 years old female presented at university hospital by disturbed consciousness, dehydration and rapid respiration (air hunger). BP 100/60 mm Hg, Temp 37.8, Cardiac Ex. Showed no abnormalities apart from tachycardia. R. blood sugar was 495 mg/dl. She has no history of diabetes mellitus before. [2nd 2014] 1- What Is most likely diagnosis. 2- What are further clinical signs and laboratory findings related to this condition? 3- treatment during the hospitalization &amp; the advice &amp; treatment post-dischargement</t>
         </is>
       </c>
       <c r="V940" t="inlineStr">
@@ -50215,23 +49898,18 @@
       <c r="AC940" t="inlineStr">
         <is>
           <t>External, Endocrine Written</t>
+        </is>
+      </c>
+      <c r="AF940" t="inlineStr">
+        <is>
+          <t>The likely diagnosis is diabetic ketoacidosis in a patient with previously undiagnosed diabetes. Look for dehydration, Kussmaul respiration, acetone breath, abdominal pain, vomiting, hypotension, tachycardia and altered consciousness. Laboratory findings include hyperglycaemia, ketonaemia/ketonuria, high-anion-gap metabolic acidosis, low bicarbonate, and total body potassium depletion (serum potassium may initially be normal or high). Treat with isotonic IV fluids, potassium-guided replacement, IV regular insulin, close monitoring and treatment of the precipitant; add dextrose as glucose falls and continue insulin until acidosis/ketosis resolves. At discharge, establish diabetes type, initiate an appropriate insulin regimen, teach glucose and ketone monitoring, sick-day rules, hypoglycaemia treatment, injection technique and follow-up.</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="C941" t="inlineStr">
         <is>
-          <t>A 23-year old female patient presented with history of 2 months dyspnea, palpitation, anxiety, insomnia, and weight loss. Her past history is irrelevant, and her mother has a similar condition. [1st 2016] A. What is the most likely diagnosis? And why? (3 marks) B. What is the first possible etiology in this patient? Mention 3 other common etiologies C. What is expected in the appetite and menstrual history in this patient (2 marks) D. What is the most sensitive sign in the eye? (1 mark). Give 4 important signs in the hand E. What are expected in the laboratory and radiological investigations of this patient? F. Give 2 different drugs (of different classes), with their dosage, for the treatment</t>
-        </is>
-      </c>
-      <c r="R941" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T941" t="inlineStr">
-        <is>
-          <t>The most likely diagnosis is Graves disease (autoimmune thyrotoxicosis), supported by weight loss, dyspnoea, palpitations, anxiety, insomnia and a family history. The likely etiology is Graves disease; other causes include toxic multinodular goitre, toxic adenoma, thyroiditis, iodine or amiodarone exposure, and exogenous thyroid hormone. Appetite is often increased despite weight loss; menstrual cycles may be scanty or irregular, with reduced fertility. The most sensitive eye sign is lid retraction/lag. Hand signs include warm moist palms, fine tremor, onycholysis, thyroid acropachy, and palmar erythema. TSH is suppressed with raised free T4 and/or T3; TSH-receptor antibodies support Graves disease. Ultrasound may show diffuse enlargement and increased vascularity; uptake scanning shows diffuse increased uptake when indicated. Treat symptoms with a beta blocker and a thionamide (for example carbimazole 15-40 mg daily initially, titrated to response); another class option is propranolol 10-40 mg every 6-8 hours for symptoms. Definitive options are radioiodine or thyroidectomy when appropriate.</t>
+          <t>21 year's Old Student Female; complaining of irritability, Excessive sweating, Cardiac palpitation &amp; occasionally hand tremors. There is no Thyroid Swelling. BL.P 138/75mmHg and TSH is low normal. [1st 2013] 1- what is the most likely diagnosis 2- What are Further clinical sign 3- discuss the important investigation 4- give one other diagnostic possibility? 5- Is this patient need psychiatric consultation and Why?</t>
         </is>
       </c>
       <c r="V941" t="inlineStr">
@@ -50254,130 +49932,7 @@
           <t>External, Endocrine Written</t>
         </is>
       </c>
-    </row>
-    <row r="942">
-      <c r="C942" t="inlineStr">
-        <is>
-          <t>An 18 years old girl Presented with unintentional weight loss, nocturia, Polyuria and high blood glucose. On examination, there was abdominal pain, dehydration, Hypotension and mental confusion. [1st 2015] A- Most likely diagnosis B- Investigations C- treatment plan</t>
-        </is>
-      </c>
-      <c r="R942" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T942" t="inlineStr">
-        <is>
-          <t>This is diabetic ketoacidosis, likely new-onset type 1 diabetes. Check bedside and laboratory glucose, venous blood gas, serum bicarbonate and anion gap, blood or urine ketones, electrolytes (especially potassium), urea/creatinine, osmolality, ECG, urinalysis, and cultures or other infection studies when indicated. Begin isotonic IV crystalloid, assess and replace potassium before insulin if potassium is low, then give IV regular insulin with frequent glucose, potassium and ketone monitoring. Add dextrose when glucose falls while continuing insulin until ketoacidosis resolves. Identify and treat the precipitating cause; monitor mental state, fluid balance and cerebral oedema risk.</t>
-        </is>
-      </c>
-      <c r="V942" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W942" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X942" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC942" t="inlineStr">
-        <is>
-          <t>External, Endocrine Written</t>
-        </is>
-      </c>
-    </row>
-    <row r="943">
-      <c r="C943" t="inlineStr">
-        <is>
-          <t>A male patient 38 old presenting by easy fatigability, dizziness on standing and recurrent vomiting blood pressure 90/60. There is skin hyperpigmentation of recent onset and patchy of buccal mucosa hyperpigmentation [2nd 2015] a. What is the most likely diagnosis? b. Discuss the investigations needed to reach the diagnosis c. Discuss the appropriate treatment.</t>
-        </is>
-      </c>
-      <c r="R943" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T943" t="inlineStr">
-        <is>
-          <t>The likely diagnosis is primary adrenal insufficiency (Addison disease), suggested by postural hypotension, vomiting and mucocutaneous hyperpigmentation. Confirm with morning cortisol and ACTH, electrolytes, glucose, plasma renin and aldosterone, and a short Synacthen stimulation test when the patient is stable; ACTH is high and cortisol response is inadequate. Check 21-hydroxylase antibodies and consider adrenal imaging or tests for infection when indicated. In adrenal crisis, draw blood if this does not delay treatment, then give IV hydrocortisone 100 mg immediately followed by 200 mg over 24 hours and rapid isotonic saline, with dextrose if hypoglycaemic. Long-term treatment is oral hydrocortisone in divided doses plus fludrocortisone, sick-day dose education and emergency steroid access.</t>
-        </is>
-      </c>
-      <c r="V943" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W943" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X943" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC943" t="inlineStr">
-        <is>
-          <t>External, Endocrine Written</t>
-        </is>
-      </c>
-    </row>
-    <row r="944">
-      <c r="C944" t="inlineStr">
-        <is>
-          <t>A 17 years old female presented at university hospital by disturbed consciousness, dehydration and rapid respiration (air hunger). BP 100/60 mm Hg, Temp 37.8, Cardiac Ex. Showed no abnormalities apart from tachycardia. R. blood sugar was 495 mg/dl. She has no history of diabetes mellitus before. [2nd 2014] 1- What Is most likely diagnosis. 2- What are further clinical signs and laboratory findings related to this condition? 3- treatment during the hospitalization &amp; the advice &amp; treatment post-dischargement</t>
-        </is>
-      </c>
-      <c r="R944" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T944" t="inlineStr">
-        <is>
-          <t>The likely diagnosis is diabetic ketoacidosis in a patient with previously undiagnosed diabetes. Look for dehydration, Kussmaul respiration, acetone breath, abdominal pain, vomiting, hypotension, tachycardia and altered consciousness. Laboratory findings include hyperglycaemia, ketonaemia/ketonuria, high-anion-gap metabolic acidosis, low bicarbonate, and total body potassium depletion (serum potassium may initially be normal or high). Treat with isotonic IV fluids, potassium-guided replacement, IV regular insulin, close monitoring and treatment of the precipitant; add dextrose as glucose falls and continue insulin until acidosis/ketosis resolves. At discharge, establish diabetes type, initiate an appropriate insulin regimen, teach glucose and ketone monitoring, sick-day rules, hypoglycaemia treatment, injection technique and follow-up.</t>
-        </is>
-      </c>
-      <c r="V944" t="inlineStr">
-        <is>
-          <t>QROC</t>
-        </is>
-      </c>
-      <c r="W944" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X944" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC944" t="inlineStr">
-        <is>
-          <t>External, Endocrine Written</t>
-        </is>
-      </c>
-    </row>
-    <row r="945">
-      <c r="C945" t="inlineStr">
-        <is>
-          <t>21 year's Old Student Female; complaining of irritability, Excessive sweating, Cardiac palpitation &amp; occasionally hand tremors. There is no Thyroid Swelling. BL.P 138/75mmHg and TSH is low normal. [1st 2013] 1- what is the most likely diagnosis 2- What are Further clinical sign 3- discuss the important investigation 4- give one other diagnostic possibility? 5- Is this patient need psychiatric consultation and Why?</t>
-        </is>
-      </c>
-      <c r="R945" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T945" t="inlineStr">
+      <c r="AF941" t="inlineStr">
         <is>
           <t>Most likely diagnosis: thyrotoxicosis without goitre - early Graves' disease, painless (silent/postpartum) thyroiditis, or factitious thyroxine intake; a low-normal TSH alone does not exclude it (T3 toxicosis possible). If thyroid tests prove normal, an anxiety state is the likely diagnosis.
 2- Further clinical signs: tachycardia (persisting during sleep in thyrotoxicosis), wide pulse pressure, warm moist hands, fine tremor of the outstretched hands, lid retraction and lid lag, exophthalmos, brisk reflexes, proximal myopathy, weight loss despite good appetite, heat intolerance, frequent stools, oligomenorrhoea.
@@ -50386,77 +49941,67 @@
 5- Psychiatric consultation: not initially - organic causes (thyrotoxicosis, pheochromocytoma, hypoglycaemia) must be excluded first, because anxiety symptoms are common manifestations of these endocrine disorders; referral is indicated only if all investigations are normal and anxiety symptoms persist.</t>
         </is>
       </c>
-      <c r="V945" t="inlineStr">
+    </row>
+    <row r="942">
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>45 years old presented to outpatient clinic by progressive loss of weight, easy fatigability, hyperpigmentation, on examination, he is hypotensive. [2nd 2013] A) What is your diagnosis? B) Discuss the possible investigations and treatment</t>
+        </is>
+      </c>
+      <c r="V942" t="inlineStr">
         <is>
           <t>QROC</t>
         </is>
       </c>
-      <c r="W945" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X945" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC945" t="inlineStr">
+      <c r="W942" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X942" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC942" t="inlineStr">
         <is>
           <t>External, Endocrine Written</t>
         </is>
       </c>
-    </row>
-    <row r="946">
-      <c r="C946" t="inlineStr">
-        <is>
-          <t>45 years old presented to outpatient clinic by progressive loss of weight, easy fatigability, hyperpigmentation, on examination, he is hypotensive. [2nd 2013] A) What is your diagnosis? B) Discuss the possible investigations and treatment</t>
-        </is>
-      </c>
-      <c r="R946" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T946" t="inlineStr">
+      <c r="AF942" t="inlineStr">
         <is>
           <t>A) Diagnosis: primary adrenal insufficiency (Addison's disease) - weight loss, easy fatigability, hyperpigmentation and hypotension.
 B) Investigations: 8 a.m. serum cortisol (low) and plasma ACTH (high); short Synacthen test (cortisol fails to rise above 18-20 microgram/dl); serum sodium (low), potassium (high), urea (high), glucose (low); plasma renin (high) and aldosterone (low); CBC (normocytic anaemia, eosinophilia, lymphocytosis); adrenal (21-hydroxylase) antibodies; chest X-ray, tuberculin test and CT adrenals (calcification in tuberculosis, enlargement in infiltration). Treatment: glucocorticoid replacement with hydrocortisone 15-25 mg/day in divided doses plus fludrocortisone 0.05-0.2 mg/day; adequate salt; double or triple the dose in intercurrent illness and give parenteral hydrocortisone before surgery or with vomiting; steroid card and emergency kit; treat the cause (antituberculous therapy); adrenal crisis - IV hydrocortisone 100 mg then 50-100 mg every 6-8 h, IV saline and dextrose.</t>
         </is>
       </c>
-      <c r="V946" t="inlineStr">
+    </row>
+    <row r="943">
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>A 15 years old boy diabetic on insulin therapy presented coma &amp; profuse Sweating. [2012] a. what is the most likely diagnosis. How can you confirm. b. Give possible explanation for this presentation and other possible clinical features c. Enumerate 5 different causes for hypoglycemia. d. Suggest the acceptable therapeutic strategy.</t>
+        </is>
+      </c>
+      <c r="V943" t="inlineStr">
         <is>
           <t>QROC</t>
         </is>
       </c>
-      <c r="W946" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X946" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC946" t="inlineStr">
+      <c r="W943" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X943" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC943" t="inlineStr">
         <is>
           <t>External, Endocrine Written</t>
         </is>
       </c>
-    </row>
-    <row r="947">
-      <c r="C947" t="inlineStr">
-        <is>
-          <t>A 15 years old boy diabetic on insulin therapy presented coma &amp; profuse Sweating. [2012] a. what is the most likely diagnosis. How can you confirm. b. Give possible explanation for this presentation and other possible clinical features c. Enumerate 5 different causes for hypoglycemia. d. Suggest the acceptable therapeutic strategy.</t>
-        </is>
-      </c>
-      <c r="R947" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T947" t="inlineStr">
+      <c r="AF943" t="inlineStr">
         <is>
           <t>a. Most likely diagnosis: hypoglycaemic coma (insulin-induced hypoglycaemia). Confirmed by capillary (bedside) and laboratory blood glucose below 70 mg/dl (often below 50 mg/dl) and prompt recovery after glucose (Whipple's triad).
 b. Explanation: excess insulin relative to glucose intake lowers blood glucose; neuroglycopenia causes impaired consciousness and coma, and the counter-regulatory sympathetic (adrenaline) discharge causes profuse sweating. Other possible clinical features: tachycardia, palpitation, tremor, pallor, hunger, anxiety, headache, confusion, abnormal behaviour, slurred speech, convulsions, focal neurological signs; the skin is moist and breathing is normal (no dehydration or acidotic breathing, unlike DKA).
@@ -50464,39 +50009,34 @@
 d. Therapeutic strategy: immediately IV dextrose (0.5-1 g/kg; e.g. 2-5 ml/kg of 10% dextrose, or 50 ml of 50% in older children) or glucagon 0.5-1 mg IM/SC if IV access is not available; recheck glucose after 15 minutes and repeat if needed; maintain with dextrose infusion then oral complex carbohydrate once conscious; identify the cause and adjust the insulin dose, meal plan and exercise; education of the patient and family about symptoms, carrying sugar, home glucose monitoring, glucagon kit and diabetic identification card.</t>
         </is>
       </c>
-      <c r="V947" t="inlineStr">
+    </row>
+    <row r="944">
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>A 57 years old patient presenting by disturbed consciousness .he is diabetic on insulin and no history of hypertension Abd. and heart Ex showed no abnormalities. [1st 2010] 1) Give 3 different causes for this presentation. 2) Discuss the Important investigations needed to reach the definite diagnosis. 3) Give 5 causes of hypoglycemia. 4) Discuss 5 Specific clinical sign of middle cerebral artery Occlusion.</t>
+        </is>
+      </c>
+      <c r="V944" t="inlineStr">
         <is>
           <t>QROC</t>
         </is>
       </c>
-      <c r="W947" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X947" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC947" t="inlineStr">
+      <c r="W944" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X944" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC944" t="inlineStr">
         <is>
           <t>External, Endocrine Written</t>
         </is>
       </c>
-    </row>
-    <row r="948">
-      <c r="C948" t="inlineStr">
-        <is>
-          <t>A 57 years old patient presenting by disturbed consciousness .he is diabetic on insulin and no history of hypertension Abd. and heart Ex showed no abnormalities. [1st 2010] 1) Give 3 different causes for this presentation. 2) Discuss the Important investigations needed to reach the definite diagnosis. 3) Give 5 causes of hypoglycemia. 4) Discuss 5 Specific clinical sign of middle cerebral artery Occlusion.</t>
-        </is>
-      </c>
-      <c r="R948" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T948" t="inlineStr">
+      <c r="AF944" t="inlineStr">
         <is>
           <t>Causes of disturbed consciousness in an insulin-treated diabetic: hypoglycaemic coma; diabetic ketoacidosis; hyperosmolar hyperglycaemic state; (also lactic acidosis, cerebrovascular stroke, uraemic coma).
 2) Important investigations: immediate capillary blood glucose then laboratory glucose; blood and urine ketones; arterial blood gases (pH, bicarbonate, anion gap); serum sodium, potassium, urea and creatinine; serum osmolality; serum lactate; CBC and cultures for infection; ECG; CT brain if focal neurological signs or no metabolic cause is found.
@@ -50504,39 +50044,34 @@
 4) Clinical signs of middle cerebral artery occlusion: contralateral hemiplegia affecting face and arm more than leg; contralateral hemisensory loss (face and arm); contralateral homonymous hemianopia; conjugate deviation of the eyes toward the side of the lesion; aphasia (Broca's, Wernicke's or global) if the dominant hemisphere is involved; neglect, anosognosia and dressing apraxia if the non-dominant hemisphere is involved.</t>
         </is>
       </c>
-      <c r="V948" t="inlineStr">
+    </row>
+    <row r="945">
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>A male patient 3 years old presenting by easy fatigue, dizziness on standing and recurrent vomiting. Blood pressure 90/60. There is skin hyperpigmentation of recent onset and patchy of buccal mucosa hyperpigmentation. [2nd 2010] a. What is the most likely diagnosis? b. Enumerate the cause of this disease. c. Discuss the investigations needed to reach the diagnosis. d. Mention 3 endocrinal causes of hyperpigmentation. e. Discuss the appropriate treatment.</t>
+        </is>
+      </c>
+      <c r="V945" t="inlineStr">
         <is>
           <t>QROC</t>
         </is>
       </c>
-      <c r="W948" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X948" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC948" t="inlineStr">
+      <c r="W945" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X945" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC945" t="inlineStr">
         <is>
           <t>External, Endocrine Written</t>
         </is>
       </c>
-    </row>
-    <row r="949">
-      <c r="C949" t="inlineStr">
-        <is>
-          <t>A male patient 3 years old presenting by easy fatigue, dizziness on standing and recurrent vomiting. Blood pressure 90/60. There is skin hyperpigmentation of recent onset and patchy of buccal mucosa hyperpigmentation. [2nd 2010] a. What is the most likely diagnosis? b. Enumerate the cause of this disease. c. Discuss the investigations needed to reach the diagnosis. d. Mention 3 endocrinal causes of hyperpigmentation. e. Discuss the appropriate treatment.</t>
-        </is>
-      </c>
-      <c r="R949" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T949" t="inlineStr">
+      <c r="AF945" t="inlineStr">
         <is>
           <t>a. Most likely diagnosis: primary adrenal insufficiency (Addison's disease) - fatigue, postural dizziness, vomiting, hypotension and recent skin and buccal hyperpigmentation.
 b. Causes: autoimmune adrenalitis (commonest; may be part of autoimmune polyglandular syndrome); tuberculosis; other infections (fungal, CMV/HIV); bilateral adrenal haemorrhage (anticoagulants, meningococcal sepsis - Waterhouse-Friderichsen); metastases; infiltration (amyloidosis, haemochromatosis); bilateral adrenalectomy; drugs (ketoconazole, mitotane); congenital adrenal hyperplasia and adrenoleukodystrophy in children and young males.
@@ -50545,39 +50080,34 @@
 e. Treatment: acute - IV hydrocortisone 100 mg (children about 2 mg/kg) then every 6-8 h, IV normal saline with dextrose, treat the precipitating cause; maintenance - hydrocortisone in divided doses plus fludrocortisone, adequate salt, stress (sick-day) dosing, parenteral hydrocortisone before surgery, steroid card and emergency injection; treat the underlying cause.</t>
         </is>
       </c>
-      <c r="V949" t="inlineStr">
+    </row>
+    <row r="946">
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>A female patient aged 43 years presenting by easy fatigue, loss of libido, constipation, recurrent knee joint pain. There is puffy face and mild edema in the lower limbs. Cardiac examination showed no abnormalities. [2008] 1) What is the most likely diagnosis? 2) What are farther symptoms and clinical signs in this case. 3) Discuss the investigations needed to confirm the diagnosis. 4) Give 2 other possibilities for this case.</t>
+        </is>
+      </c>
+      <c r="V946" t="inlineStr">
         <is>
           <t>QROC</t>
         </is>
       </c>
-      <c r="W949" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X949" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC949" t="inlineStr">
+      <c r="W946" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X946" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC946" t="inlineStr">
         <is>
           <t>External, Endocrine Written</t>
         </is>
       </c>
-    </row>
-    <row r="950">
-      <c r="C950" t="inlineStr">
-        <is>
-          <t>A female patient aged 43 years presenting by easy fatigue, loss of libido, constipation, recurrent knee joint pain. There is puffy face and mild edema in the lower limbs. Cardiac examination showed no abnormalities. [2008] 1) What is the most likely diagnosis? 2) What are farther symptoms and clinical signs in this case. 3) Discuss the investigations needed to confirm the diagnosis. 4) Give 2 other possibilities for this case.</t>
-        </is>
-      </c>
-      <c r="R950" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T950" t="inlineStr">
+      <c r="AF946" t="inlineStr">
         <is>
           <t>Most likely diagnosis: primary hypothyroidism (fatigue, loss of libido, constipation, joint pain, puffy face and mild lower limb oedema), most likely autoimmune (Hashimoto's) thyroiditis.
 2) Further symptoms and signs: cold intolerance, weight gain with poor appetite, lethargy and slow mentation, depression, hoarse voice, dry coarse skin, hair loss and loss of the outer third of the eyebrows, menorrhagia, carpal tunnel syndrome, muscle cramps; examination - bradycardia, diastolic hypertension, pallor with yellowish skin, non-pitting oedema, goitre may be present, delayed relaxation of the ankle jerks, pericardial effusion.
@@ -50585,78 +50115,68 @@
 4) Other possibilities: nephrotic syndrome or chronic kidney disease (puffy face, oedema, fatigue); heart failure; depression; rheumatological disease (joint pain with fatigue); hypopituitarism (secondary hypothyroidism with low libido).</t>
         </is>
       </c>
-      <c r="V950" t="inlineStr">
+    </row>
+    <row r="947">
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>29 years old lady presented by excessive sweating, tremor, loose motion and insomnia. Blood pressure 170/90 mmgh. [2007] a) Give further 3 symptoms and 5 signs help in diagnosis. b) What's the most likely diagnosis. c) Discuss the investigations and treatment of this case.</t>
+        </is>
+      </c>
+      <c r="V947" t="inlineStr">
         <is>
           <t>QROC</t>
         </is>
       </c>
-      <c r="W950" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X950" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC950" t="inlineStr">
+      <c r="W947" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X947" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC947" t="inlineStr">
         <is>
           <t>External, Endocrine Written</t>
         </is>
       </c>
-    </row>
-    <row r="951">
-      <c r="C951" t="inlineStr">
-        <is>
-          <t>29 years old lady presented by excessive sweating, tremor, loose motion and insomnia. Blood pressure 170/90 mmgh. [2007] a) Give further 3 symptoms and 5 signs help in diagnosis. b) What's the most likely diagnosis. c) Discuss the investigations and treatment of this case.</t>
-        </is>
-      </c>
-      <c r="R951" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T951" t="inlineStr">
+      <c r="AF947" t="inlineStr">
         <is>
           <t>a) Further symptoms: heat intolerance, weight loss despite increased appetite, palpitation, nervousness/irritability, menstrual irregularity (oligomenorrhoea), muscle weakness. Signs: tachycardia or atrial fibrillation with wide pulse pressure (systolic hypertension), warm moist skin, fine tremor of outstretched hands, lid retraction and lid lag, exophthalmos, diffuse goitre with bruit, proximal myopathy and brisk reflexes, pretibial myxoedema.
 b) Most likely diagnosis: thyrotoxicosis, most likely Graves' disease (pheochromocytoma is the main differential of sweating, tremor and hypertension).
 c) Investigations: TSH (suppressed), free T4 and free T3 (raised); TSH-receptor antibodies; radioactive iodine uptake scan; thyroid ultrasound; ECG; CBC and liver function tests before treatment; plasma metanephrines if thyroid tests are normal. Treatment: propranolol for symptoms; carbimazole/methimazole for 12-18 months (propylthiouracil in first-trimester pregnancy) with warning about agranulocytosis; definitive radioactive iodine or thyroidectomy for relapse or large goitre; follow-up thyroid function tests.</t>
         </is>
       </c>
-      <c r="V951" t="inlineStr">
+    </row>
+    <row r="948">
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>A male patient aged 52 years, with diabetes mikkits of 10 years duration, maintained 25 units of insulin daily, was admitted to hospital in a comatosed state, he had history fiver and loss of appetite 3 days before: [2002] a. What are the most probable 3 D.D. b. Mention the expected clinical signs. c. Invest required and its significance. d. Outline the ttt for one diagnosis</t>
+        </is>
+      </c>
+      <c r="V948" t="inlineStr">
         <is>
           <t>QROC</t>
         </is>
       </c>
-      <c r="W951" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X951" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AC951" t="inlineStr">
+      <c r="W948" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X948" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC948" t="inlineStr">
         <is>
           <t>External, Endocrine Written</t>
         </is>
       </c>
-    </row>
-    <row r="952">
-      <c r="C952" t="inlineStr">
-        <is>
-          <t>A male patient aged 52 years, with diabetes mikkits of 10 years duration, maintained 25 units of insulin daily, was admitted to hospital in a comatosed state, he had history fiver and loss of appetite 3 days before: [2002] a. What are the most probable 3 D.D. b. Mention the expected clinical signs. c. Invest required and its significance. d. Outline the ttt for one diagnosis</t>
-        </is>
-      </c>
-      <c r="R952" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T952" t="inlineStr">
+      <c r="AF948" t="inlineStr">
         <is>
           <t>a. Most probable 3 D.D.: diabetic ketoacidosis; hyperosmolar hyperglycaemic state; hypoglycaemic coma (continuing insulin with loss of appetite) - all precipitated by the febrile infection (also consider sepsis/meningitis and stroke).
 b. Expected clinical signs: DKA - dehydration (dry tongue, sunken eyes, hypotension, tachycardia), Kussmaul acidotic breathing, acetone odour of breath, abdominal tenderness; HHS - severe dehydration, no acidotic breathing, focal neurological signs or seizures; hypoglycaemia - sweating, tachycardia, moist skin, normal respiration, possibly convulsions or extensor plantars; plus fever and signs of the infection focus (chest, urine, skin).
@@ -50664,9 +50184,197 @@
 d. Treatment of one diagnosis (DKA): IV normal saline 1 L in the first hour then according to hydration; IV regular insulin infusion 0.1 unit/kg/h after K is above 3.3 mmol/L; potassium replacement in the fluids; add 5% dextrose when glucose reaches about 250 mg/dl and continue insulin until ketoacidosis resolves; bicarbonate only if pH below 6.9; antibiotics for the infection; hourly glucose and 2-4 hourly electrolytes and blood gases; then return to subcutaneous insulin overlapping the infusion.</t>
         </is>
       </c>
+    </row>
+    <row r="949">
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>The most common cause of primary adrenal insufficiency (Addison's disease) is</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Autoimmune process</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>Surgical excision</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>Hemorhagic shock</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>T.B.</t>
+        </is>
+      </c>
+      <c r="R949" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V949" t="inlineStr">
+        <is>
+          <t>QCS</t>
+        </is>
+      </c>
+      <c r="W949" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X949" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC949" t="inlineStr">
+        <is>
+          <t>External, Endocrine Written</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>The following is not a feature of diabetic ketoacidosis</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Hyperthermia</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>Dehydration</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>Leukocytosis</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>Air hunger</t>
+        </is>
+      </c>
+      <c r="R950" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V950" t="inlineStr">
+        <is>
+          <t>QCS</t>
+        </is>
+      </c>
+      <c r="W950" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X950" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC950" t="inlineStr">
+        <is>
+          <t>External, Endocrine Written</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>The following anti diabetic drug causes considerable weight loss</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Pioglitazone</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>Insulin</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>Sulphonylures</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>SGLT 2 inhibitors</t>
+        </is>
+      </c>
+      <c r="R951" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="V951" t="inlineStr">
+        <is>
+          <t>QCS</t>
+        </is>
+      </c>
+      <c r="W951" t="inlineStr">
+        <is>
+          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
+        </is>
+      </c>
+      <c r="X951" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
+      <c r="AC951" t="inlineStr">
+        <is>
+          <t>External, Endocrine Written</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Normal fasting plasma glucose is:</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>70-100 mg/dl</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>70-110 mg/dl</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>70-125 mg/dl</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>B. 70-140 mg/dl</t>
+        </is>
+      </c>
+      <c r="R952" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="V952" t="inlineStr">
         <is>
-          <t>QROC</t>
+          <t>QCS</t>
         </is>
       </c>
       <c r="W952" t="inlineStr">
@@ -50688,32 +50396,32 @@
     <row r="953">
       <c r="C953" t="inlineStr">
         <is>
-          <t>The most common cause of primary adrenal insufficiency (Addison's disease) is</t>
+          <t>The following drug doesn't induce hypoglycemia in type 2 diabetes:</t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t>Autoimmune process</t>
+          <t>Sulphonylureas</t>
         </is>
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>Surgical excision</t>
+          <t>Pioglitazone</t>
         </is>
       </c>
       <c r="H953" t="inlineStr">
         <is>
-          <t>Hemorhagic shock</t>
+          <t>Repaglinide</t>
         </is>
       </c>
       <c r="I953" t="inlineStr">
         <is>
-          <t>T.B.</t>
+          <t>Insulin</t>
         </is>
       </c>
       <c r="R953" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V953" t="inlineStr">
@@ -50740,32 +50448,37 @@
     <row r="954">
       <c r="C954" t="inlineStr">
         <is>
-          <t>The following is not a feature of diabetic ketoacidosis</t>
+          <t>Prolonged use of metformin requires supplementation with:</t>
         </is>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>Hyperthermia</t>
+          <t>lron</t>
         </is>
       </c>
       <c r="G954" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="H954" t="inlineStr">
         <is>
-          <t>Leukocytosis</t>
+          <t>Folic acid</t>
         </is>
       </c>
       <c r="I954" t="inlineStr">
         <is>
-          <t>Air hunger</t>
+          <t>lodine</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>2018</t>
         </is>
       </c>
       <c r="R954" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V954" t="inlineStr">
@@ -50792,32 +50505,32 @@
     <row r="955">
       <c r="C955" t="inlineStr">
         <is>
-          <t>The following anti diabetic drug causes considerable weight loss</t>
+          <t>Surgery is never indicated in</t>
         </is>
       </c>
       <c r="F955" t="inlineStr">
         <is>
-          <t>Pioglitazone</t>
+          <t>Hashimotos thyroidits</t>
         </is>
       </c>
       <c r="G955" t="inlineStr">
         <is>
-          <t>Insulin</t>
+          <t>Primary hyperparathyroidism</t>
         </is>
       </c>
       <c r="H955" t="inlineStr">
         <is>
-          <t>Sulphonylures</t>
+          <t>Cushing disease</t>
         </is>
       </c>
       <c r="I955" t="inlineStr">
         <is>
-          <t>SGLT 2 inhibitors</t>
+          <t>Thyroid carcinoma</t>
         </is>
       </c>
       <c r="R955" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V955" t="inlineStr">
@@ -50844,32 +50557,32 @@
     <row r="956">
       <c r="C956" t="inlineStr">
         <is>
-          <t>Normal fasting plasma glucose is:</t>
+          <t>Imatinib is tyrosine kinase inhibitor used for treatment of</t>
         </is>
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t>70-100 mg/dl</t>
+          <t>Acute lymphatic leukemia</t>
         </is>
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>70-110 mg/dl</t>
+          <t>chronic lymphatic leukemia</t>
         </is>
       </c>
       <c r="H956" t="inlineStr">
         <is>
-          <t>70-125 mg/dl</t>
+          <t>Acute myeloid leukemia</t>
         </is>
       </c>
       <c r="I956" t="inlineStr">
         <is>
-          <t>B. 70-140 mg/dl</t>
+          <t>chronic myeloid leukemia</t>
         </is>
       </c>
       <c r="R956" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V956" t="inlineStr">
@@ -50896,17 +50609,17 @@
     <row r="957">
       <c r="C957" t="inlineStr">
         <is>
-          <t>The following drug doesn't induce hypoglycemia in type 2 diabetes:</t>
+          <t>All can induce hypoglycemia in type 2 DM except</t>
         </is>
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t>Sulphonylureas</t>
+          <t>Sulphonylurea</t>
         </is>
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>Pioglitazone</t>
+          <t>insulin therapy</t>
         </is>
       </c>
       <c r="H957" t="inlineStr">
@@ -50916,12 +50629,12 @@
       </c>
       <c r="I957" t="inlineStr">
         <is>
-          <t>Insulin</t>
+          <t>Acarbose</t>
         </is>
       </c>
       <c r="R957" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V957" t="inlineStr">
@@ -50948,32 +50661,27 @@
     <row r="958">
       <c r="C958" t="inlineStr">
         <is>
-          <t>Prolonged use of metformin requires supplementation with:</t>
+          <t>Bromocriptin is not useful in treatment of</t>
         </is>
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t>lron</t>
+          <t>Parkinsonism</t>
         </is>
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>Alzheimer disease</t>
         </is>
       </c>
       <c r="H958" t="inlineStr">
         <is>
-          <t>Folic acid</t>
+          <t>Diabetes Mellitus</t>
         </is>
       </c>
       <c r="I958" t="inlineStr">
         <is>
-          <t>lodine</t>
-        </is>
-      </c>
-      <c r="J958" t="inlineStr">
-        <is>
-          <t>2018</t>
+          <t>Acromegaly</t>
         </is>
       </c>
       <c r="R958" t="inlineStr">
@@ -51005,32 +50713,32 @@
     <row r="959">
       <c r="C959" t="inlineStr">
         <is>
-          <t>Surgery is never indicated in</t>
+          <t>Graves' disease is best treated by:</t>
         </is>
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t>Hashimotos thyroidits</t>
+          <t>Surgery</t>
         </is>
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>Primary hyperparathyroidism</t>
+          <t>Radioactive iodine</t>
         </is>
       </c>
       <c r="H959" t="inlineStr">
         <is>
-          <t>Cushing disease</t>
+          <t>Propylthiouracil</t>
         </is>
       </c>
       <c r="I959" t="inlineStr">
         <is>
-          <t>Thyroid carcinoma</t>
+          <t>Carbimazole</t>
         </is>
       </c>
       <c r="R959" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V959" t="inlineStr">
@@ -51057,32 +50765,32 @@
     <row r="960">
       <c r="C960" t="inlineStr">
         <is>
-          <t>Imatinib is tyrosine kinase inhibitor used for treatment of</t>
+          <t>In somogyi phenomenon commonly associated with type 2 DM, the dose of insulin should be</t>
         </is>
       </c>
       <c r="F960" t="inlineStr">
         <is>
-          <t>Acute lymphatic leukemia</t>
+          <t>Increased</t>
         </is>
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>chronic lymphatic leukemia</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="H960" t="inlineStr">
         <is>
-          <t>Acute myeloid leukemia</t>
+          <t>Decreased</t>
         </is>
       </c>
       <c r="I960" t="inlineStr">
         <is>
-          <t>chronic myeloid leukemia</t>
+          <t>Needs no change</t>
         </is>
       </c>
       <c r="R960" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V960" t="inlineStr">
@@ -51109,32 +50817,32 @@
     <row r="961">
       <c r="C961" t="inlineStr">
         <is>
-          <t>All can induce hypoglycemia in type 2 DM except</t>
+          <t>Commonest cause of ambiguous genetilia in newborn is</t>
         </is>
       </c>
       <c r="F961" t="inlineStr">
         <is>
-          <t>Sulphonylurea</t>
+          <t>Conginital Adrenal Hyperplasia</t>
         </is>
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t>insulin therapy</t>
+          <t>True hermaphroditism</t>
         </is>
       </c>
       <c r="H961" t="inlineStr">
         <is>
-          <t>Repaglinide</t>
+          <t>Testicular feminisation</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
         <is>
-          <t>Acarbose</t>
+          <t>Pseudo hermaphroditism</t>
         </is>
       </c>
       <c r="R961" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V961" t="inlineStr">
@@ -51161,32 +50869,32 @@
     <row r="962">
       <c r="C962" t="inlineStr">
         <is>
-          <t>Bromocriptin is not useful in treatment of</t>
+          <t>insulin glargine is</t>
         </is>
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t>Parkinsonism</t>
+          <t>Short acting insulin</t>
         </is>
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>Alzheimer disease</t>
+          <t>ultrashort acting</t>
         </is>
       </c>
       <c r="H962" t="inlineStr">
         <is>
-          <t>Diabetes Mellitus</t>
+          <t>premixed insulin</t>
         </is>
       </c>
       <c r="I962" t="inlineStr">
         <is>
-          <t>Acromegaly</t>
+          <t>long acting basal insulin</t>
         </is>
       </c>
       <c r="R962" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V962" t="inlineStr">
@@ -51213,27 +50921,27 @@
     <row r="963">
       <c r="C963" t="inlineStr">
         <is>
-          <t>Graves' disease is best treated by:</t>
+          <t>the following are features of Cushing syndrome except</t>
         </is>
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t>Surgery</t>
+          <t>moon face</t>
         </is>
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>Radioactive iodine</t>
+          <t>buffalo hump</t>
         </is>
       </c>
       <c r="H963" t="inlineStr">
         <is>
-          <t>Propylthiouracil</t>
+          <t>stria rubra</t>
         </is>
       </c>
       <c r="I963" t="inlineStr">
         <is>
-          <t>Carbimazole</t>
+          <t>alopecia</t>
         </is>
       </c>
       <c r="R963" t="inlineStr">
@@ -51265,27 +50973,22 @@
     <row r="964">
       <c r="C964" t="inlineStr">
         <is>
-          <t>In somogyi phenomenon commonly associated with type 2 DM, the dose of insulin should be</t>
+          <t>all of the following are features of pituitary dwarfism except a-Caused by decreased growth hormone</t>
         </is>
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>Increased</t>
+          <t>proportionate dwarfism</t>
         </is>
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>Stopped</t>
+          <t>mental apathy</t>
         </is>
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>Decreased</t>
-        </is>
-      </c>
-      <c r="I964" t="inlineStr">
-        <is>
-          <t>Needs no change</t>
+          <t>may be associated with hypogonadism</t>
         </is>
       </c>
       <c r="R964" t="inlineStr">
@@ -51317,32 +51020,37 @@
     <row r="965">
       <c r="C965" t="inlineStr">
         <is>
-          <t>Commonest cause of ambiguous genetilia in newborn is</t>
+          <t>Mr. Ali, 40 y, presented with polyuria and weight loss, HbA1c 10, Bl p 170/110, BMI 27 Kg/m². The following is not accurate regarding the targets of management of Mr. Ali:</t>
         </is>
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>Conginital Adrenal Hyperplasia</t>
+          <t>HBA1C &lt; 7%</t>
         </is>
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>True hermaphroditism</t>
+          <t>Fasting plasma Glucose &lt;130 mg/dl</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>Testicular feminisation</t>
+          <t>Post prandial &lt; 180 mg/dl</t>
         </is>
       </c>
       <c r="I965" t="inlineStr">
         <is>
-          <t>Pseudo hermaphroditism</t>
+          <t>Bl p &lt;150/100 mm Hg</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>HDL &gt; 40 mg/dl</t>
         </is>
       </c>
       <c r="R965" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V965" t="inlineStr">
@@ -51360,41 +51068,54 @@
           <t>Endocrinology</t>
         </is>
       </c>
+      <c r="AB965" t="n">
+        <v>2024</v>
+      </c>
       <c r="AC965" t="inlineStr">
         <is>
-          <t>External, Endocrine Written</t>
+          <t>Exams, End 2024</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="C966" t="inlineStr">
         <is>
-          <t>insulin glargine is</t>
+          <t>The following is not a goal of treatment for Mr. Ali:</t>
         </is>
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t>Short acting insulin</t>
+          <t>To improve symptoms</t>
         </is>
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>ultrashort acting</t>
+          <t>Avoid hypoglycemia</t>
         </is>
       </c>
       <c r="H966" t="inlineStr">
         <is>
-          <t>premixed insulin</t>
+          <t>Increase body weight</t>
         </is>
       </c>
       <c r="I966" t="inlineStr">
         <is>
-          <t>long acting basal insulin</t>
+          <t>Prevent diabetic complications</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>Improve insulin sensitivity</t>
         </is>
       </c>
       <c r="R966" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T966" t="inlineStr">
+        <is>
+          <t>Treatment aims to relieve symptoms, avoid hypoglycemia, prevent diabetic complications, and improve insulin sensitivity. Increasing body weight is not a treatment goal.</t>
         </is>
       </c>
       <c r="V966" t="inlineStr">
@@ -51412,41 +51133,49 @@
           <t>Endocrinology</t>
         </is>
       </c>
+      <c r="AB966" t="n">
+        <v>2024</v>
+      </c>
       <c r="AC966" t="inlineStr">
         <is>
-          <t>External, Endocrine Written</t>
+          <t>Exams, End 2024</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="C967" t="inlineStr">
         <is>
-          <t>the following are features of Cushing syndrome except</t>
+          <t>Which statement describes gestational diabetes correctly</t>
         </is>
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t>moon face</t>
+          <t>May starts in the first trimester</t>
         </is>
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>buffalo hump</t>
+          <t>Does not require treatment</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>stria rubra</t>
+          <t>Induces fetal macrosomia</t>
         </is>
       </c>
       <c r="I967" t="inlineStr">
         <is>
-          <t>alopecia</t>
+          <t>Never recur in subsequent pregnancies</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>The patient is not at risk of developing type 2 DM later in life</t>
         </is>
       </c>
       <c r="R967" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V967" t="inlineStr">
@@ -51464,36 +51193,49 @@
           <t>Endocrinology</t>
         </is>
       </c>
+      <c r="AB967" t="n">
+        <v>2024</v>
+      </c>
       <c r="AC967" t="inlineStr">
         <is>
-          <t>External, Endocrine Written</t>
+          <t>Exams, End 2024</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="C968" t="inlineStr">
         <is>
-          <t>all of the following are features of pituitary dwarfism except a-Caused by decreased growth hormone</t>
+          <t>Screening of congenital adrenal hyperplasia is usually done by measuring the plasma level of:</t>
         </is>
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t>proportionate dwarfism</t>
+          <t>17 hydroxyprogesterone</t>
         </is>
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>mental apathy</t>
+          <t>Aldosterone</t>
         </is>
       </c>
       <c r="H968" t="inlineStr">
         <is>
-          <t>may be associated with hypogonadism</t>
+          <t>Renin</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>Metanephrine</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>Epinephrine</t>
         </is>
       </c>
       <c r="R968" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V968" t="inlineStr">
@@ -51511,46 +51253,49 @@
           <t>Endocrinology</t>
         </is>
       </c>
+      <c r="AB968" t="n">
+        <v>2024</v>
+      </c>
       <c r="AC968" t="inlineStr">
         <is>
-          <t>External, Endocrine Written</t>
+          <t>Exams, End 2024</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="C969" t="inlineStr">
         <is>
-          <t>Mr. Ali, 40 y, presented with polyuria and weight loss, HbA1c 10, Bl p 170/110, BMI 27 Kg/m². The following is not accurate regarding the targets of management of Mr. Ali:</t>
+          <t>Pseudohyperaldosteronism is not characterized by</t>
         </is>
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t>HBA1C &lt; 7%</t>
+          <t>Hypertension without hypokalemia</t>
         </is>
       </c>
       <c r="G969" t="inlineStr">
         <is>
-          <t>Fasting plasma Glucose &lt;130 mg/dl</t>
+          <t>Caused by mineralocorticoid other than aldosterone</t>
         </is>
       </c>
       <c r="H969" t="inlineStr">
         <is>
-          <t>Post prandial &lt; 180 mg/dl</t>
+          <t>May be caused by excessive liquorice drinking</t>
         </is>
       </c>
       <c r="I969" t="inlineStr">
         <is>
-          <t>Bl p &lt;150/100 mm Hg</t>
+          <t>Renin is not elevated</t>
         </is>
       </c>
       <c r="J969" t="inlineStr">
         <is>
-          <t>HDL &gt; 40 mg/dl</t>
+          <t>Aldosterone is not elevated</t>
         </is>
       </c>
       <c r="R969" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="V969" t="inlineStr">
@@ -51580,42 +51325,37 @@
     <row r="970">
       <c r="C970" t="inlineStr">
         <is>
-          <t>The following is not a goal of treatment for Mr. Ali:</t>
+          <t>In boys, delayed puberty is the lack of starting testicular enlargement at the end of</t>
         </is>
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>To improve symptoms</t>
+          <t>12 y</t>
         </is>
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>Avoid hypoglycemia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H970" t="inlineStr">
         <is>
-          <t>Increase body weight</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
         <is>
-          <t>Prevent diabetic complications</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J970" t="inlineStr">
         <is>
-          <t>Improve insulin sensitivity</t>
+          <t>16 y</t>
         </is>
       </c>
       <c r="R970" t="inlineStr">
         <is>
           <t>C</t>
-        </is>
-      </c>
-      <c r="T970" t="inlineStr">
-        <is>
-          <t>Treatment aims to relieve symptoms, avoid hypoglycemia, prevent diabetic complications, and improve insulin sensitivity. Increasing body weight is not a treatment goal.</t>
         </is>
       </c>
       <c r="V970" t="inlineStr">
@@ -51645,37 +51385,32 @@
     <row r="971">
       <c r="C971" t="inlineStr">
         <is>
-          <t>Which statement describes gestational diabetes correctly</t>
+          <t>In the treatment of hypothyroidism, which is false</t>
         </is>
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>May starts in the first trimester</t>
+          <t>LT4 (levothyroxine) is usually used</t>
         </is>
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>Does not require treatment</t>
+          <t>Start with a high dose of LT4 then gradual down titration.</t>
         </is>
       </c>
       <c r="H971" t="inlineStr">
         <is>
-          <t>Induces fetal macrosomia</t>
+          <t>For proper absorption, the drug must be taken on an empty stomach.</t>
         </is>
       </c>
       <c r="I971" t="inlineStr">
         <is>
-          <t>Never recur in subsequent pregnancies</t>
-        </is>
-      </c>
-      <c r="J971" t="inlineStr">
-        <is>
-          <t>The patient is not at risk of developing type 2 DM later in life</t>
+          <t>Don't take the LT4 with calcium or iron simultaneously to avoid decreased absorption</t>
         </is>
       </c>
       <c r="R971" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V971" t="inlineStr">
@@ -51705,37 +51440,32 @@
     <row r="972">
       <c r="C972" t="inlineStr">
         <is>
-          <t>Screening of congenital adrenal hyperplasia is usually done by measuring the plasma level of:</t>
+          <t>Gynecomastia is caused by</t>
         </is>
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t>17 hydroxyprogesterone</t>
+          <t>Elevated serum testosterone levels</t>
         </is>
       </c>
       <c r="G972" t="inlineStr">
         <is>
-          <t>Aldosterone</t>
+          <t>Elevated prolactin</t>
         </is>
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>Renin</t>
+          <t>Reduced free testosterone/estrogen ratio</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
         <is>
-          <t>Metanephrine</t>
-        </is>
-      </c>
-      <c r="J972" t="inlineStr">
-        <is>
-          <t>Epinephrine</t>
+          <t>Reduced progesterone</t>
         </is>
       </c>
       <c r="R972" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V972" t="inlineStr">
@@ -51765,37 +51495,37 @@
     <row r="973">
       <c r="C973" t="inlineStr">
         <is>
-          <t>Pseudohyperaldosteronism is not characterized by</t>
+          <t>Hypogonadotropic (secondary) hypogonadism includes all the following except</t>
         </is>
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t>Hypertension without hypokalemia</t>
+          <t>Sheehan syndrome</t>
         </is>
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>Caused by mineralocorticoid other than aldosterone</t>
+          <t>Kallman syndrome</t>
         </is>
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>May be caused by excessive liquorice drinking</t>
+          <t>GH deficiency</t>
         </is>
       </c>
       <c r="I973" t="inlineStr">
         <is>
-          <t>Renin is not elevated</t>
+          <t>Hyperprolactinemia</t>
         </is>
       </c>
       <c r="J973" t="inlineStr">
         <is>
-          <t>Aldosterone is not elevated</t>
+          <t>Acromegaly</t>
         </is>
       </c>
       <c r="R973" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V973" t="inlineStr">
@@ -51825,37 +51555,37 @@
     <row r="974">
       <c r="C974" t="inlineStr">
         <is>
-          <t>In boys, delayed puberty is the lack of starting testicular enlargement at the end of</t>
+          <t>This class of drugs does not cause hyperprolactinemia.</t>
         </is>
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t>12 y</t>
+          <t>Prokinetic drugs (dopamine antagonists)</t>
         </is>
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Antipsychotics</t>
         </is>
       </c>
       <c r="H974" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Anti-depressants</t>
         </is>
       </c>
       <c r="I974" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Proton pump inhibitors</t>
         </is>
       </c>
       <c r="J974" t="inlineStr">
         <is>
-          <t>16 y</t>
+          <t>Pioglitazone</t>
         </is>
       </c>
       <c r="R974" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="V974" t="inlineStr">
@@ -51885,32 +51615,42 @@
     <row r="975">
       <c r="C975" t="inlineStr">
         <is>
-          <t>In the treatment of hypothyroidism, which is false</t>
+          <t>Which of the following is a potential complication of Cushing syndrome?</t>
         </is>
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t>LT4 (levothyroxine) is usually used</t>
+          <t>Osteoporosis</t>
         </is>
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>Start with a high dose of LT4 then gradual down titration.</t>
+          <t>Hypoglycemia</t>
         </is>
       </c>
       <c r="H975" t="inlineStr">
         <is>
-          <t>For proper absorption, the drug must be taken on an empty stomach.</t>
+          <t>Hypothyroidism</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
         <is>
-          <t>Don't take the LT4 with calcium or iron simultaneously to avoid decreased absorption</t>
+          <t>Low blood pressure</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>Anemia</t>
         </is>
       </c>
       <c r="R975" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T975" t="inlineStr">
+        <is>
+          <t>Cortisol excess causes osteoporosis (increased bone resorption, reduced osteoblast activity and calcium absorption); Cushing syndrome causes hyperglycaemia, hypertension and polycythaemia rather than hypoglycaemia, low blood pressure or anaemia.</t>
         </is>
       </c>
       <c r="V975" t="inlineStr">
@@ -51940,32 +51680,32 @@
     <row r="976">
       <c r="C976" t="inlineStr">
         <is>
-          <t>Gynecomastia is caused by</t>
+          <t>Which of the following is false about parathyroid hormone actions?</t>
         </is>
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t>Elevated serum testosterone levels</t>
+          <t>Stimulates resorption of (Ca, Ph, and Mg) from bones</t>
         </is>
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>Elevated prolactin</t>
+          <t>Inhibits resorption of (Ca, Ph, and Mg) from bones</t>
         </is>
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>Reduced free testosterone/estrogen ratio</t>
+          <t>Increases excretion of Ph by kidneys</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
         <is>
-          <t>Reduced progesterone</t>
+          <t>Stimulates calcitriol synthesis step in kidneys.</t>
         </is>
       </c>
       <c r="R976" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V976" t="inlineStr">
@@ -51995,37 +51735,32 @@
     <row r="977">
       <c r="C977" t="inlineStr">
         <is>
-          <t>Hypogonadotropic (secondary) hypogonadism includes all the following except</t>
+          <t>post-operative complications of pituitary adenoma include:</t>
         </is>
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t>Sheehan syndrome</t>
+          <t>CSF Leak</t>
         </is>
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>Kallman syndrome</t>
+          <t>diabetes insipidus</t>
         </is>
       </c>
       <c r="H977" t="inlineStr">
         <is>
-          <t>GH deficiency</t>
+          <t>apoplexy</t>
         </is>
       </c>
       <c r="I977" t="inlineStr">
         <is>
-          <t>Hyperprolactinemia</t>
-        </is>
-      </c>
-      <c r="J977" t="inlineStr">
-        <is>
-          <t>Acromegaly</t>
+          <t>All the above</t>
         </is>
       </c>
       <c r="R977" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V977" t="inlineStr">
@@ -52055,37 +51790,32 @@
     <row r="978">
       <c r="C978" t="inlineStr">
         <is>
-          <t>This class of drugs does not cause hyperprolactinemia.</t>
+          <t>Regarding Basal insulin therapy, which statement is wrong?</t>
         </is>
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t>Prokinetic drugs (dopamine antagonists)</t>
+          <t>It consists of long-acting insulin preparations.</t>
         </is>
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>Antipsychotics</t>
+          <t>It is effective at lowering fasting plasma glucose level</t>
         </is>
       </c>
       <c r="H978" t="inlineStr">
         <is>
-          <t>Anti-depressants</t>
+          <t>It suppresses hepatic glucose production</t>
         </is>
       </c>
       <c r="I978" t="inlineStr">
         <is>
-          <t>Proton pump inhibitors</t>
-        </is>
-      </c>
-      <c r="J978" t="inlineStr">
-        <is>
-          <t>Pioglitazone</t>
+          <t>It is effective at lowering postprandial plasma glucose level.</t>
         </is>
       </c>
       <c r="R978" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V978" t="inlineStr">
@@ -52115,42 +51845,37 @@
     <row r="979">
       <c r="C979" t="inlineStr">
         <is>
-          <t>Which of the following is a potential complication of Cushing syndrome?</t>
+          <t>Hypoglycemic symptoms include all the following except</t>
         </is>
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t>Osteoporosis</t>
+          <t>Pallor</t>
         </is>
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>Hypoglycemia</t>
+          <t>Irritability and bad behavior</t>
         </is>
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>Hypothyroidism</t>
+          <t>Dizziness</t>
         </is>
       </c>
       <c r="I979" t="inlineStr">
         <is>
-          <t>Low blood pressure</t>
+          <t>Tiredness</t>
         </is>
       </c>
       <c r="J979" t="inlineStr">
         <is>
-          <t>Anemia</t>
+          <t>Dry skin</t>
         </is>
       </c>
       <c r="R979" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="T979" t="inlineStr">
-        <is>
-          <t>Cortisol excess causes osteoporosis (increased bone resorption, reduced osteoblast activity and calcium absorption); Cushing syndrome causes hyperglycaemia, hypertension and polycythaemia rather than hypoglycaemia, low blood pressure or anaemia.</t>
+          <t>E</t>
         </is>
       </c>
       <c r="V979" t="inlineStr">
@@ -52180,32 +51905,37 @@
     <row r="980">
       <c r="C980" t="inlineStr">
         <is>
-          <t>Which of the following is false about parathyroid hormone actions?</t>
+          <t>A 35-year-old woman with a history of previous right thyroidectomy for a benign thyroid nodule now undergoes completion thyroidectomy for a suspicious thyroid mass. Several hours postoperatively, she developed progressive swelling under the incision, stridor, and difficulty breathing. Orotracheal intubation is successful. Which of the following is the most appropriate next step?</t>
         </is>
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>Stimulates resorption of (Ca, Ph, and Mg) from bones</t>
+          <t>Fiberoptic laryngoscopy to rule out bilateral vocal cord paralysis</t>
         </is>
       </c>
       <c r="G980" t="inlineStr">
         <is>
-          <t>Inhibits resorption of (Ca, Ph, and Mg) from bones</t>
+          <t>Administration of intravenous calcium</t>
         </is>
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>Increases excretion of Ph by kidneys</t>
+          <t>Administration of broad-spectrum antibiotics and debridement of the wound</t>
         </is>
       </c>
       <c r="I980" t="inlineStr">
         <is>
-          <t>Stimulates calcitriol synthesis step in kidneys.</t>
+          <t>Wound exploration</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>Administration of high-dose steroids and antihistamines</t>
         </is>
       </c>
       <c r="R980" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="V980" t="inlineStr">
@@ -52235,32 +51965,37 @@
     <row r="981">
       <c r="C981" t="inlineStr">
         <is>
-          <t>post-operative complications of pituitary adenoma include:</t>
+          <t>A 36-year-old woman presents with palpitations, anxiety, and hypertension. The workup reveals a pheochromocytoma. Which of the following is the best approach to optimizing the patient preoperatively?</t>
         </is>
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t>CSF Leak</t>
+          <t>Fluid restriction 24 hours preoperatively to prevent intraoperative congestive heart failure.</t>
         </is>
       </c>
       <c r="G981" t="inlineStr">
         <is>
-          <t>diabetes insipidus</t>
+          <t>Initiation of an α-blocker 24 hours prior to surgery</t>
         </is>
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>apoplexy</t>
+          <t>Initiation of an α-blocker at 1 to 3 weeks prior to surgery</t>
         </is>
       </c>
       <c r="I981" t="inlineStr">
         <is>
-          <t>All the above</t>
+          <t>Initiation of a β-blocker 1 to 3 weeks prior to surgery</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>Antihypertensive drug therapy with β-blockade followed by α-blockade starting at least 1 week prior to surgery.</t>
         </is>
       </c>
       <c r="R981" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V981" t="inlineStr">
@@ -52290,27 +52025,32 @@
     <row r="982">
       <c r="C982" t="inlineStr">
         <is>
-          <t>Regarding Basal insulin therapy, which statement is wrong?</t>
+          <t>A 58-year-old man presents with tachycardia, fever, confusion, and vomiting. Workup reveals markedly elevated (triiodothyronine) T3 and (thyroxine) T4 levels. He is diagnosed as having a thyroid storm. Which of the following is the most appropriate next step in the management of this patient?</t>
         </is>
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t>It consists of long-acting insulin preparations.</t>
+          <t>Emergent subtotal thyroidectomy</t>
         </is>
       </c>
       <c r="G982" t="inlineStr">
         <is>
-          <t>It is effective at lowering fasting plasma glucose level</t>
+          <t>Emergent total thyroidectomy</t>
         </is>
       </c>
       <c r="H982" t="inlineStr">
         <is>
-          <t>It suppresses hepatic glucose production</t>
+          <t>Emergent hemodialysis</t>
         </is>
       </c>
       <c r="I982" t="inlineStr">
         <is>
-          <t>It is effective at lowering postprandial plasma glucose level.</t>
+          <t>Administration of fluid, antithyroid drugs, β-blockers, iodine solution, and steroids</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>Emergent radiation therapy to the neck</t>
         </is>
       </c>
       <c r="R982" t="inlineStr">
@@ -52337,246 +52077,6 @@
         <v>2024</v>
       </c>
       <c r="AC982" t="inlineStr">
-        <is>
-          <t>Exams, End 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="983">
-      <c r="C983" t="inlineStr">
-        <is>
-          <t>Hypoglycemic symptoms include all the following except</t>
-        </is>
-      </c>
-      <c r="F983" t="inlineStr">
-        <is>
-          <t>Pallor</t>
-        </is>
-      </c>
-      <c r="G983" t="inlineStr">
-        <is>
-          <t>Irritability and bad behavior</t>
-        </is>
-      </c>
-      <c r="H983" t="inlineStr">
-        <is>
-          <t>Dizziness</t>
-        </is>
-      </c>
-      <c r="I983" t="inlineStr">
-        <is>
-          <t>Tiredness</t>
-        </is>
-      </c>
-      <c r="J983" t="inlineStr">
-        <is>
-          <t>Dry skin</t>
-        </is>
-      </c>
-      <c r="R983" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="V983" t="inlineStr">
-        <is>
-          <t>QCS</t>
-        </is>
-      </c>
-      <c r="W983" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X983" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AB983" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AC983" t="inlineStr">
-        <is>
-          <t>Exams, End 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="984">
-      <c r="C984" t="inlineStr">
-        <is>
-          <t>A 35-year-old woman with a history of previous right thyroidectomy for a benign thyroid nodule now undergoes completion thyroidectomy for a suspicious thyroid mass. Several hours postoperatively, she developed progressive swelling under the incision, stridor, and difficulty breathing. Orotracheal intubation is successful. Which of the following is the most appropriate next step?</t>
-        </is>
-      </c>
-      <c r="F984" t="inlineStr">
-        <is>
-          <t>Fiberoptic laryngoscopy to rule out bilateral vocal cord paralysis</t>
-        </is>
-      </c>
-      <c r="G984" t="inlineStr">
-        <is>
-          <t>Administration of intravenous calcium</t>
-        </is>
-      </c>
-      <c r="H984" t="inlineStr">
-        <is>
-          <t>Administration of broad-spectrum antibiotics and debridement of the wound</t>
-        </is>
-      </c>
-      <c r="I984" t="inlineStr">
-        <is>
-          <t>Wound exploration</t>
-        </is>
-      </c>
-      <c r="J984" t="inlineStr">
-        <is>
-          <t>Administration of high-dose steroids and antihistamines</t>
-        </is>
-      </c>
-      <c r="R984" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="V984" t="inlineStr">
-        <is>
-          <t>QCS</t>
-        </is>
-      </c>
-      <c r="W984" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X984" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AB984" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AC984" t="inlineStr">
-        <is>
-          <t>Exams, End 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="985">
-      <c r="C985" t="inlineStr">
-        <is>
-          <t>A 36-year-old woman presents with palpitations, anxiety, and hypertension. The workup reveals a pheochromocytoma. Which of the following is the best approach to optimizing the patient preoperatively?</t>
-        </is>
-      </c>
-      <c r="F985" t="inlineStr">
-        <is>
-          <t>Fluid restriction 24 hours preoperatively to prevent intraoperative congestive heart failure.</t>
-        </is>
-      </c>
-      <c r="G985" t="inlineStr">
-        <is>
-          <t>Initiation of an α-blocker 24 hours prior to surgery</t>
-        </is>
-      </c>
-      <c r="H985" t="inlineStr">
-        <is>
-          <t>Initiation of an α-blocker at 1 to 3 weeks prior to surgery</t>
-        </is>
-      </c>
-      <c r="I985" t="inlineStr">
-        <is>
-          <t>Initiation of a β-blocker 1 to 3 weeks prior to surgery</t>
-        </is>
-      </c>
-      <c r="J985" t="inlineStr">
-        <is>
-          <t>Antihypertensive drug therapy with β-blockade followed by α-blockade starting at least 1 week prior to surgery.</t>
-        </is>
-      </c>
-      <c r="R985" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="V985" t="inlineStr">
-        <is>
-          <t>QCS</t>
-        </is>
-      </c>
-      <c r="W985" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X985" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AB985" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AC985" t="inlineStr">
-        <is>
-          <t>Exams, End 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="986">
-      <c r="C986" t="inlineStr">
-        <is>
-          <t>A 58-year-old man presents with tachycardia, fever, confusion, and vomiting. Workup reveals markedly elevated (triiodothyronine) T3 and (thyroxine) T4 levels. He is diagnosed as having a thyroid storm. Which of the following is the most appropriate next step in the management of this patient?</t>
-        </is>
-      </c>
-      <c r="F986" t="inlineStr">
-        <is>
-          <t>Emergent subtotal thyroidectomy</t>
-        </is>
-      </c>
-      <c r="G986" t="inlineStr">
-        <is>
-          <t>Emergent total thyroidectomy</t>
-        </is>
-      </c>
-      <c r="H986" t="inlineStr">
-        <is>
-          <t>Emergent hemodialysis</t>
-        </is>
-      </c>
-      <c r="I986" t="inlineStr">
-        <is>
-          <t>Administration of fluid, antithyroid drugs, β-blockers, iodine solution, and steroids</t>
-        </is>
-      </c>
-      <c r="J986" t="inlineStr">
-        <is>
-          <t>Emergent radiation therapy to the neck</t>
-        </is>
-      </c>
-      <c r="R986" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="V986" t="inlineStr">
-        <is>
-          <t>QCS</t>
-        </is>
-      </c>
-      <c r="W986" t="inlineStr">
-        <is>
-          <t>DamiettaFa_ENDOCRINOLOGY_2</t>
-        </is>
-      </c>
-      <c r="X986" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
-        </is>
-      </c>
-      <c r="AB986" t="n">
-        <v>2024</v>
-      </c>
-      <c r="AC986" t="inlineStr">
         <is>
           <t>Exams, End 2024</t>
         </is>

--- a/أزهر دمياط/Endocrinology/Endocrinology_Questions.xlsx
+++ b/أزهر دمياط/Endocrinology/Endocrinology_Questions.xlsx
@@ -22954,7 +22954,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>HbAIC 5.7-6.4 gm/dl</t>
+          <t>HbA1C 5.7-6.4 gm/dl</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -22969,7 +22969,7 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>It is not associated witty increased risk of macrovascular complications</t>
+          <t>It is not associated with increased risk of macrovascular complications</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -33534,12 +33534,12 @@
     <row r="641">
       <c r="C641" t="inlineStr">
         <is>
-          <t>Steps in the synthesis of thyro Except: id hormone include all of the following</t>
+          <t>Steps in the synthesis of thyroid hormone include all of the following Except:</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Coupling of iodo-tyrosines,</t>
+          <t>Coupling of iodo-tyrosines.</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
@@ -33549,12 +33549,12 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Form active thyroxine b y coupling iodo-tyrosines.</t>
+          <t>Linkage of iodine with tyrosine residues.</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>Von Hippel-Lindau syndrome.</t>
+          <t>Oxidation of iodide to iodine.</t>
         </is>
       </c>
       <c r="R641" t="inlineStr">
@@ -33960,7 +33960,7 @@
     <row r="649">
       <c r="C649" t="inlineStr">
         <is>
-          <t>The diagn osis of primary hyperparathyroidism is most strongly su ggested by:</t>
+          <t>The diagnosis of primary hyperparathyroidism is most strongly suggested by:</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
@@ -33970,22 +33970,22 @@
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>Serum alkaline phosphatase &gt; 120 IU/L,</t>
+          <t>Serum alkaline phosphatase &gt; 120 IU/L.</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Serum calcium &gt; 11 mg/dL,</t>
+          <t>Serum calcium &gt; 11 mg/dL.</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>Urinary calcium &lt;100 mg/day</t>
+          <t>Urinary calcium &lt;100 mg/day.</t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>Parathyroid hormone levels &lt; 5 pmol/L,</t>
+          <t>Parathyroid hormone levels &lt; 5 pmol/L.</t>
         </is>
       </c>
       <c r="R649" t="inlineStr">
@@ -35164,27 +35164,27 @@
     <row r="671">
       <c r="C671" t="inlineStr">
         <is>
-          <t>A 40-year-old male undergoes an aed ene r '. thyroidectomy for follicular carcinoma of develops circum-oral numbness, followed by laryngospasm, and then a generalized seizure. Of the following, which is the first priority 'or ex. operative site.</t>
+          <t>A 40-year-old male undergoes an apparently uneventful total thyroidectomy for follicular carcinoma of the thyroid. 48 hours later he develops circum-oral numbness, followed by laryngospasm, and then has a generalized seizure. Of the following, which is the first priority?</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>Proceed to OR for exploration of the of</t>
+          <t>Proceed to OR for exploration of the operative site.</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>Administer 25 ml of 10 calcium g 10% calet Jucon</t>
+          <t>Administer 25 ml of 10% calcium gluconate intravenously.</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Obtain a serum 1; and administer intravenous. jagnesium measurement chlonde STAT.</t>
+          <t>Obtain a serum magnesium measurement and administer intravenous magnesium chloride STAT.</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>Obtain a CT scan of the head to ev</t>
+          <t>Obtain a CT scan of the head to evaluate the possibility of brain metastases.</t>
         </is>
       </c>
       <c r="R671" t="inlineStr">
